--- a/Kalkulator_Kredytu_Hipotecznego.xlsx
+++ b/Kalkulator_Kredytu_Hipotecznego.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Nowa rata II okresu jest liczona od kolejnej raty po tym okresie</t>
+          <t>II okres zaczyna się od raty o numerze równym tej wartości</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C14" s="39">
-        <f>IF(C6&lt;=C9+1,0,ROUND(-PMT(C10/12,C6-C9-1,INDEX(Harmonogram!D:D,C9+4)),2))</f>
+        <f>IF(C6&lt;C9,0,ROUND(-PMT(C10/12,C6-C9+1,INDEX(Harmonogram!D:D,C9+2)),2))</f>
         <v/>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1102,7 +1102,7 @@
         <v/>
       </c>
       <c r="E3" s="17">
-        <f>IF(OR(D3&lt;=0,C3&gt;Parametry!$C$6),0,IF(C3&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D3&lt;=0,C3&gt;Parametry!$C$6),0,IF(C3&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F3" s="16">
@@ -1110,7 +1110,7 @@
         <v/>
       </c>
       <c r="G3" s="16">
-        <f>IF(OR(D3&lt;=0,C3&gt;Parametry!$C$6),0,MIN(IF(C3&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D3+F3,2)))</f>
+        <f>IF(OR(D3&lt;=0,C3&gt;Parametry!$C$6),0,MIN(IF(C3&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D3+F3,2)))</f>
         <v/>
       </c>
       <c r="H3" s="18" t="n"/>
@@ -1151,7 +1151,7 @@
         <v/>
       </c>
       <c r="E4" s="26">
-        <f>IF(OR(D4&lt;=0,C4&gt;Parametry!$C$6),0,IF(C4&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D4&lt;=0,C4&gt;Parametry!$C$6),0,IF(C4&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F4" s="25">
@@ -1159,7 +1159,7 @@
         <v/>
       </c>
       <c r="G4" s="25">
-        <f>IF(OR(D4&lt;=0,C4&gt;Parametry!$C$6),0,MIN(IF(C4&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D4+F4,2)))</f>
+        <f>IF(OR(D4&lt;=0,C4&gt;Parametry!$C$6),0,MIN(IF(C4&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D4+F4,2)))</f>
         <v/>
       </c>
       <c r="H4" s="18" t="n"/>
@@ -1200,7 +1200,7 @@
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>IF(OR(D5&lt;=0,C5&gt;Parametry!$C$6),0,IF(C5&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D5&lt;=0,C5&gt;Parametry!$C$6),0,IF(C5&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F5" s="16">
@@ -1208,7 +1208,7 @@
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>IF(OR(D5&lt;=0,C5&gt;Parametry!$C$6),0,MIN(IF(C5&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D5+F5,2)))</f>
+        <f>IF(OR(D5&lt;=0,C5&gt;Parametry!$C$6),0,MIN(IF(C5&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D5+F5,2)))</f>
         <v/>
       </c>
       <c r="H5" s="18" t="n"/>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>IF(OR(D6&lt;=0,C6&gt;Parametry!$C$6),0,IF(C6&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D6&lt;=0,C6&gt;Parametry!$C$6),0,IF(C6&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F6" s="25">
@@ -1257,7 +1257,7 @@
         <v/>
       </c>
       <c r="G6" s="25">
-        <f>IF(OR(D6&lt;=0,C6&gt;Parametry!$C$6),0,MIN(IF(C6&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D6+F6,2)))</f>
+        <f>IF(OR(D6&lt;=0,C6&gt;Parametry!$C$6),0,MIN(IF(C6&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D6+F6,2)))</f>
         <v/>
       </c>
       <c r="H6" s="18" t="n"/>
@@ -1298,7 +1298,7 @@
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>IF(OR(D7&lt;=0,C7&gt;Parametry!$C$6),0,IF(C7&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D7&lt;=0,C7&gt;Parametry!$C$6),0,IF(C7&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F7" s="16">
@@ -1306,7 +1306,7 @@
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>IF(OR(D7&lt;=0,C7&gt;Parametry!$C$6),0,MIN(IF(C7&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D7+F7,2)))</f>
+        <f>IF(OR(D7&lt;=0,C7&gt;Parametry!$C$6),0,MIN(IF(C7&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D7+F7,2)))</f>
         <v/>
       </c>
       <c r="H7" s="18" t="n"/>
@@ -1347,7 +1347,7 @@
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>IF(OR(D8&lt;=0,C8&gt;Parametry!$C$6),0,IF(C8&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D8&lt;=0,C8&gt;Parametry!$C$6),0,IF(C8&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F8" s="25">
@@ -1355,7 +1355,7 @@
         <v/>
       </c>
       <c r="G8" s="25">
-        <f>IF(OR(D8&lt;=0,C8&gt;Parametry!$C$6),0,MIN(IF(C8&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D8+F8,2)))</f>
+        <f>IF(OR(D8&lt;=0,C8&gt;Parametry!$C$6),0,MIN(IF(C8&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D8+F8,2)))</f>
         <v/>
       </c>
       <c r="H8" s="18" t="n"/>
@@ -1396,7 +1396,7 @@
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>IF(OR(D9&lt;=0,C9&gt;Parametry!$C$6),0,IF(C9&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D9&lt;=0,C9&gt;Parametry!$C$6),0,IF(C9&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F9" s="16">
@@ -1404,7 +1404,7 @@
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>IF(OR(D9&lt;=0,C9&gt;Parametry!$C$6),0,MIN(IF(C9&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D9+F9,2)))</f>
+        <f>IF(OR(D9&lt;=0,C9&gt;Parametry!$C$6),0,MIN(IF(C9&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D9+F9,2)))</f>
         <v/>
       </c>
       <c r="H9" s="18" t="n"/>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="E10" s="26">
-        <f>IF(OR(D10&lt;=0,C10&gt;Parametry!$C$6),0,IF(C10&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D10&lt;=0,C10&gt;Parametry!$C$6),0,IF(C10&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F10" s="25">
@@ -1453,7 +1453,7 @@
         <v/>
       </c>
       <c r="G10" s="25">
-        <f>IF(OR(D10&lt;=0,C10&gt;Parametry!$C$6),0,MIN(IF(C10&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D10+F10,2)))</f>
+        <f>IF(OR(D10&lt;=0,C10&gt;Parametry!$C$6),0,MIN(IF(C10&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D10+F10,2)))</f>
         <v/>
       </c>
       <c r="H10" s="18" t="n"/>
@@ -1494,7 +1494,7 @@
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>IF(OR(D11&lt;=0,C11&gt;Parametry!$C$6),0,IF(C11&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D11&lt;=0,C11&gt;Parametry!$C$6),0,IF(C11&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F11" s="16">
@@ -1502,7 +1502,7 @@
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>IF(OR(D11&lt;=0,C11&gt;Parametry!$C$6),0,MIN(IF(C11&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D11+F11,2)))</f>
+        <f>IF(OR(D11&lt;=0,C11&gt;Parametry!$C$6),0,MIN(IF(C11&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D11+F11,2)))</f>
         <v/>
       </c>
       <c r="H11" s="18" t="n"/>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="E12" s="26">
-        <f>IF(OR(D12&lt;=0,C12&gt;Parametry!$C$6),0,IF(C12&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D12&lt;=0,C12&gt;Parametry!$C$6),0,IF(C12&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F12" s="25">
@@ -1551,7 +1551,7 @@
         <v/>
       </c>
       <c r="G12" s="25">
-        <f>IF(OR(D12&lt;=0,C12&gt;Parametry!$C$6),0,MIN(IF(C12&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D12+F12,2)))</f>
+        <f>IF(OR(D12&lt;=0,C12&gt;Parametry!$C$6),0,MIN(IF(C12&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D12+F12,2)))</f>
         <v/>
       </c>
       <c r="H12" s="18" t="n"/>
@@ -1592,7 +1592,7 @@
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>IF(OR(D13&lt;=0,C13&gt;Parametry!$C$6),0,IF(C13&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D13&lt;=0,C13&gt;Parametry!$C$6),0,IF(C13&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F13" s="16">
@@ -1600,7 +1600,7 @@
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>IF(OR(D13&lt;=0,C13&gt;Parametry!$C$6),0,MIN(IF(C13&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D13+F13,2)))</f>
+        <f>IF(OR(D13&lt;=0,C13&gt;Parametry!$C$6),0,MIN(IF(C13&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D13+F13,2)))</f>
         <v/>
       </c>
       <c r="H13" s="18" t="n"/>
@@ -1641,7 +1641,7 @@
         <v/>
       </c>
       <c r="E14" s="26">
-        <f>IF(OR(D14&lt;=0,C14&gt;Parametry!$C$6),0,IF(C14&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D14&lt;=0,C14&gt;Parametry!$C$6),0,IF(C14&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F14" s="25">
@@ -1649,7 +1649,7 @@
         <v/>
       </c>
       <c r="G14" s="25">
-        <f>IF(OR(D14&lt;=0,C14&gt;Parametry!$C$6),0,MIN(IF(C14&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D14+F14,2)))</f>
+        <f>IF(OR(D14&lt;=0,C14&gt;Parametry!$C$6),0,MIN(IF(C14&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D14+F14,2)))</f>
         <v/>
       </c>
       <c r="H14" s="18" t="n"/>
@@ -1690,7 +1690,7 @@
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>IF(OR(D15&lt;=0,C15&gt;Parametry!$C$6),0,IF(C15&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D15&lt;=0,C15&gt;Parametry!$C$6),0,IF(C15&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F15" s="16">
@@ -1698,7 +1698,7 @@
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>IF(OR(D15&lt;=0,C15&gt;Parametry!$C$6),0,MIN(IF(C15&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D15+F15,2)))</f>
+        <f>IF(OR(D15&lt;=0,C15&gt;Parametry!$C$6),0,MIN(IF(C15&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D15+F15,2)))</f>
         <v/>
       </c>
       <c r="H15" s="18" t="n"/>
@@ -1739,7 +1739,7 @@
         <v/>
       </c>
       <c r="E16" s="26">
-        <f>IF(OR(D16&lt;=0,C16&gt;Parametry!$C$6),0,IF(C16&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D16&lt;=0,C16&gt;Parametry!$C$6),0,IF(C16&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F16" s="25">
@@ -1747,7 +1747,7 @@
         <v/>
       </c>
       <c r="G16" s="25">
-        <f>IF(OR(D16&lt;=0,C16&gt;Parametry!$C$6),0,MIN(IF(C16&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D16+F16,2)))</f>
+        <f>IF(OR(D16&lt;=0,C16&gt;Parametry!$C$6),0,MIN(IF(C16&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D16+F16,2)))</f>
         <v/>
       </c>
       <c r="H16" s="18" t="n"/>
@@ -1788,7 +1788,7 @@
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>IF(OR(D17&lt;=0,C17&gt;Parametry!$C$6),0,IF(C17&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D17&lt;=0,C17&gt;Parametry!$C$6),0,IF(C17&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F17" s="16">
@@ -1796,7 +1796,7 @@
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>IF(OR(D17&lt;=0,C17&gt;Parametry!$C$6),0,MIN(IF(C17&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D17+F17,2)))</f>
+        <f>IF(OR(D17&lt;=0,C17&gt;Parametry!$C$6),0,MIN(IF(C17&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D17+F17,2)))</f>
         <v/>
       </c>
       <c r="H17" s="18" t="n"/>
@@ -1837,7 +1837,7 @@
         <v/>
       </c>
       <c r="E18" s="26">
-        <f>IF(OR(D18&lt;=0,C18&gt;Parametry!$C$6),0,IF(C18&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D18&lt;=0,C18&gt;Parametry!$C$6),0,IF(C18&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F18" s="25">
@@ -1845,7 +1845,7 @@
         <v/>
       </c>
       <c r="G18" s="25">
-        <f>IF(OR(D18&lt;=0,C18&gt;Parametry!$C$6),0,MIN(IF(C18&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D18+F18,2)))</f>
+        <f>IF(OR(D18&lt;=0,C18&gt;Parametry!$C$6),0,MIN(IF(C18&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D18+F18,2)))</f>
         <v/>
       </c>
       <c r="H18" s="18" t="n"/>
@@ -1886,7 +1886,7 @@
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>IF(OR(D19&lt;=0,C19&gt;Parametry!$C$6),0,IF(C19&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D19&lt;=0,C19&gt;Parametry!$C$6),0,IF(C19&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F19" s="16">
@@ -1894,7 +1894,7 @@
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>IF(OR(D19&lt;=0,C19&gt;Parametry!$C$6),0,MIN(IF(C19&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D19+F19,2)))</f>
+        <f>IF(OR(D19&lt;=0,C19&gt;Parametry!$C$6),0,MIN(IF(C19&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D19+F19,2)))</f>
         <v/>
       </c>
       <c r="H19" s="18" t="n"/>
@@ -1935,7 +1935,7 @@
         <v/>
       </c>
       <c r="E20" s="26">
-        <f>IF(OR(D20&lt;=0,C20&gt;Parametry!$C$6),0,IF(C20&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D20&lt;=0,C20&gt;Parametry!$C$6),0,IF(C20&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F20" s="25">
@@ -1943,7 +1943,7 @@
         <v/>
       </c>
       <c r="G20" s="25">
-        <f>IF(OR(D20&lt;=0,C20&gt;Parametry!$C$6),0,MIN(IF(C20&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D20+F20,2)))</f>
+        <f>IF(OR(D20&lt;=0,C20&gt;Parametry!$C$6),0,MIN(IF(C20&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D20+F20,2)))</f>
         <v/>
       </c>
       <c r="H20" s="18" t="n"/>
@@ -1984,7 +1984,7 @@
         <v/>
       </c>
       <c r="E21" s="17">
-        <f>IF(OR(D21&lt;=0,C21&gt;Parametry!$C$6),0,IF(C21&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D21&lt;=0,C21&gt;Parametry!$C$6),0,IF(C21&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F21" s="16">
@@ -1992,7 +1992,7 @@
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>IF(OR(D21&lt;=0,C21&gt;Parametry!$C$6),0,MIN(IF(C21&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D21+F21,2)))</f>
+        <f>IF(OR(D21&lt;=0,C21&gt;Parametry!$C$6),0,MIN(IF(C21&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D21+F21,2)))</f>
         <v/>
       </c>
       <c r="H21" s="18" t="n"/>
@@ -2033,7 +2033,7 @@
         <v/>
       </c>
       <c r="E22" s="26">
-        <f>IF(OR(D22&lt;=0,C22&gt;Parametry!$C$6),0,IF(C22&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D22&lt;=0,C22&gt;Parametry!$C$6),0,IF(C22&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F22" s="25">
@@ -2041,7 +2041,7 @@
         <v/>
       </c>
       <c r="G22" s="25">
-        <f>IF(OR(D22&lt;=0,C22&gt;Parametry!$C$6),0,MIN(IF(C22&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D22+F22,2)))</f>
+        <f>IF(OR(D22&lt;=0,C22&gt;Parametry!$C$6),0,MIN(IF(C22&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D22+F22,2)))</f>
         <v/>
       </c>
       <c r="H22" s="18" t="n"/>
@@ -2082,7 +2082,7 @@
         <v/>
       </c>
       <c r="E23" s="17">
-        <f>IF(OR(D23&lt;=0,C23&gt;Parametry!$C$6),0,IF(C23&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D23&lt;=0,C23&gt;Parametry!$C$6),0,IF(C23&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F23" s="16">
@@ -2090,7 +2090,7 @@
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>IF(OR(D23&lt;=0,C23&gt;Parametry!$C$6),0,MIN(IF(C23&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D23+F23,2)))</f>
+        <f>IF(OR(D23&lt;=0,C23&gt;Parametry!$C$6),0,MIN(IF(C23&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D23+F23,2)))</f>
         <v/>
       </c>
       <c r="H23" s="18" t="n"/>
@@ -2131,7 +2131,7 @@
         <v/>
       </c>
       <c r="E24" s="26">
-        <f>IF(OR(D24&lt;=0,C24&gt;Parametry!$C$6),0,IF(C24&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D24&lt;=0,C24&gt;Parametry!$C$6),0,IF(C24&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F24" s="25">
@@ -2139,7 +2139,7 @@
         <v/>
       </c>
       <c r="G24" s="25">
-        <f>IF(OR(D24&lt;=0,C24&gt;Parametry!$C$6),0,MIN(IF(C24&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D24+F24,2)))</f>
+        <f>IF(OR(D24&lt;=0,C24&gt;Parametry!$C$6),0,MIN(IF(C24&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D24+F24,2)))</f>
         <v/>
       </c>
       <c r="H24" s="18" t="n"/>
@@ -2180,7 +2180,7 @@
         <v/>
       </c>
       <c r="E25" s="17">
-        <f>IF(OR(D25&lt;=0,C25&gt;Parametry!$C$6),0,IF(C25&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D25&lt;=0,C25&gt;Parametry!$C$6),0,IF(C25&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F25" s="16">
@@ -2188,7 +2188,7 @@
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>IF(OR(D25&lt;=0,C25&gt;Parametry!$C$6),0,MIN(IF(C25&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D25+F25,2)))</f>
+        <f>IF(OR(D25&lt;=0,C25&gt;Parametry!$C$6),0,MIN(IF(C25&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D25+F25,2)))</f>
         <v/>
       </c>
       <c r="H25" s="18" t="n"/>
@@ -2229,7 +2229,7 @@
         <v/>
       </c>
       <c r="E26" s="26">
-        <f>IF(OR(D26&lt;=0,C26&gt;Parametry!$C$6),0,IF(C26&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D26&lt;=0,C26&gt;Parametry!$C$6),0,IF(C26&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F26" s="25">
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="G26" s="25">
-        <f>IF(OR(D26&lt;=0,C26&gt;Parametry!$C$6),0,MIN(IF(C26&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D26+F26,2)))</f>
+        <f>IF(OR(D26&lt;=0,C26&gt;Parametry!$C$6),0,MIN(IF(C26&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D26+F26,2)))</f>
         <v/>
       </c>
       <c r="H26" s="18" t="n"/>
@@ -2278,7 +2278,7 @@
         <v/>
       </c>
       <c r="E27" s="17">
-        <f>IF(OR(D27&lt;=0,C27&gt;Parametry!$C$6),0,IF(C27&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D27&lt;=0,C27&gt;Parametry!$C$6),0,IF(C27&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F27" s="16">
@@ -2286,7 +2286,7 @@
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>IF(OR(D27&lt;=0,C27&gt;Parametry!$C$6),0,MIN(IF(C27&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D27+F27,2)))</f>
+        <f>IF(OR(D27&lt;=0,C27&gt;Parametry!$C$6),0,MIN(IF(C27&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D27+F27,2)))</f>
         <v/>
       </c>
       <c r="H27" s="18" t="n"/>
@@ -2327,7 +2327,7 @@
         <v/>
       </c>
       <c r="E28" s="26">
-        <f>IF(OR(D28&lt;=0,C28&gt;Parametry!$C$6),0,IF(C28&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D28&lt;=0,C28&gt;Parametry!$C$6),0,IF(C28&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F28" s="25">
@@ -2335,7 +2335,7 @@
         <v/>
       </c>
       <c r="G28" s="25">
-        <f>IF(OR(D28&lt;=0,C28&gt;Parametry!$C$6),0,MIN(IF(C28&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D28+F28,2)))</f>
+        <f>IF(OR(D28&lt;=0,C28&gt;Parametry!$C$6),0,MIN(IF(C28&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D28+F28,2)))</f>
         <v/>
       </c>
       <c r="H28" s="18" t="n"/>
@@ -2376,7 +2376,7 @@
         <v/>
       </c>
       <c r="E29" s="17">
-        <f>IF(OR(D29&lt;=0,C29&gt;Parametry!$C$6),0,IF(C29&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D29&lt;=0,C29&gt;Parametry!$C$6),0,IF(C29&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F29" s="16">
@@ -2384,7 +2384,7 @@
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>IF(OR(D29&lt;=0,C29&gt;Parametry!$C$6),0,MIN(IF(C29&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D29+F29,2)))</f>
+        <f>IF(OR(D29&lt;=0,C29&gt;Parametry!$C$6),0,MIN(IF(C29&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D29+F29,2)))</f>
         <v/>
       </c>
       <c r="H29" s="18" t="n"/>
@@ -2425,7 +2425,7 @@
         <v/>
       </c>
       <c r="E30" s="26">
-        <f>IF(OR(D30&lt;=0,C30&gt;Parametry!$C$6),0,IF(C30&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D30&lt;=0,C30&gt;Parametry!$C$6),0,IF(C30&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F30" s="25">
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="G30" s="25">
-        <f>IF(OR(D30&lt;=0,C30&gt;Parametry!$C$6),0,MIN(IF(C30&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D30+F30,2)))</f>
+        <f>IF(OR(D30&lt;=0,C30&gt;Parametry!$C$6),0,MIN(IF(C30&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D30+F30,2)))</f>
         <v/>
       </c>
       <c r="H30" s="18" t="n"/>
@@ -2474,7 +2474,7 @@
         <v/>
       </c>
       <c r="E31" s="17">
-        <f>IF(OR(D31&lt;=0,C31&gt;Parametry!$C$6),0,IF(C31&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D31&lt;=0,C31&gt;Parametry!$C$6),0,IF(C31&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F31" s="16">
@@ -2482,7 +2482,7 @@
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>IF(OR(D31&lt;=0,C31&gt;Parametry!$C$6),0,MIN(IF(C31&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D31+F31,2)))</f>
+        <f>IF(OR(D31&lt;=0,C31&gt;Parametry!$C$6),0,MIN(IF(C31&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D31+F31,2)))</f>
         <v/>
       </c>
       <c r="H31" s="18" t="n"/>
@@ -2523,7 +2523,7 @@
         <v/>
       </c>
       <c r="E32" s="26">
-        <f>IF(OR(D32&lt;=0,C32&gt;Parametry!$C$6),0,IF(C32&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D32&lt;=0,C32&gt;Parametry!$C$6),0,IF(C32&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F32" s="25">
@@ -2531,7 +2531,7 @@
         <v/>
       </c>
       <c r="G32" s="25">
-        <f>IF(OR(D32&lt;=0,C32&gt;Parametry!$C$6),0,MIN(IF(C32&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D32+F32,2)))</f>
+        <f>IF(OR(D32&lt;=0,C32&gt;Parametry!$C$6),0,MIN(IF(C32&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D32+F32,2)))</f>
         <v/>
       </c>
       <c r="H32" s="18" t="n"/>
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="E33" s="17">
-        <f>IF(OR(D33&lt;=0,C33&gt;Parametry!$C$6),0,IF(C33&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D33&lt;=0,C33&gt;Parametry!$C$6),0,IF(C33&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F33" s="16">
@@ -2580,7 +2580,7 @@
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>IF(OR(D33&lt;=0,C33&gt;Parametry!$C$6),0,MIN(IF(C33&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D33+F33,2)))</f>
+        <f>IF(OR(D33&lt;=0,C33&gt;Parametry!$C$6),0,MIN(IF(C33&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D33+F33,2)))</f>
         <v/>
       </c>
       <c r="H33" s="18" t="n"/>
@@ -2621,7 +2621,7 @@
         <v/>
       </c>
       <c r="E34" s="26">
-        <f>IF(OR(D34&lt;=0,C34&gt;Parametry!$C$6),0,IF(C34&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D34&lt;=0,C34&gt;Parametry!$C$6),0,IF(C34&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F34" s="25">
@@ -2629,7 +2629,7 @@
         <v/>
       </c>
       <c r="G34" s="25">
-        <f>IF(OR(D34&lt;=0,C34&gt;Parametry!$C$6),0,MIN(IF(C34&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D34+F34,2)))</f>
+        <f>IF(OR(D34&lt;=0,C34&gt;Parametry!$C$6),0,MIN(IF(C34&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D34+F34,2)))</f>
         <v/>
       </c>
       <c r="H34" s="18" t="n"/>
@@ -2670,7 +2670,7 @@
         <v/>
       </c>
       <c r="E35" s="17">
-        <f>IF(OR(D35&lt;=0,C35&gt;Parametry!$C$6),0,IF(C35&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D35&lt;=0,C35&gt;Parametry!$C$6),0,IF(C35&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F35" s="16">
@@ -2678,7 +2678,7 @@
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>IF(OR(D35&lt;=0,C35&gt;Parametry!$C$6),0,MIN(IF(C35&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D35+F35,2)))</f>
+        <f>IF(OR(D35&lt;=0,C35&gt;Parametry!$C$6),0,MIN(IF(C35&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D35+F35,2)))</f>
         <v/>
       </c>
       <c r="H35" s="18" t="n"/>
@@ -2719,7 +2719,7 @@
         <v/>
       </c>
       <c r="E36" s="26">
-        <f>IF(OR(D36&lt;=0,C36&gt;Parametry!$C$6),0,IF(C36&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D36&lt;=0,C36&gt;Parametry!$C$6),0,IF(C36&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F36" s="25">
@@ -2727,7 +2727,7 @@
         <v/>
       </c>
       <c r="G36" s="25">
-        <f>IF(OR(D36&lt;=0,C36&gt;Parametry!$C$6),0,MIN(IF(C36&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D36+F36,2)))</f>
+        <f>IF(OR(D36&lt;=0,C36&gt;Parametry!$C$6),0,MIN(IF(C36&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D36+F36,2)))</f>
         <v/>
       </c>
       <c r="H36" s="18" t="n"/>
@@ -2768,7 +2768,7 @@
         <v/>
       </c>
       <c r="E37" s="17">
-        <f>IF(OR(D37&lt;=0,C37&gt;Parametry!$C$6),0,IF(C37&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D37&lt;=0,C37&gt;Parametry!$C$6),0,IF(C37&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F37" s="16">
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="G37" s="16">
-        <f>IF(OR(D37&lt;=0,C37&gt;Parametry!$C$6),0,MIN(IF(C37&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D37+F37,2)))</f>
+        <f>IF(OR(D37&lt;=0,C37&gt;Parametry!$C$6),0,MIN(IF(C37&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D37+F37,2)))</f>
         <v/>
       </c>
       <c r="H37" s="18" t="n"/>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="E38" s="26">
-        <f>IF(OR(D38&lt;=0,C38&gt;Parametry!$C$6),0,IF(C38&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D38&lt;=0,C38&gt;Parametry!$C$6),0,IF(C38&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F38" s="25">
@@ -2825,7 +2825,7 @@
         <v/>
       </c>
       <c r="G38" s="25">
-        <f>IF(OR(D38&lt;=0,C38&gt;Parametry!$C$6),0,MIN(IF(C38&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D38+F38,2)))</f>
+        <f>IF(OR(D38&lt;=0,C38&gt;Parametry!$C$6),0,MIN(IF(C38&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D38+F38,2)))</f>
         <v/>
       </c>
       <c r="H38" s="18" t="n"/>
@@ -2866,7 +2866,7 @@
         <v/>
       </c>
       <c r="E39" s="17">
-        <f>IF(OR(D39&lt;=0,C39&gt;Parametry!$C$6),0,IF(C39&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D39&lt;=0,C39&gt;Parametry!$C$6),0,IF(C39&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F39" s="16">
@@ -2874,7 +2874,7 @@
         <v/>
       </c>
       <c r="G39" s="16">
-        <f>IF(OR(D39&lt;=0,C39&gt;Parametry!$C$6),0,MIN(IF(C39&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D39+F39,2)))</f>
+        <f>IF(OR(D39&lt;=0,C39&gt;Parametry!$C$6),0,MIN(IF(C39&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D39+F39,2)))</f>
         <v/>
       </c>
       <c r="H39" s="18" t="n"/>
@@ -2915,7 +2915,7 @@
         <v/>
       </c>
       <c r="E40" s="26">
-        <f>IF(OR(D40&lt;=0,C40&gt;Parametry!$C$6),0,IF(C40&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D40&lt;=0,C40&gt;Parametry!$C$6),0,IF(C40&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F40" s="25">
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="G40" s="25">
-        <f>IF(OR(D40&lt;=0,C40&gt;Parametry!$C$6),0,MIN(IF(C40&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D40+F40,2)))</f>
+        <f>IF(OR(D40&lt;=0,C40&gt;Parametry!$C$6),0,MIN(IF(C40&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D40+F40,2)))</f>
         <v/>
       </c>
       <c r="H40" s="18" t="n"/>
@@ -2964,7 +2964,7 @@
         <v/>
       </c>
       <c r="E41" s="17">
-        <f>IF(OR(D41&lt;=0,C41&gt;Parametry!$C$6),0,IF(C41&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D41&lt;=0,C41&gt;Parametry!$C$6),0,IF(C41&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F41" s="16">
@@ -2972,7 +2972,7 @@
         <v/>
       </c>
       <c r="G41" s="16">
-        <f>IF(OR(D41&lt;=0,C41&gt;Parametry!$C$6),0,MIN(IF(C41&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D41+F41,2)))</f>
+        <f>IF(OR(D41&lt;=0,C41&gt;Parametry!$C$6),0,MIN(IF(C41&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D41+F41,2)))</f>
         <v/>
       </c>
       <c r="H41" s="18" t="n"/>
@@ -3013,7 +3013,7 @@
         <v/>
       </c>
       <c r="E42" s="26">
-        <f>IF(OR(D42&lt;=0,C42&gt;Parametry!$C$6),0,IF(C42&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D42&lt;=0,C42&gt;Parametry!$C$6),0,IF(C42&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F42" s="25">
@@ -3021,7 +3021,7 @@
         <v/>
       </c>
       <c r="G42" s="25">
-        <f>IF(OR(D42&lt;=0,C42&gt;Parametry!$C$6),0,MIN(IF(C42&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D42+F42,2)))</f>
+        <f>IF(OR(D42&lt;=0,C42&gt;Parametry!$C$6),0,MIN(IF(C42&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D42+F42,2)))</f>
         <v/>
       </c>
       <c r="H42" s="18" t="n"/>
@@ -3062,7 +3062,7 @@
         <v/>
       </c>
       <c r="E43" s="17">
-        <f>IF(OR(D43&lt;=0,C43&gt;Parametry!$C$6),0,IF(C43&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D43&lt;=0,C43&gt;Parametry!$C$6),0,IF(C43&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F43" s="16">
@@ -3070,7 +3070,7 @@
         <v/>
       </c>
       <c r="G43" s="16">
-        <f>IF(OR(D43&lt;=0,C43&gt;Parametry!$C$6),0,MIN(IF(C43&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D43+F43,2)))</f>
+        <f>IF(OR(D43&lt;=0,C43&gt;Parametry!$C$6),0,MIN(IF(C43&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D43+F43,2)))</f>
         <v/>
       </c>
       <c r="H43" s="18" t="n"/>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="E44" s="26">
-        <f>IF(OR(D44&lt;=0,C44&gt;Parametry!$C$6),0,IF(C44&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D44&lt;=0,C44&gt;Parametry!$C$6),0,IF(C44&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F44" s="25">
@@ -3119,7 +3119,7 @@
         <v/>
       </c>
       <c r="G44" s="25">
-        <f>IF(OR(D44&lt;=0,C44&gt;Parametry!$C$6),0,MIN(IF(C44&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D44+F44,2)))</f>
+        <f>IF(OR(D44&lt;=0,C44&gt;Parametry!$C$6),0,MIN(IF(C44&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D44+F44,2)))</f>
         <v/>
       </c>
       <c r="H44" s="18" t="n"/>
@@ -3160,7 +3160,7 @@
         <v/>
       </c>
       <c r="E45" s="17">
-        <f>IF(OR(D45&lt;=0,C45&gt;Parametry!$C$6),0,IF(C45&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D45&lt;=0,C45&gt;Parametry!$C$6),0,IF(C45&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F45" s="16">
@@ -3168,7 +3168,7 @@
         <v/>
       </c>
       <c r="G45" s="16">
-        <f>IF(OR(D45&lt;=0,C45&gt;Parametry!$C$6),0,MIN(IF(C45&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D45+F45,2)))</f>
+        <f>IF(OR(D45&lt;=0,C45&gt;Parametry!$C$6),0,MIN(IF(C45&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D45+F45,2)))</f>
         <v/>
       </c>
       <c r="H45" s="18" t="n"/>
@@ -3209,7 +3209,7 @@
         <v/>
       </c>
       <c r="E46" s="26">
-        <f>IF(OR(D46&lt;=0,C46&gt;Parametry!$C$6),0,IF(C46&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D46&lt;=0,C46&gt;Parametry!$C$6),0,IF(C46&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F46" s="25">
@@ -3217,7 +3217,7 @@
         <v/>
       </c>
       <c r="G46" s="25">
-        <f>IF(OR(D46&lt;=0,C46&gt;Parametry!$C$6),0,MIN(IF(C46&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D46+F46,2)))</f>
+        <f>IF(OR(D46&lt;=0,C46&gt;Parametry!$C$6),0,MIN(IF(C46&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D46+F46,2)))</f>
         <v/>
       </c>
       <c r="H46" s="18" t="n"/>
@@ -3258,7 +3258,7 @@
         <v/>
       </c>
       <c r="E47" s="17">
-        <f>IF(OR(D47&lt;=0,C47&gt;Parametry!$C$6),0,IF(C47&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D47&lt;=0,C47&gt;Parametry!$C$6),0,IF(C47&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F47" s="16">
@@ -3266,7 +3266,7 @@
         <v/>
       </c>
       <c r="G47" s="16">
-        <f>IF(OR(D47&lt;=0,C47&gt;Parametry!$C$6),0,MIN(IF(C47&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D47+F47,2)))</f>
+        <f>IF(OR(D47&lt;=0,C47&gt;Parametry!$C$6),0,MIN(IF(C47&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D47+F47,2)))</f>
         <v/>
       </c>
       <c r="H47" s="18" t="n"/>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="E48" s="26">
-        <f>IF(OR(D48&lt;=0,C48&gt;Parametry!$C$6),0,IF(C48&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D48&lt;=0,C48&gt;Parametry!$C$6),0,IF(C48&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F48" s="25">
@@ -3315,7 +3315,7 @@
         <v/>
       </c>
       <c r="G48" s="25">
-        <f>IF(OR(D48&lt;=0,C48&gt;Parametry!$C$6),0,MIN(IF(C48&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D48+F48,2)))</f>
+        <f>IF(OR(D48&lt;=0,C48&gt;Parametry!$C$6),0,MIN(IF(C48&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D48+F48,2)))</f>
         <v/>
       </c>
       <c r="H48" s="18" t="n"/>
@@ -3356,7 +3356,7 @@
         <v/>
       </c>
       <c r="E49" s="17">
-        <f>IF(OR(D49&lt;=0,C49&gt;Parametry!$C$6),0,IF(C49&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D49&lt;=0,C49&gt;Parametry!$C$6),0,IF(C49&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F49" s="16">
@@ -3364,7 +3364,7 @@
         <v/>
       </c>
       <c r="G49" s="16">
-        <f>IF(OR(D49&lt;=0,C49&gt;Parametry!$C$6),0,MIN(IF(C49&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D49+F49,2)))</f>
+        <f>IF(OR(D49&lt;=0,C49&gt;Parametry!$C$6),0,MIN(IF(C49&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D49+F49,2)))</f>
         <v/>
       </c>
       <c r="H49" s="18" t="n"/>
@@ -3405,7 +3405,7 @@
         <v/>
       </c>
       <c r="E50" s="26">
-        <f>IF(OR(D50&lt;=0,C50&gt;Parametry!$C$6),0,IF(C50&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D50&lt;=0,C50&gt;Parametry!$C$6),0,IF(C50&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F50" s="25">
@@ -3413,7 +3413,7 @@
         <v/>
       </c>
       <c r="G50" s="25">
-        <f>IF(OR(D50&lt;=0,C50&gt;Parametry!$C$6),0,MIN(IF(C50&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D50+F50,2)))</f>
+        <f>IF(OR(D50&lt;=0,C50&gt;Parametry!$C$6),0,MIN(IF(C50&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D50+F50,2)))</f>
         <v/>
       </c>
       <c r="H50" s="18" t="n"/>
@@ -3454,7 +3454,7 @@
         <v/>
       </c>
       <c r="E51" s="17">
-        <f>IF(OR(D51&lt;=0,C51&gt;Parametry!$C$6),0,IF(C51&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D51&lt;=0,C51&gt;Parametry!$C$6),0,IF(C51&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F51" s="16">
@@ -3462,7 +3462,7 @@
         <v/>
       </c>
       <c r="G51" s="16">
-        <f>IF(OR(D51&lt;=0,C51&gt;Parametry!$C$6),0,MIN(IF(C51&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D51+F51,2)))</f>
+        <f>IF(OR(D51&lt;=0,C51&gt;Parametry!$C$6),0,MIN(IF(C51&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D51+F51,2)))</f>
         <v/>
       </c>
       <c r="H51" s="18" t="n"/>
@@ -3503,7 +3503,7 @@
         <v/>
       </c>
       <c r="E52" s="26">
-        <f>IF(OR(D52&lt;=0,C52&gt;Parametry!$C$6),0,IF(C52&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D52&lt;=0,C52&gt;Parametry!$C$6),0,IF(C52&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F52" s="25">
@@ -3511,7 +3511,7 @@
         <v/>
       </c>
       <c r="G52" s="25">
-        <f>IF(OR(D52&lt;=0,C52&gt;Parametry!$C$6),0,MIN(IF(C52&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D52+F52,2)))</f>
+        <f>IF(OR(D52&lt;=0,C52&gt;Parametry!$C$6),0,MIN(IF(C52&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D52+F52,2)))</f>
         <v/>
       </c>
       <c r="H52" s="18" t="n"/>
@@ -3552,7 +3552,7 @@
         <v/>
       </c>
       <c r="E53" s="17">
-        <f>IF(OR(D53&lt;=0,C53&gt;Parametry!$C$6),0,IF(C53&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D53&lt;=0,C53&gt;Parametry!$C$6),0,IF(C53&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F53" s="16">
@@ -3560,7 +3560,7 @@
         <v/>
       </c>
       <c r="G53" s="16">
-        <f>IF(OR(D53&lt;=0,C53&gt;Parametry!$C$6),0,MIN(IF(C53&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D53+F53,2)))</f>
+        <f>IF(OR(D53&lt;=0,C53&gt;Parametry!$C$6),0,MIN(IF(C53&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D53+F53,2)))</f>
         <v/>
       </c>
       <c r="H53" s="18" t="n"/>
@@ -3601,7 +3601,7 @@
         <v/>
       </c>
       <c r="E54" s="26">
-        <f>IF(OR(D54&lt;=0,C54&gt;Parametry!$C$6),0,IF(C54&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D54&lt;=0,C54&gt;Parametry!$C$6),0,IF(C54&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F54" s="25">
@@ -3609,7 +3609,7 @@
         <v/>
       </c>
       <c r="G54" s="25">
-        <f>IF(OR(D54&lt;=0,C54&gt;Parametry!$C$6),0,MIN(IF(C54&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D54+F54,2)))</f>
+        <f>IF(OR(D54&lt;=0,C54&gt;Parametry!$C$6),0,MIN(IF(C54&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D54+F54,2)))</f>
         <v/>
       </c>
       <c r="H54" s="18" t="n"/>
@@ -3650,7 +3650,7 @@
         <v/>
       </c>
       <c r="E55" s="17">
-        <f>IF(OR(D55&lt;=0,C55&gt;Parametry!$C$6),0,IF(C55&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D55&lt;=0,C55&gt;Parametry!$C$6),0,IF(C55&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F55" s="16">
@@ -3658,7 +3658,7 @@
         <v/>
       </c>
       <c r="G55" s="16">
-        <f>IF(OR(D55&lt;=0,C55&gt;Parametry!$C$6),0,MIN(IF(C55&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D55+F55,2)))</f>
+        <f>IF(OR(D55&lt;=0,C55&gt;Parametry!$C$6),0,MIN(IF(C55&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D55+F55,2)))</f>
         <v/>
       </c>
       <c r="H55" s="18" t="n"/>
@@ -3699,7 +3699,7 @@
         <v/>
       </c>
       <c r="E56" s="26">
-        <f>IF(OR(D56&lt;=0,C56&gt;Parametry!$C$6),0,IF(C56&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D56&lt;=0,C56&gt;Parametry!$C$6),0,IF(C56&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F56" s="25">
@@ -3707,7 +3707,7 @@
         <v/>
       </c>
       <c r="G56" s="25">
-        <f>IF(OR(D56&lt;=0,C56&gt;Parametry!$C$6),0,MIN(IF(C56&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D56+F56,2)))</f>
+        <f>IF(OR(D56&lt;=0,C56&gt;Parametry!$C$6),0,MIN(IF(C56&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D56+F56,2)))</f>
         <v/>
       </c>
       <c r="H56" s="18" t="n"/>
@@ -3748,7 +3748,7 @@
         <v/>
       </c>
       <c r="E57" s="17">
-        <f>IF(OR(D57&lt;=0,C57&gt;Parametry!$C$6),0,IF(C57&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D57&lt;=0,C57&gt;Parametry!$C$6),0,IF(C57&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F57" s="16">
@@ -3756,7 +3756,7 @@
         <v/>
       </c>
       <c r="G57" s="16">
-        <f>IF(OR(D57&lt;=0,C57&gt;Parametry!$C$6),0,MIN(IF(C57&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D57+F57,2)))</f>
+        <f>IF(OR(D57&lt;=0,C57&gt;Parametry!$C$6),0,MIN(IF(C57&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D57+F57,2)))</f>
         <v/>
       </c>
       <c r="H57" s="18" t="n"/>
@@ -3797,7 +3797,7 @@
         <v/>
       </c>
       <c r="E58" s="26">
-        <f>IF(OR(D58&lt;=0,C58&gt;Parametry!$C$6),0,IF(C58&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D58&lt;=0,C58&gt;Parametry!$C$6),0,IF(C58&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F58" s="25">
@@ -3805,7 +3805,7 @@
         <v/>
       </c>
       <c r="G58" s="25">
-        <f>IF(OR(D58&lt;=0,C58&gt;Parametry!$C$6),0,MIN(IF(C58&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D58+F58,2)))</f>
+        <f>IF(OR(D58&lt;=0,C58&gt;Parametry!$C$6),0,MIN(IF(C58&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D58+F58,2)))</f>
         <v/>
       </c>
       <c r="H58" s="18" t="n"/>
@@ -3846,7 +3846,7 @@
         <v/>
       </c>
       <c r="E59" s="17">
-        <f>IF(OR(D59&lt;=0,C59&gt;Parametry!$C$6),0,IF(C59&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D59&lt;=0,C59&gt;Parametry!$C$6),0,IF(C59&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F59" s="16">
@@ -3854,7 +3854,7 @@
         <v/>
       </c>
       <c r="G59" s="16">
-        <f>IF(OR(D59&lt;=0,C59&gt;Parametry!$C$6),0,MIN(IF(C59&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D59+F59,2)))</f>
+        <f>IF(OR(D59&lt;=0,C59&gt;Parametry!$C$6),0,MIN(IF(C59&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D59+F59,2)))</f>
         <v/>
       </c>
       <c r="H59" s="18" t="n"/>
@@ -3895,7 +3895,7 @@
         <v/>
       </c>
       <c r="E60" s="26">
-        <f>IF(OR(D60&lt;=0,C60&gt;Parametry!$C$6),0,IF(C60&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D60&lt;=0,C60&gt;Parametry!$C$6),0,IF(C60&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F60" s="25">
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="G60" s="25">
-        <f>IF(OR(D60&lt;=0,C60&gt;Parametry!$C$6),0,MIN(IF(C60&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D60+F60,2)))</f>
+        <f>IF(OR(D60&lt;=0,C60&gt;Parametry!$C$6),0,MIN(IF(C60&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D60+F60,2)))</f>
         <v/>
       </c>
       <c r="H60" s="18" t="n"/>
@@ -3944,7 +3944,7 @@
         <v/>
       </c>
       <c r="E61" s="17">
-        <f>IF(OR(D61&lt;=0,C61&gt;Parametry!$C$6),0,IF(C61&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D61&lt;=0,C61&gt;Parametry!$C$6),0,IF(C61&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F61" s="16">
@@ -3952,7 +3952,7 @@
         <v/>
       </c>
       <c r="G61" s="16">
-        <f>IF(OR(D61&lt;=0,C61&gt;Parametry!$C$6),0,MIN(IF(C61&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D61+F61,2)))</f>
+        <f>IF(OR(D61&lt;=0,C61&gt;Parametry!$C$6),0,MIN(IF(C61&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D61+F61,2)))</f>
         <v/>
       </c>
       <c r="H61" s="18" t="n"/>
@@ -3993,7 +3993,7 @@
         <v/>
       </c>
       <c r="E62" s="26">
-        <f>IF(OR(D62&lt;=0,C62&gt;Parametry!$C$6),0,IF(C62&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D62&lt;=0,C62&gt;Parametry!$C$6),0,IF(C62&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F62" s="25">
@@ -4001,7 +4001,7 @@
         <v/>
       </c>
       <c r="G62" s="25">
-        <f>IF(OR(D62&lt;=0,C62&gt;Parametry!$C$6),0,MIN(IF(C62&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D62+F62,2)))</f>
+        <f>IF(OR(D62&lt;=0,C62&gt;Parametry!$C$6),0,MIN(IF(C62&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D62+F62,2)))</f>
         <v/>
       </c>
       <c r="H62" s="18" t="n"/>
@@ -4042,7 +4042,7 @@
         <v/>
       </c>
       <c r="E63" s="17">
-        <f>IF(OR(D63&lt;=0,C63&gt;Parametry!$C$6),0,IF(C63&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D63&lt;=0,C63&gt;Parametry!$C$6),0,IF(C63&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F63" s="16">
@@ -4050,7 +4050,7 @@
         <v/>
       </c>
       <c r="G63" s="16">
-        <f>IF(OR(D63&lt;=0,C63&gt;Parametry!$C$6),0,MIN(IF(C63&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D63+F63,2)))</f>
+        <f>IF(OR(D63&lt;=0,C63&gt;Parametry!$C$6),0,MIN(IF(C63&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D63+F63,2)))</f>
         <v/>
       </c>
       <c r="H63" s="18" t="n"/>
@@ -4091,7 +4091,7 @@
         <v/>
       </c>
       <c r="E64" s="26">
-        <f>IF(OR(D64&lt;=0,C64&gt;Parametry!$C$6),0,IF(C64&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D64&lt;=0,C64&gt;Parametry!$C$6),0,IF(C64&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F64" s="25">
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="G64" s="25">
-        <f>IF(OR(D64&lt;=0,C64&gt;Parametry!$C$6),0,MIN(IF(C64&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D64+F64,2)))</f>
+        <f>IF(OR(D64&lt;=0,C64&gt;Parametry!$C$6),0,MIN(IF(C64&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D64+F64,2)))</f>
         <v/>
       </c>
       <c r="H64" s="18" t="n"/>
@@ -4140,7 +4140,7 @@
         <v/>
       </c>
       <c r="E65" s="17">
-        <f>IF(OR(D65&lt;=0,C65&gt;Parametry!$C$6),0,IF(C65&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D65&lt;=0,C65&gt;Parametry!$C$6),0,IF(C65&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F65" s="16">
@@ -4148,7 +4148,7 @@
         <v/>
       </c>
       <c r="G65" s="16">
-        <f>IF(OR(D65&lt;=0,C65&gt;Parametry!$C$6),0,MIN(IF(C65&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D65+F65,2)))</f>
+        <f>IF(OR(D65&lt;=0,C65&gt;Parametry!$C$6),0,MIN(IF(C65&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D65+F65,2)))</f>
         <v/>
       </c>
       <c r="H65" s="18" t="n"/>
@@ -4189,7 +4189,7 @@
         <v/>
       </c>
       <c r="E66" s="26">
-        <f>IF(OR(D66&lt;=0,C66&gt;Parametry!$C$6),0,IF(C66&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D66&lt;=0,C66&gt;Parametry!$C$6),0,IF(C66&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F66" s="25">
@@ -4197,7 +4197,7 @@
         <v/>
       </c>
       <c r="G66" s="25">
-        <f>IF(OR(D66&lt;=0,C66&gt;Parametry!$C$6),0,MIN(IF(C66&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D66+F66,2)))</f>
+        <f>IF(OR(D66&lt;=0,C66&gt;Parametry!$C$6),0,MIN(IF(C66&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D66+F66,2)))</f>
         <v/>
       </c>
       <c r="H66" s="18" t="n"/>
@@ -4238,7 +4238,7 @@
         <v/>
       </c>
       <c r="E67" s="17">
-        <f>IF(OR(D67&lt;=0,C67&gt;Parametry!$C$6),0,IF(C67&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D67&lt;=0,C67&gt;Parametry!$C$6),0,IF(C67&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F67" s="16">
@@ -4246,7 +4246,7 @@
         <v/>
       </c>
       <c r="G67" s="16">
-        <f>IF(OR(D67&lt;=0,C67&gt;Parametry!$C$6),0,MIN(IF(C67&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D67+F67,2)))</f>
+        <f>IF(OR(D67&lt;=0,C67&gt;Parametry!$C$6),0,MIN(IF(C67&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D67+F67,2)))</f>
         <v/>
       </c>
       <c r="H67" s="18" t="n"/>
@@ -4287,7 +4287,7 @@
         <v/>
       </c>
       <c r="E68" s="26">
-        <f>IF(OR(D68&lt;=0,C68&gt;Parametry!$C$6),0,IF(C68&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D68&lt;=0,C68&gt;Parametry!$C$6),0,IF(C68&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F68" s="25">
@@ -4295,7 +4295,7 @@
         <v/>
       </c>
       <c r="G68" s="25">
-        <f>IF(OR(D68&lt;=0,C68&gt;Parametry!$C$6),0,MIN(IF(C68&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D68+F68,2)))</f>
+        <f>IF(OR(D68&lt;=0,C68&gt;Parametry!$C$6),0,MIN(IF(C68&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D68+F68,2)))</f>
         <v/>
       </c>
       <c r="H68" s="18" t="n"/>
@@ -4336,7 +4336,7 @@
         <v/>
       </c>
       <c r="E69" s="17">
-        <f>IF(OR(D69&lt;=0,C69&gt;Parametry!$C$6),0,IF(C69&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D69&lt;=0,C69&gt;Parametry!$C$6),0,IF(C69&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F69" s="16">
@@ -4344,7 +4344,7 @@
         <v/>
       </c>
       <c r="G69" s="16">
-        <f>IF(OR(D69&lt;=0,C69&gt;Parametry!$C$6),0,MIN(IF(C69&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D69+F69,2)))</f>
+        <f>IF(OR(D69&lt;=0,C69&gt;Parametry!$C$6),0,MIN(IF(C69&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D69+F69,2)))</f>
         <v/>
       </c>
       <c r="H69" s="18" t="n"/>
@@ -4385,7 +4385,7 @@
         <v/>
       </c>
       <c r="E70" s="26">
-        <f>IF(OR(D70&lt;=0,C70&gt;Parametry!$C$6),0,IF(C70&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D70&lt;=0,C70&gt;Parametry!$C$6),0,IF(C70&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F70" s="25">
@@ -4393,7 +4393,7 @@
         <v/>
       </c>
       <c r="G70" s="25">
-        <f>IF(OR(D70&lt;=0,C70&gt;Parametry!$C$6),0,MIN(IF(C70&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D70+F70,2)))</f>
+        <f>IF(OR(D70&lt;=0,C70&gt;Parametry!$C$6),0,MIN(IF(C70&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D70+F70,2)))</f>
         <v/>
       </c>
       <c r="H70" s="18" t="n"/>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="E71" s="17">
-        <f>IF(OR(D71&lt;=0,C71&gt;Parametry!$C$6),0,IF(C71&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D71&lt;=0,C71&gt;Parametry!$C$6),0,IF(C71&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F71" s="16">
@@ -4442,7 +4442,7 @@
         <v/>
       </c>
       <c r="G71" s="16">
-        <f>IF(OR(D71&lt;=0,C71&gt;Parametry!$C$6),0,MIN(IF(C71&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D71+F71,2)))</f>
+        <f>IF(OR(D71&lt;=0,C71&gt;Parametry!$C$6),0,MIN(IF(C71&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D71+F71,2)))</f>
         <v/>
       </c>
       <c r="H71" s="18" t="n"/>
@@ -4483,7 +4483,7 @@
         <v/>
       </c>
       <c r="E72" s="26">
-        <f>IF(OR(D72&lt;=0,C72&gt;Parametry!$C$6),0,IF(C72&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D72&lt;=0,C72&gt;Parametry!$C$6),0,IF(C72&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F72" s="25">
@@ -4491,7 +4491,7 @@
         <v/>
       </c>
       <c r="G72" s="25">
-        <f>IF(OR(D72&lt;=0,C72&gt;Parametry!$C$6),0,MIN(IF(C72&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D72+F72,2)))</f>
+        <f>IF(OR(D72&lt;=0,C72&gt;Parametry!$C$6),0,MIN(IF(C72&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D72+F72,2)))</f>
         <v/>
       </c>
       <c r="H72" s="18" t="n"/>
@@ -4532,7 +4532,7 @@
         <v/>
       </c>
       <c r="E73" s="17">
-        <f>IF(OR(D73&lt;=0,C73&gt;Parametry!$C$6),0,IF(C73&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D73&lt;=0,C73&gt;Parametry!$C$6),0,IF(C73&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F73" s="16">
@@ -4540,7 +4540,7 @@
         <v/>
       </c>
       <c r="G73" s="16">
-        <f>IF(OR(D73&lt;=0,C73&gt;Parametry!$C$6),0,MIN(IF(C73&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D73+F73,2)))</f>
+        <f>IF(OR(D73&lt;=0,C73&gt;Parametry!$C$6),0,MIN(IF(C73&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D73+F73,2)))</f>
         <v/>
       </c>
       <c r="H73" s="18" t="n"/>
@@ -4581,7 +4581,7 @@
         <v/>
       </c>
       <c r="E74" s="26">
-        <f>IF(OR(D74&lt;=0,C74&gt;Parametry!$C$6),0,IF(C74&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D74&lt;=0,C74&gt;Parametry!$C$6),0,IF(C74&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F74" s="25">
@@ -4589,7 +4589,7 @@
         <v/>
       </c>
       <c r="G74" s="25">
-        <f>IF(OR(D74&lt;=0,C74&gt;Parametry!$C$6),0,MIN(IF(C74&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D74+F74,2)))</f>
+        <f>IF(OR(D74&lt;=0,C74&gt;Parametry!$C$6),0,MIN(IF(C74&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D74+F74,2)))</f>
         <v/>
       </c>
       <c r="H74" s="18" t="n"/>
@@ -4630,7 +4630,7 @@
         <v/>
       </c>
       <c r="E75" s="17">
-        <f>IF(OR(D75&lt;=0,C75&gt;Parametry!$C$6),0,IF(C75&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D75&lt;=0,C75&gt;Parametry!$C$6),0,IF(C75&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F75" s="16">
@@ -4638,7 +4638,7 @@
         <v/>
       </c>
       <c r="G75" s="16">
-        <f>IF(OR(D75&lt;=0,C75&gt;Parametry!$C$6),0,MIN(IF(C75&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D75+F75,2)))</f>
+        <f>IF(OR(D75&lt;=0,C75&gt;Parametry!$C$6),0,MIN(IF(C75&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D75+F75,2)))</f>
         <v/>
       </c>
       <c r="H75" s="18" t="n"/>
@@ -4679,7 +4679,7 @@
         <v/>
       </c>
       <c r="E76" s="26">
-        <f>IF(OR(D76&lt;=0,C76&gt;Parametry!$C$6),0,IF(C76&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D76&lt;=0,C76&gt;Parametry!$C$6),0,IF(C76&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F76" s="25">
@@ -4687,7 +4687,7 @@
         <v/>
       </c>
       <c r="G76" s="25">
-        <f>IF(OR(D76&lt;=0,C76&gt;Parametry!$C$6),0,MIN(IF(C76&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D76+F76,2)))</f>
+        <f>IF(OR(D76&lt;=0,C76&gt;Parametry!$C$6),0,MIN(IF(C76&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D76+F76,2)))</f>
         <v/>
       </c>
       <c r="H76" s="18" t="n"/>
@@ -4728,7 +4728,7 @@
         <v/>
       </c>
       <c r="E77" s="17">
-        <f>IF(OR(D77&lt;=0,C77&gt;Parametry!$C$6),0,IF(C77&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D77&lt;=0,C77&gt;Parametry!$C$6),0,IF(C77&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F77" s="16">
@@ -4736,7 +4736,7 @@
         <v/>
       </c>
       <c r="G77" s="16">
-        <f>IF(OR(D77&lt;=0,C77&gt;Parametry!$C$6),0,MIN(IF(C77&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D77+F77,2)))</f>
+        <f>IF(OR(D77&lt;=0,C77&gt;Parametry!$C$6),0,MIN(IF(C77&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D77+F77,2)))</f>
         <v/>
       </c>
       <c r="H77" s="18" t="n"/>
@@ -4777,7 +4777,7 @@
         <v/>
       </c>
       <c r="E78" s="26">
-        <f>IF(OR(D78&lt;=0,C78&gt;Parametry!$C$6),0,IF(C78&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D78&lt;=0,C78&gt;Parametry!$C$6),0,IF(C78&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F78" s="25">
@@ -4785,7 +4785,7 @@
         <v/>
       </c>
       <c r="G78" s="25">
-        <f>IF(OR(D78&lt;=0,C78&gt;Parametry!$C$6),0,MIN(IF(C78&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D78+F78,2)))</f>
+        <f>IF(OR(D78&lt;=0,C78&gt;Parametry!$C$6),0,MIN(IF(C78&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D78+F78,2)))</f>
         <v/>
       </c>
       <c r="H78" s="18" t="n"/>
@@ -4826,7 +4826,7 @@
         <v/>
       </c>
       <c r="E79" s="17">
-        <f>IF(OR(D79&lt;=0,C79&gt;Parametry!$C$6),0,IF(C79&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D79&lt;=0,C79&gt;Parametry!$C$6),0,IF(C79&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F79" s="16">
@@ -4834,7 +4834,7 @@
         <v/>
       </c>
       <c r="G79" s="16">
-        <f>IF(OR(D79&lt;=0,C79&gt;Parametry!$C$6),0,MIN(IF(C79&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D79+F79,2)))</f>
+        <f>IF(OR(D79&lt;=0,C79&gt;Parametry!$C$6),0,MIN(IF(C79&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D79+F79,2)))</f>
         <v/>
       </c>
       <c r="H79" s="18" t="n"/>
@@ -4875,7 +4875,7 @@
         <v/>
       </c>
       <c r="E80" s="26">
-        <f>IF(OR(D80&lt;=0,C80&gt;Parametry!$C$6),0,IF(C80&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D80&lt;=0,C80&gt;Parametry!$C$6),0,IF(C80&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F80" s="25">
@@ -4883,7 +4883,7 @@
         <v/>
       </c>
       <c r="G80" s="25">
-        <f>IF(OR(D80&lt;=0,C80&gt;Parametry!$C$6),0,MIN(IF(C80&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D80+F80,2)))</f>
+        <f>IF(OR(D80&lt;=0,C80&gt;Parametry!$C$6),0,MIN(IF(C80&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D80+F80,2)))</f>
         <v/>
       </c>
       <c r="H80" s="18" t="n"/>
@@ -4924,7 +4924,7 @@
         <v/>
       </c>
       <c r="E81" s="17">
-        <f>IF(OR(D81&lt;=0,C81&gt;Parametry!$C$6),0,IF(C81&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D81&lt;=0,C81&gt;Parametry!$C$6),0,IF(C81&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F81" s="16">
@@ -4932,7 +4932,7 @@
         <v/>
       </c>
       <c r="G81" s="16">
-        <f>IF(OR(D81&lt;=0,C81&gt;Parametry!$C$6),0,MIN(IF(C81&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D81+F81,2)))</f>
+        <f>IF(OR(D81&lt;=0,C81&gt;Parametry!$C$6),0,MIN(IF(C81&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D81+F81,2)))</f>
         <v/>
       </c>
       <c r="H81" s="18" t="n"/>
@@ -4973,7 +4973,7 @@
         <v/>
       </c>
       <c r="E82" s="26">
-        <f>IF(OR(D82&lt;=0,C82&gt;Parametry!$C$6),0,IF(C82&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D82&lt;=0,C82&gt;Parametry!$C$6),0,IF(C82&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F82" s="25">
@@ -4981,7 +4981,7 @@
         <v/>
       </c>
       <c r="G82" s="25">
-        <f>IF(OR(D82&lt;=0,C82&gt;Parametry!$C$6),0,MIN(IF(C82&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D82+F82,2)))</f>
+        <f>IF(OR(D82&lt;=0,C82&gt;Parametry!$C$6),0,MIN(IF(C82&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D82+F82,2)))</f>
         <v/>
       </c>
       <c r="H82" s="18" t="n"/>
@@ -5022,7 +5022,7 @@
         <v/>
       </c>
       <c r="E83" s="17">
-        <f>IF(OR(D83&lt;=0,C83&gt;Parametry!$C$6),0,IF(C83&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D83&lt;=0,C83&gt;Parametry!$C$6),0,IF(C83&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F83" s="16">
@@ -5030,7 +5030,7 @@
         <v/>
       </c>
       <c r="G83" s="16">
-        <f>IF(OR(D83&lt;=0,C83&gt;Parametry!$C$6),0,MIN(IF(C83&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D83+F83,2)))</f>
+        <f>IF(OR(D83&lt;=0,C83&gt;Parametry!$C$6),0,MIN(IF(C83&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D83+F83,2)))</f>
         <v/>
       </c>
       <c r="H83" s="18" t="n"/>
@@ -5071,7 +5071,7 @@
         <v/>
       </c>
       <c r="E84" s="26">
-        <f>IF(OR(D84&lt;=0,C84&gt;Parametry!$C$6),0,IF(C84&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D84&lt;=0,C84&gt;Parametry!$C$6),0,IF(C84&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F84" s="25">
@@ -5079,7 +5079,7 @@
         <v/>
       </c>
       <c r="G84" s="25">
-        <f>IF(OR(D84&lt;=0,C84&gt;Parametry!$C$6),0,MIN(IF(C84&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D84+F84,2)))</f>
+        <f>IF(OR(D84&lt;=0,C84&gt;Parametry!$C$6),0,MIN(IF(C84&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D84+F84,2)))</f>
         <v/>
       </c>
       <c r="H84" s="18" t="n"/>
@@ -5120,7 +5120,7 @@
         <v/>
       </c>
       <c r="E85" s="17">
-        <f>IF(OR(D85&lt;=0,C85&gt;Parametry!$C$6),0,IF(C85&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D85&lt;=0,C85&gt;Parametry!$C$6),0,IF(C85&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F85" s="16">
@@ -5128,7 +5128,7 @@
         <v/>
       </c>
       <c r="G85" s="16">
-        <f>IF(OR(D85&lt;=0,C85&gt;Parametry!$C$6),0,MIN(IF(C85&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D85+F85,2)))</f>
+        <f>IF(OR(D85&lt;=0,C85&gt;Parametry!$C$6),0,MIN(IF(C85&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D85+F85,2)))</f>
         <v/>
       </c>
       <c r="H85" s="18" t="n"/>
@@ -5169,7 +5169,7 @@
         <v/>
       </c>
       <c r="E86" s="26">
-        <f>IF(OR(D86&lt;=0,C86&gt;Parametry!$C$6),0,IF(C86&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D86&lt;=0,C86&gt;Parametry!$C$6),0,IF(C86&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F86" s="25">
@@ -5177,7 +5177,7 @@
         <v/>
       </c>
       <c r="G86" s="25">
-        <f>IF(OR(D86&lt;=0,C86&gt;Parametry!$C$6),0,MIN(IF(C86&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D86+F86,2)))</f>
+        <f>IF(OR(D86&lt;=0,C86&gt;Parametry!$C$6),0,MIN(IF(C86&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D86+F86,2)))</f>
         <v/>
       </c>
       <c r="H86" s="18" t="n"/>
@@ -5218,7 +5218,7 @@
         <v/>
       </c>
       <c r="E87" s="17">
-        <f>IF(OR(D87&lt;=0,C87&gt;Parametry!$C$6),0,IF(C87&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D87&lt;=0,C87&gt;Parametry!$C$6),0,IF(C87&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F87" s="16">
@@ -5226,7 +5226,7 @@
         <v/>
       </c>
       <c r="G87" s="16">
-        <f>IF(OR(D87&lt;=0,C87&gt;Parametry!$C$6),0,MIN(IF(C87&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D87+F87,2)))</f>
+        <f>IF(OR(D87&lt;=0,C87&gt;Parametry!$C$6),0,MIN(IF(C87&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D87+F87,2)))</f>
         <v/>
       </c>
       <c r="H87" s="18" t="n"/>
@@ -5267,7 +5267,7 @@
         <v/>
       </c>
       <c r="E88" s="26">
-        <f>IF(OR(D88&lt;=0,C88&gt;Parametry!$C$6),0,IF(C88&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D88&lt;=0,C88&gt;Parametry!$C$6),0,IF(C88&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F88" s="25">
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="G88" s="25">
-        <f>IF(OR(D88&lt;=0,C88&gt;Parametry!$C$6),0,MIN(IF(C88&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D88+F88,2)))</f>
+        <f>IF(OR(D88&lt;=0,C88&gt;Parametry!$C$6),0,MIN(IF(C88&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D88+F88,2)))</f>
         <v/>
       </c>
       <c r="H88" s="18" t="n"/>
@@ -5316,7 +5316,7 @@
         <v/>
       </c>
       <c r="E89" s="17">
-        <f>IF(OR(D89&lt;=0,C89&gt;Parametry!$C$6),0,IF(C89&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D89&lt;=0,C89&gt;Parametry!$C$6),0,IF(C89&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F89" s="16">
@@ -5324,7 +5324,7 @@
         <v/>
       </c>
       <c r="G89" s="16">
-        <f>IF(OR(D89&lt;=0,C89&gt;Parametry!$C$6),0,MIN(IF(C89&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D89+F89,2)))</f>
+        <f>IF(OR(D89&lt;=0,C89&gt;Parametry!$C$6),0,MIN(IF(C89&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D89+F89,2)))</f>
         <v/>
       </c>
       <c r="H89" s="18" t="n"/>
@@ -5365,7 +5365,7 @@
         <v/>
       </c>
       <c r="E90" s="26">
-        <f>IF(OR(D90&lt;=0,C90&gt;Parametry!$C$6),0,IF(C90&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D90&lt;=0,C90&gt;Parametry!$C$6),0,IF(C90&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F90" s="25">
@@ -5373,7 +5373,7 @@
         <v/>
       </c>
       <c r="G90" s="25">
-        <f>IF(OR(D90&lt;=0,C90&gt;Parametry!$C$6),0,MIN(IF(C90&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D90+F90,2)))</f>
+        <f>IF(OR(D90&lt;=0,C90&gt;Parametry!$C$6),0,MIN(IF(C90&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D90+F90,2)))</f>
         <v/>
       </c>
       <c r="H90" s="18" t="n"/>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="E91" s="17">
-        <f>IF(OR(D91&lt;=0,C91&gt;Parametry!$C$6),0,IF(C91&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D91&lt;=0,C91&gt;Parametry!$C$6),0,IF(C91&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F91" s="16">
@@ -5422,7 +5422,7 @@
         <v/>
       </c>
       <c r="G91" s="16">
-        <f>IF(OR(D91&lt;=0,C91&gt;Parametry!$C$6),0,MIN(IF(C91&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D91+F91,2)))</f>
+        <f>IF(OR(D91&lt;=0,C91&gt;Parametry!$C$6),0,MIN(IF(C91&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D91+F91,2)))</f>
         <v/>
       </c>
       <c r="H91" s="18" t="n"/>
@@ -5463,7 +5463,7 @@
         <v/>
       </c>
       <c r="E92" s="26">
-        <f>IF(OR(D92&lt;=0,C92&gt;Parametry!$C$6),0,IF(C92&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D92&lt;=0,C92&gt;Parametry!$C$6),0,IF(C92&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F92" s="25">
@@ -5471,7 +5471,7 @@
         <v/>
       </c>
       <c r="G92" s="25">
-        <f>IF(OR(D92&lt;=0,C92&gt;Parametry!$C$6),0,MIN(IF(C92&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D92+F92,2)))</f>
+        <f>IF(OR(D92&lt;=0,C92&gt;Parametry!$C$6),0,MIN(IF(C92&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D92+F92,2)))</f>
         <v/>
       </c>
       <c r="H92" s="18" t="n"/>
@@ -5512,7 +5512,7 @@
         <v/>
       </c>
       <c r="E93" s="17">
-        <f>IF(OR(D93&lt;=0,C93&gt;Parametry!$C$6),0,IF(C93&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D93&lt;=0,C93&gt;Parametry!$C$6),0,IF(C93&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F93" s="16">
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="G93" s="16">
-        <f>IF(OR(D93&lt;=0,C93&gt;Parametry!$C$6),0,MIN(IF(C93&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D93+F93,2)))</f>
+        <f>IF(OR(D93&lt;=0,C93&gt;Parametry!$C$6),0,MIN(IF(C93&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D93+F93,2)))</f>
         <v/>
       </c>
       <c r="H93" s="18" t="n"/>
@@ -5561,7 +5561,7 @@
         <v/>
       </c>
       <c r="E94" s="26">
-        <f>IF(OR(D94&lt;=0,C94&gt;Parametry!$C$6),0,IF(C94&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D94&lt;=0,C94&gt;Parametry!$C$6),0,IF(C94&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F94" s="25">
@@ -5569,7 +5569,7 @@
         <v/>
       </c>
       <c r="G94" s="25">
-        <f>IF(OR(D94&lt;=0,C94&gt;Parametry!$C$6),0,MIN(IF(C94&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D94+F94,2)))</f>
+        <f>IF(OR(D94&lt;=0,C94&gt;Parametry!$C$6),0,MIN(IF(C94&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D94+F94,2)))</f>
         <v/>
       </c>
       <c r="H94" s="18" t="n"/>
@@ -5610,7 +5610,7 @@
         <v/>
       </c>
       <c r="E95" s="17">
-        <f>IF(OR(D95&lt;=0,C95&gt;Parametry!$C$6),0,IF(C95&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D95&lt;=0,C95&gt;Parametry!$C$6),0,IF(C95&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F95" s="16">
@@ -5618,7 +5618,7 @@
         <v/>
       </c>
       <c r="G95" s="16">
-        <f>IF(OR(D95&lt;=0,C95&gt;Parametry!$C$6),0,MIN(IF(C95&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D95+F95,2)))</f>
+        <f>IF(OR(D95&lt;=0,C95&gt;Parametry!$C$6),0,MIN(IF(C95&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D95+F95,2)))</f>
         <v/>
       </c>
       <c r="H95" s="18" t="n"/>
@@ -5659,7 +5659,7 @@
         <v/>
       </c>
       <c r="E96" s="26">
-        <f>IF(OR(D96&lt;=0,C96&gt;Parametry!$C$6),0,IF(C96&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D96&lt;=0,C96&gt;Parametry!$C$6),0,IF(C96&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F96" s="25">
@@ -5667,7 +5667,7 @@
         <v/>
       </c>
       <c r="G96" s="25">
-        <f>IF(OR(D96&lt;=0,C96&gt;Parametry!$C$6),0,MIN(IF(C96&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D96+F96,2)))</f>
+        <f>IF(OR(D96&lt;=0,C96&gt;Parametry!$C$6),0,MIN(IF(C96&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D96+F96,2)))</f>
         <v/>
       </c>
       <c r="H96" s="18" t="n"/>
@@ -5708,7 +5708,7 @@
         <v/>
       </c>
       <c r="E97" s="17">
-        <f>IF(OR(D97&lt;=0,C97&gt;Parametry!$C$6),0,IF(C97&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D97&lt;=0,C97&gt;Parametry!$C$6),0,IF(C97&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F97" s="16">
@@ -5716,7 +5716,7 @@
         <v/>
       </c>
       <c r="G97" s="16">
-        <f>IF(OR(D97&lt;=0,C97&gt;Parametry!$C$6),0,MIN(IF(C97&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D97+F97,2)))</f>
+        <f>IF(OR(D97&lt;=0,C97&gt;Parametry!$C$6),0,MIN(IF(C97&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D97+F97,2)))</f>
         <v/>
       </c>
       <c r="H97" s="18" t="n"/>
@@ -5757,7 +5757,7 @@
         <v/>
       </c>
       <c r="E98" s="26">
-        <f>IF(OR(D98&lt;=0,C98&gt;Parametry!$C$6),0,IF(C98&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D98&lt;=0,C98&gt;Parametry!$C$6),0,IF(C98&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F98" s="25">
@@ -5765,7 +5765,7 @@
         <v/>
       </c>
       <c r="G98" s="25">
-        <f>IF(OR(D98&lt;=0,C98&gt;Parametry!$C$6),0,MIN(IF(C98&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D98+F98,2)))</f>
+        <f>IF(OR(D98&lt;=0,C98&gt;Parametry!$C$6),0,MIN(IF(C98&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D98+F98,2)))</f>
         <v/>
       </c>
       <c r="H98" s="18" t="n"/>
@@ -5806,7 +5806,7 @@
         <v/>
       </c>
       <c r="E99" s="17">
-        <f>IF(OR(D99&lt;=0,C99&gt;Parametry!$C$6),0,IF(C99&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D99&lt;=0,C99&gt;Parametry!$C$6),0,IF(C99&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F99" s="16">
@@ -5814,7 +5814,7 @@
         <v/>
       </c>
       <c r="G99" s="16">
-        <f>IF(OR(D99&lt;=0,C99&gt;Parametry!$C$6),0,MIN(IF(C99&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D99+F99,2)))</f>
+        <f>IF(OR(D99&lt;=0,C99&gt;Parametry!$C$6),0,MIN(IF(C99&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D99+F99,2)))</f>
         <v/>
       </c>
       <c r="H99" s="18" t="n"/>
@@ -5855,7 +5855,7 @@
         <v/>
       </c>
       <c r="E100" s="26">
-        <f>IF(OR(D100&lt;=0,C100&gt;Parametry!$C$6),0,IF(C100&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D100&lt;=0,C100&gt;Parametry!$C$6),0,IF(C100&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F100" s="25">
@@ -5863,7 +5863,7 @@
         <v/>
       </c>
       <c r="G100" s="25">
-        <f>IF(OR(D100&lt;=0,C100&gt;Parametry!$C$6),0,MIN(IF(C100&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D100+F100,2)))</f>
+        <f>IF(OR(D100&lt;=0,C100&gt;Parametry!$C$6),0,MIN(IF(C100&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D100+F100,2)))</f>
         <v/>
       </c>
       <c r="H100" s="18" t="n"/>
@@ -5904,7 +5904,7 @@
         <v/>
       </c>
       <c r="E101" s="17">
-        <f>IF(OR(D101&lt;=0,C101&gt;Parametry!$C$6),0,IF(C101&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D101&lt;=0,C101&gt;Parametry!$C$6),0,IF(C101&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F101" s="16">
@@ -5912,7 +5912,7 @@
         <v/>
       </c>
       <c r="G101" s="16">
-        <f>IF(OR(D101&lt;=0,C101&gt;Parametry!$C$6),0,MIN(IF(C101&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D101+F101,2)))</f>
+        <f>IF(OR(D101&lt;=0,C101&gt;Parametry!$C$6),0,MIN(IF(C101&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D101+F101,2)))</f>
         <v/>
       </c>
       <c r="H101" s="18" t="n"/>
@@ -5953,7 +5953,7 @@
         <v/>
       </c>
       <c r="E102" s="26">
-        <f>IF(OR(D102&lt;=0,C102&gt;Parametry!$C$6),0,IF(C102&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D102&lt;=0,C102&gt;Parametry!$C$6),0,IF(C102&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F102" s="25">
@@ -5961,7 +5961,7 @@
         <v/>
       </c>
       <c r="G102" s="25">
-        <f>IF(OR(D102&lt;=0,C102&gt;Parametry!$C$6),0,MIN(IF(C102&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D102+F102,2)))</f>
+        <f>IF(OR(D102&lt;=0,C102&gt;Parametry!$C$6),0,MIN(IF(C102&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D102+F102,2)))</f>
         <v/>
       </c>
       <c r="H102" s="18" t="n"/>
@@ -6002,7 +6002,7 @@
         <v/>
       </c>
       <c r="E103" s="17">
-        <f>IF(OR(D103&lt;=0,C103&gt;Parametry!$C$6),0,IF(C103&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D103&lt;=0,C103&gt;Parametry!$C$6),0,IF(C103&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F103" s="16">
@@ -6010,7 +6010,7 @@
         <v/>
       </c>
       <c r="G103" s="16">
-        <f>IF(OR(D103&lt;=0,C103&gt;Parametry!$C$6),0,MIN(IF(C103&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D103+F103,2)))</f>
+        <f>IF(OR(D103&lt;=0,C103&gt;Parametry!$C$6),0,MIN(IF(C103&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D103+F103,2)))</f>
         <v/>
       </c>
       <c r="H103" s="18" t="n"/>
@@ -6051,7 +6051,7 @@
         <v/>
       </c>
       <c r="E104" s="26">
-        <f>IF(OR(D104&lt;=0,C104&gt;Parametry!$C$6),0,IF(C104&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D104&lt;=0,C104&gt;Parametry!$C$6),0,IF(C104&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F104" s="25">
@@ -6059,7 +6059,7 @@
         <v/>
       </c>
       <c r="G104" s="25">
-        <f>IF(OR(D104&lt;=0,C104&gt;Parametry!$C$6),0,MIN(IF(C104&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D104+F104,2)))</f>
+        <f>IF(OR(D104&lt;=0,C104&gt;Parametry!$C$6),0,MIN(IF(C104&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D104+F104,2)))</f>
         <v/>
       </c>
       <c r="H104" s="18" t="n"/>
@@ -6100,7 +6100,7 @@
         <v/>
       </c>
       <c r="E105" s="17">
-        <f>IF(OR(D105&lt;=0,C105&gt;Parametry!$C$6),0,IF(C105&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D105&lt;=0,C105&gt;Parametry!$C$6),0,IF(C105&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F105" s="16">
@@ -6108,7 +6108,7 @@
         <v/>
       </c>
       <c r="G105" s="16">
-        <f>IF(OR(D105&lt;=0,C105&gt;Parametry!$C$6),0,MIN(IF(C105&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D105+F105,2)))</f>
+        <f>IF(OR(D105&lt;=0,C105&gt;Parametry!$C$6),0,MIN(IF(C105&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D105+F105,2)))</f>
         <v/>
       </c>
       <c r="H105" s="18" t="n"/>
@@ -6149,7 +6149,7 @@
         <v/>
       </c>
       <c r="E106" s="26">
-        <f>IF(OR(D106&lt;=0,C106&gt;Parametry!$C$6),0,IF(C106&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D106&lt;=0,C106&gt;Parametry!$C$6),0,IF(C106&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F106" s="25">
@@ -6157,7 +6157,7 @@
         <v/>
       </c>
       <c r="G106" s="25">
-        <f>IF(OR(D106&lt;=0,C106&gt;Parametry!$C$6),0,MIN(IF(C106&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D106+F106,2)))</f>
+        <f>IF(OR(D106&lt;=0,C106&gt;Parametry!$C$6),0,MIN(IF(C106&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D106+F106,2)))</f>
         <v/>
       </c>
       <c r="H106" s="18" t="n"/>
@@ -6198,7 +6198,7 @@
         <v/>
       </c>
       <c r="E107" s="17">
-        <f>IF(OR(D107&lt;=0,C107&gt;Parametry!$C$6),0,IF(C107&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D107&lt;=0,C107&gt;Parametry!$C$6),0,IF(C107&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F107" s="16">
@@ -6206,7 +6206,7 @@
         <v/>
       </c>
       <c r="G107" s="16">
-        <f>IF(OR(D107&lt;=0,C107&gt;Parametry!$C$6),0,MIN(IF(C107&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D107+F107,2)))</f>
+        <f>IF(OR(D107&lt;=0,C107&gt;Parametry!$C$6),0,MIN(IF(C107&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D107+F107,2)))</f>
         <v/>
       </c>
       <c r="H107" s="18" t="n"/>
@@ -6247,7 +6247,7 @@
         <v/>
       </c>
       <c r="E108" s="26">
-        <f>IF(OR(D108&lt;=0,C108&gt;Parametry!$C$6),0,IF(C108&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D108&lt;=0,C108&gt;Parametry!$C$6),0,IF(C108&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F108" s="25">
@@ -6255,7 +6255,7 @@
         <v/>
       </c>
       <c r="G108" s="25">
-        <f>IF(OR(D108&lt;=0,C108&gt;Parametry!$C$6),0,MIN(IF(C108&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D108+F108,2)))</f>
+        <f>IF(OR(D108&lt;=0,C108&gt;Parametry!$C$6),0,MIN(IF(C108&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D108+F108,2)))</f>
         <v/>
       </c>
       <c r="H108" s="18" t="n"/>
@@ -6296,7 +6296,7 @@
         <v/>
       </c>
       <c r="E109" s="17">
-        <f>IF(OR(D109&lt;=0,C109&gt;Parametry!$C$6),0,IF(C109&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D109&lt;=0,C109&gt;Parametry!$C$6),0,IF(C109&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F109" s="16">
@@ -6304,7 +6304,7 @@
         <v/>
       </c>
       <c r="G109" s="16">
-        <f>IF(OR(D109&lt;=0,C109&gt;Parametry!$C$6),0,MIN(IF(C109&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D109+F109,2)))</f>
+        <f>IF(OR(D109&lt;=0,C109&gt;Parametry!$C$6),0,MIN(IF(C109&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D109+F109,2)))</f>
         <v/>
       </c>
       <c r="H109" s="18" t="n"/>
@@ -6345,7 +6345,7 @@
         <v/>
       </c>
       <c r="E110" s="26">
-        <f>IF(OR(D110&lt;=0,C110&gt;Parametry!$C$6),0,IF(C110&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D110&lt;=0,C110&gt;Parametry!$C$6),0,IF(C110&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F110" s="25">
@@ -6353,7 +6353,7 @@
         <v/>
       </c>
       <c r="G110" s="25">
-        <f>IF(OR(D110&lt;=0,C110&gt;Parametry!$C$6),0,MIN(IF(C110&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D110+F110,2)))</f>
+        <f>IF(OR(D110&lt;=0,C110&gt;Parametry!$C$6),0,MIN(IF(C110&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D110+F110,2)))</f>
         <v/>
       </c>
       <c r="H110" s="18" t="n"/>
@@ -6394,7 +6394,7 @@
         <v/>
       </c>
       <c r="E111" s="17">
-        <f>IF(OR(D111&lt;=0,C111&gt;Parametry!$C$6),0,IF(C111&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D111&lt;=0,C111&gt;Parametry!$C$6),0,IF(C111&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F111" s="16">
@@ -6402,7 +6402,7 @@
         <v/>
       </c>
       <c r="G111" s="16">
-        <f>IF(OR(D111&lt;=0,C111&gt;Parametry!$C$6),0,MIN(IF(C111&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D111+F111,2)))</f>
+        <f>IF(OR(D111&lt;=0,C111&gt;Parametry!$C$6),0,MIN(IF(C111&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D111+F111,2)))</f>
         <v/>
       </c>
       <c r="H111" s="18" t="n"/>
@@ -6443,7 +6443,7 @@
         <v/>
       </c>
       <c r="E112" s="26">
-        <f>IF(OR(D112&lt;=0,C112&gt;Parametry!$C$6),0,IF(C112&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D112&lt;=0,C112&gt;Parametry!$C$6),0,IF(C112&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F112" s="25">
@@ -6451,7 +6451,7 @@
         <v/>
       </c>
       <c r="G112" s="25">
-        <f>IF(OR(D112&lt;=0,C112&gt;Parametry!$C$6),0,MIN(IF(C112&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D112+F112,2)))</f>
+        <f>IF(OR(D112&lt;=0,C112&gt;Parametry!$C$6),0,MIN(IF(C112&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D112+F112,2)))</f>
         <v/>
       </c>
       <c r="H112" s="18" t="n"/>
@@ -6492,7 +6492,7 @@
         <v/>
       </c>
       <c r="E113" s="17">
-        <f>IF(OR(D113&lt;=0,C113&gt;Parametry!$C$6),0,IF(C113&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D113&lt;=0,C113&gt;Parametry!$C$6),0,IF(C113&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F113" s="16">
@@ -6500,7 +6500,7 @@
         <v/>
       </c>
       <c r="G113" s="16">
-        <f>IF(OR(D113&lt;=0,C113&gt;Parametry!$C$6),0,MIN(IF(C113&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D113+F113,2)))</f>
+        <f>IF(OR(D113&lt;=0,C113&gt;Parametry!$C$6),0,MIN(IF(C113&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D113+F113,2)))</f>
         <v/>
       </c>
       <c r="H113" s="18" t="n"/>
@@ -6541,7 +6541,7 @@
         <v/>
       </c>
       <c r="E114" s="26">
-        <f>IF(OR(D114&lt;=0,C114&gt;Parametry!$C$6),0,IF(C114&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D114&lt;=0,C114&gt;Parametry!$C$6),0,IF(C114&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F114" s="25">
@@ -6549,7 +6549,7 @@
         <v/>
       </c>
       <c r="G114" s="25">
-        <f>IF(OR(D114&lt;=0,C114&gt;Parametry!$C$6),0,MIN(IF(C114&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D114+F114,2)))</f>
+        <f>IF(OR(D114&lt;=0,C114&gt;Parametry!$C$6),0,MIN(IF(C114&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D114+F114,2)))</f>
         <v/>
       </c>
       <c r="H114" s="18" t="n"/>
@@ -6590,7 +6590,7 @@
         <v/>
       </c>
       <c r="E115" s="17">
-        <f>IF(OR(D115&lt;=0,C115&gt;Parametry!$C$6),0,IF(C115&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D115&lt;=0,C115&gt;Parametry!$C$6),0,IF(C115&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F115" s="16">
@@ -6598,7 +6598,7 @@
         <v/>
       </c>
       <c r="G115" s="16">
-        <f>IF(OR(D115&lt;=0,C115&gt;Parametry!$C$6),0,MIN(IF(C115&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D115+F115,2)))</f>
+        <f>IF(OR(D115&lt;=0,C115&gt;Parametry!$C$6),0,MIN(IF(C115&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D115+F115,2)))</f>
         <v/>
       </c>
       <c r="H115" s="18" t="n"/>
@@ -6639,7 +6639,7 @@
         <v/>
       </c>
       <c r="E116" s="26">
-        <f>IF(OR(D116&lt;=0,C116&gt;Parametry!$C$6),0,IF(C116&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D116&lt;=0,C116&gt;Parametry!$C$6),0,IF(C116&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F116" s="25">
@@ -6647,7 +6647,7 @@
         <v/>
       </c>
       <c r="G116" s="25">
-        <f>IF(OR(D116&lt;=0,C116&gt;Parametry!$C$6),0,MIN(IF(C116&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D116+F116,2)))</f>
+        <f>IF(OR(D116&lt;=0,C116&gt;Parametry!$C$6),0,MIN(IF(C116&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D116+F116,2)))</f>
         <v/>
       </c>
       <c r="H116" s="18" t="n"/>
@@ -6688,7 +6688,7 @@
         <v/>
       </c>
       <c r="E117" s="17">
-        <f>IF(OR(D117&lt;=0,C117&gt;Parametry!$C$6),0,IF(C117&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D117&lt;=0,C117&gt;Parametry!$C$6),0,IF(C117&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F117" s="16">
@@ -6696,7 +6696,7 @@
         <v/>
       </c>
       <c r="G117" s="16">
-        <f>IF(OR(D117&lt;=0,C117&gt;Parametry!$C$6),0,MIN(IF(C117&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D117+F117,2)))</f>
+        <f>IF(OR(D117&lt;=0,C117&gt;Parametry!$C$6),0,MIN(IF(C117&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D117+F117,2)))</f>
         <v/>
       </c>
       <c r="H117" s="18" t="n"/>
@@ -6737,7 +6737,7 @@
         <v/>
       </c>
       <c r="E118" s="26">
-        <f>IF(OR(D118&lt;=0,C118&gt;Parametry!$C$6),0,IF(C118&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D118&lt;=0,C118&gt;Parametry!$C$6),0,IF(C118&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F118" s="25">
@@ -6745,7 +6745,7 @@
         <v/>
       </c>
       <c r="G118" s="25">
-        <f>IF(OR(D118&lt;=0,C118&gt;Parametry!$C$6),0,MIN(IF(C118&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D118+F118,2)))</f>
+        <f>IF(OR(D118&lt;=0,C118&gt;Parametry!$C$6),0,MIN(IF(C118&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D118+F118,2)))</f>
         <v/>
       </c>
       <c r="H118" s="18" t="n"/>
@@ -6786,7 +6786,7 @@
         <v/>
       </c>
       <c r="E119" s="17">
-        <f>IF(OR(D119&lt;=0,C119&gt;Parametry!$C$6),0,IF(C119&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D119&lt;=0,C119&gt;Parametry!$C$6),0,IF(C119&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F119" s="16">
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="G119" s="16">
-        <f>IF(OR(D119&lt;=0,C119&gt;Parametry!$C$6),0,MIN(IF(C119&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D119+F119,2)))</f>
+        <f>IF(OR(D119&lt;=0,C119&gt;Parametry!$C$6),0,MIN(IF(C119&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D119+F119,2)))</f>
         <v/>
       </c>
       <c r="H119" s="18" t="n"/>
@@ -6835,7 +6835,7 @@
         <v/>
       </c>
       <c r="E120" s="26">
-        <f>IF(OR(D120&lt;=0,C120&gt;Parametry!$C$6),0,IF(C120&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D120&lt;=0,C120&gt;Parametry!$C$6),0,IF(C120&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F120" s="25">
@@ -6843,7 +6843,7 @@
         <v/>
       </c>
       <c r="G120" s="25">
-        <f>IF(OR(D120&lt;=0,C120&gt;Parametry!$C$6),0,MIN(IF(C120&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D120+F120,2)))</f>
+        <f>IF(OR(D120&lt;=0,C120&gt;Parametry!$C$6),0,MIN(IF(C120&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D120+F120,2)))</f>
         <v/>
       </c>
       <c r="H120" s="18" t="n"/>
@@ -6884,7 +6884,7 @@
         <v/>
       </c>
       <c r="E121" s="17">
-        <f>IF(OR(D121&lt;=0,C121&gt;Parametry!$C$6),0,IF(C121&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D121&lt;=0,C121&gt;Parametry!$C$6),0,IF(C121&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F121" s="16">
@@ -6892,7 +6892,7 @@
         <v/>
       </c>
       <c r="G121" s="16">
-        <f>IF(OR(D121&lt;=0,C121&gt;Parametry!$C$6),0,MIN(IF(C121&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D121+F121,2)))</f>
+        <f>IF(OR(D121&lt;=0,C121&gt;Parametry!$C$6),0,MIN(IF(C121&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D121+F121,2)))</f>
         <v/>
       </c>
       <c r="H121" s="18" t="n"/>
@@ -6933,7 +6933,7 @@
         <v/>
       </c>
       <c r="E122" s="26">
-        <f>IF(OR(D122&lt;=0,C122&gt;Parametry!$C$6),0,IF(C122&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D122&lt;=0,C122&gt;Parametry!$C$6),0,IF(C122&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F122" s="25">
@@ -6941,7 +6941,7 @@
         <v/>
       </c>
       <c r="G122" s="25">
-        <f>IF(OR(D122&lt;=0,C122&gt;Parametry!$C$6),0,MIN(IF(C122&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D122+F122,2)))</f>
+        <f>IF(OR(D122&lt;=0,C122&gt;Parametry!$C$6),0,MIN(IF(C122&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D122+F122,2)))</f>
         <v/>
       </c>
       <c r="H122" s="18" t="n"/>
@@ -6982,7 +6982,7 @@
         <v/>
       </c>
       <c r="E123" s="17">
-        <f>IF(OR(D123&lt;=0,C123&gt;Parametry!$C$6),0,IF(C123&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D123&lt;=0,C123&gt;Parametry!$C$6),0,IF(C123&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F123" s="16">
@@ -6990,7 +6990,7 @@
         <v/>
       </c>
       <c r="G123" s="16">
-        <f>IF(OR(D123&lt;=0,C123&gt;Parametry!$C$6),0,MIN(IF(C123&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D123+F123,2)))</f>
+        <f>IF(OR(D123&lt;=0,C123&gt;Parametry!$C$6),0,MIN(IF(C123&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D123+F123,2)))</f>
         <v/>
       </c>
       <c r="H123" s="18" t="n"/>
@@ -7031,7 +7031,7 @@
         <v/>
       </c>
       <c r="E124" s="26">
-        <f>IF(OR(D124&lt;=0,C124&gt;Parametry!$C$6),0,IF(C124&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D124&lt;=0,C124&gt;Parametry!$C$6),0,IF(C124&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F124" s="25">
@@ -7039,7 +7039,7 @@
         <v/>
       </c>
       <c r="G124" s="25">
-        <f>IF(OR(D124&lt;=0,C124&gt;Parametry!$C$6),0,MIN(IF(C124&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D124+F124,2)))</f>
+        <f>IF(OR(D124&lt;=0,C124&gt;Parametry!$C$6),0,MIN(IF(C124&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D124+F124,2)))</f>
         <v/>
       </c>
       <c r="H124" s="18" t="n"/>
@@ -7080,7 +7080,7 @@
         <v/>
       </c>
       <c r="E125" s="17">
-        <f>IF(OR(D125&lt;=0,C125&gt;Parametry!$C$6),0,IF(C125&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D125&lt;=0,C125&gt;Parametry!$C$6),0,IF(C125&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F125" s="16">
@@ -7088,7 +7088,7 @@
         <v/>
       </c>
       <c r="G125" s="16">
-        <f>IF(OR(D125&lt;=0,C125&gt;Parametry!$C$6),0,MIN(IF(C125&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D125+F125,2)))</f>
+        <f>IF(OR(D125&lt;=0,C125&gt;Parametry!$C$6),0,MIN(IF(C125&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D125+F125,2)))</f>
         <v/>
       </c>
       <c r="H125" s="18" t="n"/>
@@ -7129,7 +7129,7 @@
         <v/>
       </c>
       <c r="E126" s="26">
-        <f>IF(OR(D126&lt;=0,C126&gt;Parametry!$C$6),0,IF(C126&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D126&lt;=0,C126&gt;Parametry!$C$6),0,IF(C126&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F126" s="25">
@@ -7137,7 +7137,7 @@
         <v/>
       </c>
       <c r="G126" s="25">
-        <f>IF(OR(D126&lt;=0,C126&gt;Parametry!$C$6),0,MIN(IF(C126&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D126+F126,2)))</f>
+        <f>IF(OR(D126&lt;=0,C126&gt;Parametry!$C$6),0,MIN(IF(C126&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D126+F126,2)))</f>
         <v/>
       </c>
       <c r="H126" s="18" t="n"/>
@@ -7178,7 +7178,7 @@
         <v/>
       </c>
       <c r="E127" s="17">
-        <f>IF(OR(D127&lt;=0,C127&gt;Parametry!$C$6),0,IF(C127&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D127&lt;=0,C127&gt;Parametry!$C$6),0,IF(C127&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F127" s="16">
@@ -7186,7 +7186,7 @@
         <v/>
       </c>
       <c r="G127" s="16">
-        <f>IF(OR(D127&lt;=0,C127&gt;Parametry!$C$6),0,MIN(IF(C127&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D127+F127,2)))</f>
+        <f>IF(OR(D127&lt;=0,C127&gt;Parametry!$C$6),0,MIN(IF(C127&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D127+F127,2)))</f>
         <v/>
       </c>
       <c r="H127" s="18" t="n"/>
@@ -7227,7 +7227,7 @@
         <v/>
       </c>
       <c r="E128" s="26">
-        <f>IF(OR(D128&lt;=0,C128&gt;Parametry!$C$6),0,IF(C128&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D128&lt;=0,C128&gt;Parametry!$C$6),0,IF(C128&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F128" s="25">
@@ -7235,7 +7235,7 @@
         <v/>
       </c>
       <c r="G128" s="25">
-        <f>IF(OR(D128&lt;=0,C128&gt;Parametry!$C$6),0,MIN(IF(C128&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D128+F128,2)))</f>
+        <f>IF(OR(D128&lt;=0,C128&gt;Parametry!$C$6),0,MIN(IF(C128&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D128+F128,2)))</f>
         <v/>
       </c>
       <c r="H128" s="18" t="n"/>
@@ -7276,7 +7276,7 @@
         <v/>
       </c>
       <c r="E129" s="17">
-        <f>IF(OR(D129&lt;=0,C129&gt;Parametry!$C$6),0,IF(C129&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D129&lt;=0,C129&gt;Parametry!$C$6),0,IF(C129&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F129" s="16">
@@ -7284,7 +7284,7 @@
         <v/>
       </c>
       <c r="G129" s="16">
-        <f>IF(OR(D129&lt;=0,C129&gt;Parametry!$C$6),0,MIN(IF(C129&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D129+F129,2)))</f>
+        <f>IF(OR(D129&lt;=0,C129&gt;Parametry!$C$6),0,MIN(IF(C129&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D129+F129,2)))</f>
         <v/>
       </c>
       <c r="H129" s="18" t="n"/>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="E130" s="26">
-        <f>IF(OR(D130&lt;=0,C130&gt;Parametry!$C$6),0,IF(C130&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D130&lt;=0,C130&gt;Parametry!$C$6),0,IF(C130&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F130" s="25">
@@ -7333,7 +7333,7 @@
         <v/>
       </c>
       <c r="G130" s="25">
-        <f>IF(OR(D130&lt;=0,C130&gt;Parametry!$C$6),0,MIN(IF(C130&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D130+F130,2)))</f>
+        <f>IF(OR(D130&lt;=0,C130&gt;Parametry!$C$6),0,MIN(IF(C130&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D130+F130,2)))</f>
         <v/>
       </c>
       <c r="H130" s="18" t="n"/>
@@ -7374,7 +7374,7 @@
         <v/>
       </c>
       <c r="E131" s="17">
-        <f>IF(OR(D131&lt;=0,C131&gt;Parametry!$C$6),0,IF(C131&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D131&lt;=0,C131&gt;Parametry!$C$6),0,IF(C131&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F131" s="16">
@@ -7382,7 +7382,7 @@
         <v/>
       </c>
       <c r="G131" s="16">
-        <f>IF(OR(D131&lt;=0,C131&gt;Parametry!$C$6),0,MIN(IF(C131&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D131+F131,2)))</f>
+        <f>IF(OR(D131&lt;=0,C131&gt;Parametry!$C$6),0,MIN(IF(C131&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D131+F131,2)))</f>
         <v/>
       </c>
       <c r="H131" s="18" t="n"/>
@@ -7423,7 +7423,7 @@
         <v/>
       </c>
       <c r="E132" s="26">
-        <f>IF(OR(D132&lt;=0,C132&gt;Parametry!$C$6),0,IF(C132&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D132&lt;=0,C132&gt;Parametry!$C$6),0,IF(C132&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F132" s="25">
@@ -7431,7 +7431,7 @@
         <v/>
       </c>
       <c r="G132" s="25">
-        <f>IF(OR(D132&lt;=0,C132&gt;Parametry!$C$6),0,MIN(IF(C132&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D132+F132,2)))</f>
+        <f>IF(OR(D132&lt;=0,C132&gt;Parametry!$C$6),0,MIN(IF(C132&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D132+F132,2)))</f>
         <v/>
       </c>
       <c r="H132" s="18" t="n"/>
@@ -7472,7 +7472,7 @@
         <v/>
       </c>
       <c r="E133" s="17">
-        <f>IF(OR(D133&lt;=0,C133&gt;Parametry!$C$6),0,IF(C133&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D133&lt;=0,C133&gt;Parametry!$C$6),0,IF(C133&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F133" s="16">
@@ -7480,7 +7480,7 @@
         <v/>
       </c>
       <c r="G133" s="16">
-        <f>IF(OR(D133&lt;=0,C133&gt;Parametry!$C$6),0,MIN(IF(C133&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D133+F133,2)))</f>
+        <f>IF(OR(D133&lt;=0,C133&gt;Parametry!$C$6),0,MIN(IF(C133&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D133+F133,2)))</f>
         <v/>
       </c>
       <c r="H133" s="18" t="n"/>
@@ -7521,7 +7521,7 @@
         <v/>
       </c>
       <c r="E134" s="26">
-        <f>IF(OR(D134&lt;=0,C134&gt;Parametry!$C$6),0,IF(C134&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D134&lt;=0,C134&gt;Parametry!$C$6),0,IF(C134&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F134" s="25">
@@ -7529,7 +7529,7 @@
         <v/>
       </c>
       <c r="G134" s="25">
-        <f>IF(OR(D134&lt;=0,C134&gt;Parametry!$C$6),0,MIN(IF(C134&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D134+F134,2)))</f>
+        <f>IF(OR(D134&lt;=0,C134&gt;Parametry!$C$6),0,MIN(IF(C134&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D134+F134,2)))</f>
         <v/>
       </c>
       <c r="H134" s="18" t="n"/>
@@ -7570,7 +7570,7 @@
         <v/>
       </c>
       <c r="E135" s="17">
-        <f>IF(OR(D135&lt;=0,C135&gt;Parametry!$C$6),0,IF(C135&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D135&lt;=0,C135&gt;Parametry!$C$6),0,IF(C135&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F135" s="16">
@@ -7578,7 +7578,7 @@
         <v/>
       </c>
       <c r="G135" s="16">
-        <f>IF(OR(D135&lt;=0,C135&gt;Parametry!$C$6),0,MIN(IF(C135&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D135+F135,2)))</f>
+        <f>IF(OR(D135&lt;=0,C135&gt;Parametry!$C$6),0,MIN(IF(C135&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D135+F135,2)))</f>
         <v/>
       </c>
       <c r="H135" s="18" t="n"/>
@@ -7619,7 +7619,7 @@
         <v/>
       </c>
       <c r="E136" s="26">
-        <f>IF(OR(D136&lt;=0,C136&gt;Parametry!$C$6),0,IF(C136&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D136&lt;=0,C136&gt;Parametry!$C$6),0,IF(C136&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F136" s="25">
@@ -7627,7 +7627,7 @@
         <v/>
       </c>
       <c r="G136" s="25">
-        <f>IF(OR(D136&lt;=0,C136&gt;Parametry!$C$6),0,MIN(IF(C136&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D136+F136,2)))</f>
+        <f>IF(OR(D136&lt;=0,C136&gt;Parametry!$C$6),0,MIN(IF(C136&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D136+F136,2)))</f>
         <v/>
       </c>
       <c r="H136" s="18" t="n"/>
@@ -7668,7 +7668,7 @@
         <v/>
       </c>
       <c r="E137" s="17">
-        <f>IF(OR(D137&lt;=0,C137&gt;Parametry!$C$6),0,IF(C137&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D137&lt;=0,C137&gt;Parametry!$C$6),0,IF(C137&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F137" s="16">
@@ -7676,7 +7676,7 @@
         <v/>
       </c>
       <c r="G137" s="16">
-        <f>IF(OR(D137&lt;=0,C137&gt;Parametry!$C$6),0,MIN(IF(C137&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D137+F137,2)))</f>
+        <f>IF(OR(D137&lt;=0,C137&gt;Parametry!$C$6),0,MIN(IF(C137&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D137+F137,2)))</f>
         <v/>
       </c>
       <c r="H137" s="18" t="n"/>
@@ -7717,7 +7717,7 @@
         <v/>
       </c>
       <c r="E138" s="26">
-        <f>IF(OR(D138&lt;=0,C138&gt;Parametry!$C$6),0,IF(C138&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D138&lt;=0,C138&gt;Parametry!$C$6),0,IF(C138&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F138" s="25">
@@ -7725,7 +7725,7 @@
         <v/>
       </c>
       <c r="G138" s="25">
-        <f>IF(OR(D138&lt;=0,C138&gt;Parametry!$C$6),0,MIN(IF(C138&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D138+F138,2)))</f>
+        <f>IF(OR(D138&lt;=0,C138&gt;Parametry!$C$6),0,MIN(IF(C138&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D138+F138,2)))</f>
         <v/>
       </c>
       <c r="H138" s="18" t="n"/>
@@ -7766,7 +7766,7 @@
         <v/>
       </c>
       <c r="E139" s="17">
-        <f>IF(OR(D139&lt;=0,C139&gt;Parametry!$C$6),0,IF(C139&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D139&lt;=0,C139&gt;Parametry!$C$6),0,IF(C139&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F139" s="16">
@@ -7774,7 +7774,7 @@
         <v/>
       </c>
       <c r="G139" s="16">
-        <f>IF(OR(D139&lt;=0,C139&gt;Parametry!$C$6),0,MIN(IF(C139&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D139+F139,2)))</f>
+        <f>IF(OR(D139&lt;=0,C139&gt;Parametry!$C$6),0,MIN(IF(C139&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D139+F139,2)))</f>
         <v/>
       </c>
       <c r="H139" s="18" t="n"/>
@@ -7815,7 +7815,7 @@
         <v/>
       </c>
       <c r="E140" s="26">
-        <f>IF(OR(D140&lt;=0,C140&gt;Parametry!$C$6),0,IF(C140&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D140&lt;=0,C140&gt;Parametry!$C$6),0,IF(C140&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F140" s="25">
@@ -7823,7 +7823,7 @@
         <v/>
       </c>
       <c r="G140" s="25">
-        <f>IF(OR(D140&lt;=0,C140&gt;Parametry!$C$6),0,MIN(IF(C140&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D140+F140,2)))</f>
+        <f>IF(OR(D140&lt;=0,C140&gt;Parametry!$C$6),0,MIN(IF(C140&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D140+F140,2)))</f>
         <v/>
       </c>
       <c r="H140" s="18" t="n"/>
@@ -7864,7 +7864,7 @@
         <v/>
       </c>
       <c r="E141" s="17">
-        <f>IF(OR(D141&lt;=0,C141&gt;Parametry!$C$6),0,IF(C141&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D141&lt;=0,C141&gt;Parametry!$C$6),0,IF(C141&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F141" s="16">
@@ -7872,7 +7872,7 @@
         <v/>
       </c>
       <c r="G141" s="16">
-        <f>IF(OR(D141&lt;=0,C141&gt;Parametry!$C$6),0,MIN(IF(C141&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D141+F141,2)))</f>
+        <f>IF(OR(D141&lt;=0,C141&gt;Parametry!$C$6),0,MIN(IF(C141&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D141+F141,2)))</f>
         <v/>
       </c>
       <c r="H141" s="18" t="n"/>
@@ -7913,7 +7913,7 @@
         <v/>
       </c>
       <c r="E142" s="26">
-        <f>IF(OR(D142&lt;=0,C142&gt;Parametry!$C$6),0,IF(C142&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D142&lt;=0,C142&gt;Parametry!$C$6),0,IF(C142&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F142" s="25">
@@ -7921,7 +7921,7 @@
         <v/>
       </c>
       <c r="G142" s="25">
-        <f>IF(OR(D142&lt;=0,C142&gt;Parametry!$C$6),0,MIN(IF(C142&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D142+F142,2)))</f>
+        <f>IF(OR(D142&lt;=0,C142&gt;Parametry!$C$6),0,MIN(IF(C142&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D142+F142,2)))</f>
         <v/>
       </c>
       <c r="H142" s="18" t="n"/>
@@ -7962,7 +7962,7 @@
         <v/>
       </c>
       <c r="E143" s="17">
-        <f>IF(OR(D143&lt;=0,C143&gt;Parametry!$C$6),0,IF(C143&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D143&lt;=0,C143&gt;Parametry!$C$6),0,IF(C143&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F143" s="16">
@@ -7970,7 +7970,7 @@
         <v/>
       </c>
       <c r="G143" s="16">
-        <f>IF(OR(D143&lt;=0,C143&gt;Parametry!$C$6),0,MIN(IF(C143&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D143+F143,2)))</f>
+        <f>IF(OR(D143&lt;=0,C143&gt;Parametry!$C$6),0,MIN(IF(C143&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D143+F143,2)))</f>
         <v/>
       </c>
       <c r="H143" s="18" t="n"/>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="E144" s="26">
-        <f>IF(OR(D144&lt;=0,C144&gt;Parametry!$C$6),0,IF(C144&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D144&lt;=0,C144&gt;Parametry!$C$6),0,IF(C144&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F144" s="25">
@@ -8019,7 +8019,7 @@
         <v/>
       </c>
       <c r="G144" s="25">
-        <f>IF(OR(D144&lt;=0,C144&gt;Parametry!$C$6),0,MIN(IF(C144&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D144+F144,2)))</f>
+        <f>IF(OR(D144&lt;=0,C144&gt;Parametry!$C$6),0,MIN(IF(C144&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D144+F144,2)))</f>
         <v/>
       </c>
       <c r="H144" s="18" t="n"/>
@@ -8060,7 +8060,7 @@
         <v/>
       </c>
       <c r="E145" s="17">
-        <f>IF(OR(D145&lt;=0,C145&gt;Parametry!$C$6),0,IF(C145&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D145&lt;=0,C145&gt;Parametry!$C$6),0,IF(C145&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F145" s="16">
@@ -8068,7 +8068,7 @@
         <v/>
       </c>
       <c r="G145" s="16">
-        <f>IF(OR(D145&lt;=0,C145&gt;Parametry!$C$6),0,MIN(IF(C145&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D145+F145,2)))</f>
+        <f>IF(OR(D145&lt;=0,C145&gt;Parametry!$C$6),0,MIN(IF(C145&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D145+F145,2)))</f>
         <v/>
       </c>
       <c r="H145" s="18" t="n"/>
@@ -8109,7 +8109,7 @@
         <v/>
       </c>
       <c r="E146" s="26">
-        <f>IF(OR(D146&lt;=0,C146&gt;Parametry!$C$6),0,IF(C146&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D146&lt;=0,C146&gt;Parametry!$C$6),0,IF(C146&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F146" s="25">
@@ -8117,7 +8117,7 @@
         <v/>
       </c>
       <c r="G146" s="25">
-        <f>IF(OR(D146&lt;=0,C146&gt;Parametry!$C$6),0,MIN(IF(C146&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D146+F146,2)))</f>
+        <f>IF(OR(D146&lt;=0,C146&gt;Parametry!$C$6),0,MIN(IF(C146&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D146+F146,2)))</f>
         <v/>
       </c>
       <c r="H146" s="18" t="n"/>
@@ -8158,7 +8158,7 @@
         <v/>
       </c>
       <c r="E147" s="17">
-        <f>IF(OR(D147&lt;=0,C147&gt;Parametry!$C$6),0,IF(C147&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D147&lt;=0,C147&gt;Parametry!$C$6),0,IF(C147&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F147" s="16">
@@ -8166,7 +8166,7 @@
         <v/>
       </c>
       <c r="G147" s="16">
-        <f>IF(OR(D147&lt;=0,C147&gt;Parametry!$C$6),0,MIN(IF(C147&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D147+F147,2)))</f>
+        <f>IF(OR(D147&lt;=0,C147&gt;Parametry!$C$6),0,MIN(IF(C147&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D147+F147,2)))</f>
         <v/>
       </c>
       <c r="H147" s="18" t="n"/>
@@ -8207,7 +8207,7 @@
         <v/>
       </c>
       <c r="E148" s="26">
-        <f>IF(OR(D148&lt;=0,C148&gt;Parametry!$C$6),0,IF(C148&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D148&lt;=0,C148&gt;Parametry!$C$6),0,IF(C148&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F148" s="25">
@@ -8215,7 +8215,7 @@
         <v/>
       </c>
       <c r="G148" s="25">
-        <f>IF(OR(D148&lt;=0,C148&gt;Parametry!$C$6),0,MIN(IF(C148&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D148+F148,2)))</f>
+        <f>IF(OR(D148&lt;=0,C148&gt;Parametry!$C$6),0,MIN(IF(C148&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D148+F148,2)))</f>
         <v/>
       </c>
       <c r="H148" s="18" t="n"/>
@@ -8256,7 +8256,7 @@
         <v/>
       </c>
       <c r="E149" s="17">
-        <f>IF(OR(D149&lt;=0,C149&gt;Parametry!$C$6),0,IF(C149&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D149&lt;=0,C149&gt;Parametry!$C$6),0,IF(C149&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F149" s="16">
@@ -8264,7 +8264,7 @@
         <v/>
       </c>
       <c r="G149" s="16">
-        <f>IF(OR(D149&lt;=0,C149&gt;Parametry!$C$6),0,MIN(IF(C149&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D149+F149,2)))</f>
+        <f>IF(OR(D149&lt;=0,C149&gt;Parametry!$C$6),0,MIN(IF(C149&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D149+F149,2)))</f>
         <v/>
       </c>
       <c r="H149" s="18" t="n"/>
@@ -8305,7 +8305,7 @@
         <v/>
       </c>
       <c r="E150" s="26">
-        <f>IF(OR(D150&lt;=0,C150&gt;Parametry!$C$6),0,IF(C150&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D150&lt;=0,C150&gt;Parametry!$C$6),0,IF(C150&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F150" s="25">
@@ -8313,7 +8313,7 @@
         <v/>
       </c>
       <c r="G150" s="25">
-        <f>IF(OR(D150&lt;=0,C150&gt;Parametry!$C$6),0,MIN(IF(C150&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D150+F150,2)))</f>
+        <f>IF(OR(D150&lt;=0,C150&gt;Parametry!$C$6),0,MIN(IF(C150&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D150+F150,2)))</f>
         <v/>
       </c>
       <c r="H150" s="18" t="n"/>
@@ -8354,7 +8354,7 @@
         <v/>
       </c>
       <c r="E151" s="17">
-        <f>IF(OR(D151&lt;=0,C151&gt;Parametry!$C$6),0,IF(C151&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D151&lt;=0,C151&gt;Parametry!$C$6),0,IF(C151&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F151" s="16">
@@ -8362,7 +8362,7 @@
         <v/>
       </c>
       <c r="G151" s="16">
-        <f>IF(OR(D151&lt;=0,C151&gt;Parametry!$C$6),0,MIN(IF(C151&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D151+F151,2)))</f>
+        <f>IF(OR(D151&lt;=0,C151&gt;Parametry!$C$6),0,MIN(IF(C151&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D151+F151,2)))</f>
         <v/>
       </c>
       <c r="H151" s="18" t="n"/>
@@ -8403,7 +8403,7 @@
         <v/>
       </c>
       <c r="E152" s="26">
-        <f>IF(OR(D152&lt;=0,C152&gt;Parametry!$C$6),0,IF(C152&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D152&lt;=0,C152&gt;Parametry!$C$6),0,IF(C152&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F152" s="25">
@@ -8411,7 +8411,7 @@
         <v/>
       </c>
       <c r="G152" s="25">
-        <f>IF(OR(D152&lt;=0,C152&gt;Parametry!$C$6),0,MIN(IF(C152&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D152+F152,2)))</f>
+        <f>IF(OR(D152&lt;=0,C152&gt;Parametry!$C$6),0,MIN(IF(C152&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D152+F152,2)))</f>
         <v/>
       </c>
       <c r="H152" s="18" t="n"/>
@@ -8452,7 +8452,7 @@
         <v/>
       </c>
       <c r="E153" s="17">
-        <f>IF(OR(D153&lt;=0,C153&gt;Parametry!$C$6),0,IF(C153&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D153&lt;=0,C153&gt;Parametry!$C$6),0,IF(C153&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F153" s="16">
@@ -8460,7 +8460,7 @@
         <v/>
       </c>
       <c r="G153" s="16">
-        <f>IF(OR(D153&lt;=0,C153&gt;Parametry!$C$6),0,MIN(IF(C153&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D153+F153,2)))</f>
+        <f>IF(OR(D153&lt;=0,C153&gt;Parametry!$C$6),0,MIN(IF(C153&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D153+F153,2)))</f>
         <v/>
       </c>
       <c r="H153" s="18" t="n"/>
@@ -8501,7 +8501,7 @@
         <v/>
       </c>
       <c r="E154" s="26">
-        <f>IF(OR(D154&lt;=0,C154&gt;Parametry!$C$6),0,IF(C154&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D154&lt;=0,C154&gt;Parametry!$C$6),0,IF(C154&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F154" s="25">
@@ -8509,7 +8509,7 @@
         <v/>
       </c>
       <c r="G154" s="25">
-        <f>IF(OR(D154&lt;=0,C154&gt;Parametry!$C$6),0,MIN(IF(C154&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D154+F154,2)))</f>
+        <f>IF(OR(D154&lt;=0,C154&gt;Parametry!$C$6),0,MIN(IF(C154&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D154+F154,2)))</f>
         <v/>
       </c>
       <c r="H154" s="18" t="n"/>
@@ -8550,7 +8550,7 @@
         <v/>
       </c>
       <c r="E155" s="17">
-        <f>IF(OR(D155&lt;=0,C155&gt;Parametry!$C$6),0,IF(C155&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D155&lt;=0,C155&gt;Parametry!$C$6),0,IF(C155&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F155" s="16">
@@ -8558,7 +8558,7 @@
         <v/>
       </c>
       <c r="G155" s="16">
-        <f>IF(OR(D155&lt;=0,C155&gt;Parametry!$C$6),0,MIN(IF(C155&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D155+F155,2)))</f>
+        <f>IF(OR(D155&lt;=0,C155&gt;Parametry!$C$6),0,MIN(IF(C155&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D155+F155,2)))</f>
         <v/>
       </c>
       <c r="H155" s="18" t="n"/>
@@ -8599,7 +8599,7 @@
         <v/>
       </c>
       <c r="E156" s="26">
-        <f>IF(OR(D156&lt;=0,C156&gt;Parametry!$C$6),0,IF(C156&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D156&lt;=0,C156&gt;Parametry!$C$6),0,IF(C156&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F156" s="25">
@@ -8607,7 +8607,7 @@
         <v/>
       </c>
       <c r="G156" s="25">
-        <f>IF(OR(D156&lt;=0,C156&gt;Parametry!$C$6),0,MIN(IF(C156&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D156+F156,2)))</f>
+        <f>IF(OR(D156&lt;=0,C156&gt;Parametry!$C$6),0,MIN(IF(C156&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D156+F156,2)))</f>
         <v/>
       </c>
       <c r="H156" s="18" t="n"/>
@@ -8648,7 +8648,7 @@
         <v/>
       </c>
       <c r="E157" s="17">
-        <f>IF(OR(D157&lt;=0,C157&gt;Parametry!$C$6),0,IF(C157&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D157&lt;=0,C157&gt;Parametry!$C$6),0,IF(C157&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F157" s="16">
@@ -8656,7 +8656,7 @@
         <v/>
       </c>
       <c r="G157" s="16">
-        <f>IF(OR(D157&lt;=0,C157&gt;Parametry!$C$6),0,MIN(IF(C157&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D157+F157,2)))</f>
+        <f>IF(OR(D157&lt;=0,C157&gt;Parametry!$C$6),0,MIN(IF(C157&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D157+F157,2)))</f>
         <v/>
       </c>
       <c r="H157" s="18" t="n"/>
@@ -8697,7 +8697,7 @@
         <v/>
       </c>
       <c r="E158" s="26">
-        <f>IF(OR(D158&lt;=0,C158&gt;Parametry!$C$6),0,IF(C158&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D158&lt;=0,C158&gt;Parametry!$C$6),0,IF(C158&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F158" s="25">
@@ -8705,7 +8705,7 @@
         <v/>
       </c>
       <c r="G158" s="25">
-        <f>IF(OR(D158&lt;=0,C158&gt;Parametry!$C$6),0,MIN(IF(C158&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D158+F158,2)))</f>
+        <f>IF(OR(D158&lt;=0,C158&gt;Parametry!$C$6),0,MIN(IF(C158&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D158+F158,2)))</f>
         <v/>
       </c>
       <c r="H158" s="18" t="n"/>
@@ -8746,7 +8746,7 @@
         <v/>
       </c>
       <c r="E159" s="17">
-        <f>IF(OR(D159&lt;=0,C159&gt;Parametry!$C$6),0,IF(C159&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D159&lt;=0,C159&gt;Parametry!$C$6),0,IF(C159&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F159" s="16">
@@ -8754,7 +8754,7 @@
         <v/>
       </c>
       <c r="G159" s="16">
-        <f>IF(OR(D159&lt;=0,C159&gt;Parametry!$C$6),0,MIN(IF(C159&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D159+F159,2)))</f>
+        <f>IF(OR(D159&lt;=0,C159&gt;Parametry!$C$6),0,MIN(IF(C159&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D159+F159,2)))</f>
         <v/>
       </c>
       <c r="H159" s="18" t="n"/>
@@ -8795,7 +8795,7 @@
         <v/>
       </c>
       <c r="E160" s="26">
-        <f>IF(OR(D160&lt;=0,C160&gt;Parametry!$C$6),0,IF(C160&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D160&lt;=0,C160&gt;Parametry!$C$6),0,IF(C160&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F160" s="25">
@@ -8803,7 +8803,7 @@
         <v/>
       </c>
       <c r="G160" s="25">
-        <f>IF(OR(D160&lt;=0,C160&gt;Parametry!$C$6),0,MIN(IF(C160&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D160+F160,2)))</f>
+        <f>IF(OR(D160&lt;=0,C160&gt;Parametry!$C$6),0,MIN(IF(C160&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D160+F160,2)))</f>
         <v/>
       </c>
       <c r="H160" s="18" t="n"/>
@@ -8844,7 +8844,7 @@
         <v/>
       </c>
       <c r="E161" s="17">
-        <f>IF(OR(D161&lt;=0,C161&gt;Parametry!$C$6),0,IF(C161&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D161&lt;=0,C161&gt;Parametry!$C$6),0,IF(C161&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F161" s="16">
@@ -8852,7 +8852,7 @@
         <v/>
       </c>
       <c r="G161" s="16">
-        <f>IF(OR(D161&lt;=0,C161&gt;Parametry!$C$6),0,MIN(IF(C161&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D161+F161,2)))</f>
+        <f>IF(OR(D161&lt;=0,C161&gt;Parametry!$C$6),0,MIN(IF(C161&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D161+F161,2)))</f>
         <v/>
       </c>
       <c r="H161" s="18" t="n"/>
@@ -8893,7 +8893,7 @@
         <v/>
       </c>
       <c r="E162" s="26">
-        <f>IF(OR(D162&lt;=0,C162&gt;Parametry!$C$6),0,IF(C162&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D162&lt;=0,C162&gt;Parametry!$C$6),0,IF(C162&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F162" s="25">
@@ -8901,7 +8901,7 @@
         <v/>
       </c>
       <c r="G162" s="25">
-        <f>IF(OR(D162&lt;=0,C162&gt;Parametry!$C$6),0,MIN(IF(C162&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D162+F162,2)))</f>
+        <f>IF(OR(D162&lt;=0,C162&gt;Parametry!$C$6),0,MIN(IF(C162&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D162+F162,2)))</f>
         <v/>
       </c>
       <c r="H162" s="18" t="n"/>
@@ -8942,7 +8942,7 @@
         <v/>
       </c>
       <c r="E163" s="17">
-        <f>IF(OR(D163&lt;=0,C163&gt;Parametry!$C$6),0,IF(C163&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D163&lt;=0,C163&gt;Parametry!$C$6),0,IF(C163&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F163" s="16">
@@ -8950,7 +8950,7 @@
         <v/>
       </c>
       <c r="G163" s="16">
-        <f>IF(OR(D163&lt;=0,C163&gt;Parametry!$C$6),0,MIN(IF(C163&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D163+F163,2)))</f>
+        <f>IF(OR(D163&lt;=0,C163&gt;Parametry!$C$6),0,MIN(IF(C163&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D163+F163,2)))</f>
         <v/>
       </c>
       <c r="H163" s="18" t="n"/>
@@ -8991,7 +8991,7 @@
         <v/>
       </c>
       <c r="E164" s="26">
-        <f>IF(OR(D164&lt;=0,C164&gt;Parametry!$C$6),0,IF(C164&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D164&lt;=0,C164&gt;Parametry!$C$6),0,IF(C164&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F164" s="25">
@@ -8999,7 +8999,7 @@
         <v/>
       </c>
       <c r="G164" s="25">
-        <f>IF(OR(D164&lt;=0,C164&gt;Parametry!$C$6),0,MIN(IF(C164&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D164+F164,2)))</f>
+        <f>IF(OR(D164&lt;=0,C164&gt;Parametry!$C$6),0,MIN(IF(C164&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D164+F164,2)))</f>
         <v/>
       </c>
       <c r="H164" s="18" t="n"/>
@@ -9040,7 +9040,7 @@
         <v/>
       </c>
       <c r="E165" s="17">
-        <f>IF(OR(D165&lt;=0,C165&gt;Parametry!$C$6),0,IF(C165&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D165&lt;=0,C165&gt;Parametry!$C$6),0,IF(C165&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F165" s="16">
@@ -9048,7 +9048,7 @@
         <v/>
       </c>
       <c r="G165" s="16">
-        <f>IF(OR(D165&lt;=0,C165&gt;Parametry!$C$6),0,MIN(IF(C165&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D165+F165,2)))</f>
+        <f>IF(OR(D165&lt;=0,C165&gt;Parametry!$C$6),0,MIN(IF(C165&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D165+F165,2)))</f>
         <v/>
       </c>
       <c r="H165" s="18" t="n"/>
@@ -9089,7 +9089,7 @@
         <v/>
       </c>
       <c r="E166" s="26">
-        <f>IF(OR(D166&lt;=0,C166&gt;Parametry!$C$6),0,IF(C166&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D166&lt;=0,C166&gt;Parametry!$C$6),0,IF(C166&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F166" s="25">
@@ -9097,7 +9097,7 @@
         <v/>
       </c>
       <c r="G166" s="25">
-        <f>IF(OR(D166&lt;=0,C166&gt;Parametry!$C$6),0,MIN(IF(C166&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D166+F166,2)))</f>
+        <f>IF(OR(D166&lt;=0,C166&gt;Parametry!$C$6),0,MIN(IF(C166&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D166+F166,2)))</f>
         <v/>
       </c>
       <c r="H166" s="18" t="n"/>
@@ -9138,7 +9138,7 @@
         <v/>
       </c>
       <c r="E167" s="17">
-        <f>IF(OR(D167&lt;=0,C167&gt;Parametry!$C$6),0,IF(C167&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D167&lt;=0,C167&gt;Parametry!$C$6),0,IF(C167&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F167" s="16">
@@ -9146,7 +9146,7 @@
         <v/>
       </c>
       <c r="G167" s="16">
-        <f>IF(OR(D167&lt;=0,C167&gt;Parametry!$C$6),0,MIN(IF(C167&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D167+F167,2)))</f>
+        <f>IF(OR(D167&lt;=0,C167&gt;Parametry!$C$6),0,MIN(IF(C167&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D167+F167,2)))</f>
         <v/>
       </c>
       <c r="H167" s="18" t="n"/>
@@ -9187,7 +9187,7 @@
         <v/>
       </c>
       <c r="E168" s="26">
-        <f>IF(OR(D168&lt;=0,C168&gt;Parametry!$C$6),0,IF(C168&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D168&lt;=0,C168&gt;Parametry!$C$6),0,IF(C168&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F168" s="25">
@@ -9195,7 +9195,7 @@
         <v/>
       </c>
       <c r="G168" s="25">
-        <f>IF(OR(D168&lt;=0,C168&gt;Parametry!$C$6),0,MIN(IF(C168&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D168+F168,2)))</f>
+        <f>IF(OR(D168&lt;=0,C168&gt;Parametry!$C$6),0,MIN(IF(C168&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D168+F168,2)))</f>
         <v/>
       </c>
       <c r="H168" s="18" t="n"/>
@@ -9236,7 +9236,7 @@
         <v/>
       </c>
       <c r="E169" s="17">
-        <f>IF(OR(D169&lt;=0,C169&gt;Parametry!$C$6),0,IF(C169&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D169&lt;=0,C169&gt;Parametry!$C$6),0,IF(C169&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F169" s="16">
@@ -9244,7 +9244,7 @@
         <v/>
       </c>
       <c r="G169" s="16">
-        <f>IF(OR(D169&lt;=0,C169&gt;Parametry!$C$6),0,MIN(IF(C169&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D169+F169,2)))</f>
+        <f>IF(OR(D169&lt;=0,C169&gt;Parametry!$C$6),0,MIN(IF(C169&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D169+F169,2)))</f>
         <v/>
       </c>
       <c r="H169" s="18" t="n"/>
@@ -9285,7 +9285,7 @@
         <v/>
       </c>
       <c r="E170" s="26">
-        <f>IF(OR(D170&lt;=0,C170&gt;Parametry!$C$6),0,IF(C170&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D170&lt;=0,C170&gt;Parametry!$C$6),0,IF(C170&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F170" s="25">
@@ -9293,7 +9293,7 @@
         <v/>
       </c>
       <c r="G170" s="25">
-        <f>IF(OR(D170&lt;=0,C170&gt;Parametry!$C$6),0,MIN(IF(C170&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D170+F170,2)))</f>
+        <f>IF(OR(D170&lt;=0,C170&gt;Parametry!$C$6),0,MIN(IF(C170&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D170+F170,2)))</f>
         <v/>
       </c>
       <c r="H170" s="18" t="n"/>
@@ -9334,7 +9334,7 @@
         <v/>
       </c>
       <c r="E171" s="17">
-        <f>IF(OR(D171&lt;=0,C171&gt;Parametry!$C$6),0,IF(C171&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D171&lt;=0,C171&gt;Parametry!$C$6),0,IF(C171&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F171" s="16">
@@ -9342,7 +9342,7 @@
         <v/>
       </c>
       <c r="G171" s="16">
-        <f>IF(OR(D171&lt;=0,C171&gt;Parametry!$C$6),0,MIN(IF(C171&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D171+F171,2)))</f>
+        <f>IF(OR(D171&lt;=0,C171&gt;Parametry!$C$6),0,MIN(IF(C171&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D171+F171,2)))</f>
         <v/>
       </c>
       <c r="H171" s="18" t="n"/>
@@ -9383,7 +9383,7 @@
         <v/>
       </c>
       <c r="E172" s="26">
-        <f>IF(OR(D172&lt;=0,C172&gt;Parametry!$C$6),0,IF(C172&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D172&lt;=0,C172&gt;Parametry!$C$6),0,IF(C172&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F172" s="25">
@@ -9391,7 +9391,7 @@
         <v/>
       </c>
       <c r="G172" s="25">
-        <f>IF(OR(D172&lt;=0,C172&gt;Parametry!$C$6),0,MIN(IF(C172&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D172+F172,2)))</f>
+        <f>IF(OR(D172&lt;=0,C172&gt;Parametry!$C$6),0,MIN(IF(C172&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D172+F172,2)))</f>
         <v/>
       </c>
       <c r="H172" s="18" t="n"/>
@@ -9432,7 +9432,7 @@
         <v/>
       </c>
       <c r="E173" s="17">
-        <f>IF(OR(D173&lt;=0,C173&gt;Parametry!$C$6),0,IF(C173&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D173&lt;=0,C173&gt;Parametry!$C$6),0,IF(C173&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F173" s="16">
@@ -9440,7 +9440,7 @@
         <v/>
       </c>
       <c r="G173" s="16">
-        <f>IF(OR(D173&lt;=0,C173&gt;Parametry!$C$6),0,MIN(IF(C173&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D173+F173,2)))</f>
+        <f>IF(OR(D173&lt;=0,C173&gt;Parametry!$C$6),0,MIN(IF(C173&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D173+F173,2)))</f>
         <v/>
       </c>
       <c r="H173" s="18" t="n"/>
@@ -9481,7 +9481,7 @@
         <v/>
       </c>
       <c r="E174" s="26">
-        <f>IF(OR(D174&lt;=0,C174&gt;Parametry!$C$6),0,IF(C174&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D174&lt;=0,C174&gt;Parametry!$C$6),0,IF(C174&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F174" s="25">
@@ -9489,7 +9489,7 @@
         <v/>
       </c>
       <c r="G174" s="25">
-        <f>IF(OR(D174&lt;=0,C174&gt;Parametry!$C$6),0,MIN(IF(C174&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D174+F174,2)))</f>
+        <f>IF(OR(D174&lt;=0,C174&gt;Parametry!$C$6),0,MIN(IF(C174&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D174+F174,2)))</f>
         <v/>
       </c>
       <c r="H174" s="18" t="n"/>
@@ -9530,7 +9530,7 @@
         <v/>
       </c>
       <c r="E175" s="17">
-        <f>IF(OR(D175&lt;=0,C175&gt;Parametry!$C$6),0,IF(C175&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D175&lt;=0,C175&gt;Parametry!$C$6),0,IF(C175&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F175" s="16">
@@ -9538,7 +9538,7 @@
         <v/>
       </c>
       <c r="G175" s="16">
-        <f>IF(OR(D175&lt;=0,C175&gt;Parametry!$C$6),0,MIN(IF(C175&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D175+F175,2)))</f>
+        <f>IF(OR(D175&lt;=0,C175&gt;Parametry!$C$6),0,MIN(IF(C175&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D175+F175,2)))</f>
         <v/>
       </c>
       <c r="H175" s="18" t="n"/>
@@ -9579,7 +9579,7 @@
         <v/>
       </c>
       <c r="E176" s="26">
-        <f>IF(OR(D176&lt;=0,C176&gt;Parametry!$C$6),0,IF(C176&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D176&lt;=0,C176&gt;Parametry!$C$6),0,IF(C176&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F176" s="25">
@@ -9587,7 +9587,7 @@
         <v/>
       </c>
       <c r="G176" s="25">
-        <f>IF(OR(D176&lt;=0,C176&gt;Parametry!$C$6),0,MIN(IF(C176&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D176+F176,2)))</f>
+        <f>IF(OR(D176&lt;=0,C176&gt;Parametry!$C$6),0,MIN(IF(C176&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D176+F176,2)))</f>
         <v/>
       </c>
       <c r="H176" s="18" t="n"/>
@@ -9628,7 +9628,7 @@
         <v/>
       </c>
       <c r="E177" s="17">
-        <f>IF(OR(D177&lt;=0,C177&gt;Parametry!$C$6),0,IF(C177&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D177&lt;=0,C177&gt;Parametry!$C$6),0,IF(C177&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F177" s="16">
@@ -9636,7 +9636,7 @@
         <v/>
       </c>
       <c r="G177" s="16">
-        <f>IF(OR(D177&lt;=0,C177&gt;Parametry!$C$6),0,MIN(IF(C177&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D177+F177,2)))</f>
+        <f>IF(OR(D177&lt;=0,C177&gt;Parametry!$C$6),0,MIN(IF(C177&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D177+F177,2)))</f>
         <v/>
       </c>
       <c r="H177" s="18" t="n"/>
@@ -9677,7 +9677,7 @@
         <v/>
       </c>
       <c r="E178" s="26">
-        <f>IF(OR(D178&lt;=0,C178&gt;Parametry!$C$6),0,IF(C178&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D178&lt;=0,C178&gt;Parametry!$C$6),0,IF(C178&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F178" s="25">
@@ -9685,7 +9685,7 @@
         <v/>
       </c>
       <c r="G178" s="25">
-        <f>IF(OR(D178&lt;=0,C178&gt;Parametry!$C$6),0,MIN(IF(C178&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D178+F178,2)))</f>
+        <f>IF(OR(D178&lt;=0,C178&gt;Parametry!$C$6),0,MIN(IF(C178&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D178+F178,2)))</f>
         <v/>
       </c>
       <c r="H178" s="18" t="n"/>
@@ -9726,7 +9726,7 @@
         <v/>
       </c>
       <c r="E179" s="17">
-        <f>IF(OR(D179&lt;=0,C179&gt;Parametry!$C$6),0,IF(C179&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D179&lt;=0,C179&gt;Parametry!$C$6),0,IF(C179&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F179" s="16">
@@ -9734,7 +9734,7 @@
         <v/>
       </c>
       <c r="G179" s="16">
-        <f>IF(OR(D179&lt;=0,C179&gt;Parametry!$C$6),0,MIN(IF(C179&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D179+F179,2)))</f>
+        <f>IF(OR(D179&lt;=0,C179&gt;Parametry!$C$6),0,MIN(IF(C179&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D179+F179,2)))</f>
         <v/>
       </c>
       <c r="H179" s="18" t="n"/>
@@ -9775,7 +9775,7 @@
         <v/>
       </c>
       <c r="E180" s="26">
-        <f>IF(OR(D180&lt;=0,C180&gt;Parametry!$C$6),0,IF(C180&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D180&lt;=0,C180&gt;Parametry!$C$6),0,IF(C180&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F180" s="25">
@@ -9783,7 +9783,7 @@
         <v/>
       </c>
       <c r="G180" s="25">
-        <f>IF(OR(D180&lt;=0,C180&gt;Parametry!$C$6),0,MIN(IF(C180&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D180+F180,2)))</f>
+        <f>IF(OR(D180&lt;=0,C180&gt;Parametry!$C$6),0,MIN(IF(C180&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D180+F180,2)))</f>
         <v/>
       </c>
       <c r="H180" s="18" t="n"/>
@@ -9824,7 +9824,7 @@
         <v/>
       </c>
       <c r="E181" s="17">
-        <f>IF(OR(D181&lt;=0,C181&gt;Parametry!$C$6),0,IF(C181&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D181&lt;=0,C181&gt;Parametry!$C$6),0,IF(C181&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F181" s="16">
@@ -9832,7 +9832,7 @@
         <v/>
       </c>
       <c r="G181" s="16">
-        <f>IF(OR(D181&lt;=0,C181&gt;Parametry!$C$6),0,MIN(IF(C181&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D181+F181,2)))</f>
+        <f>IF(OR(D181&lt;=0,C181&gt;Parametry!$C$6),0,MIN(IF(C181&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D181+F181,2)))</f>
         <v/>
       </c>
       <c r="H181" s="18" t="n"/>
@@ -9873,7 +9873,7 @@
         <v/>
       </c>
       <c r="E182" s="26">
-        <f>IF(OR(D182&lt;=0,C182&gt;Parametry!$C$6),0,IF(C182&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D182&lt;=0,C182&gt;Parametry!$C$6),0,IF(C182&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F182" s="25">
@@ -9881,7 +9881,7 @@
         <v/>
       </c>
       <c r="G182" s="25">
-        <f>IF(OR(D182&lt;=0,C182&gt;Parametry!$C$6),0,MIN(IF(C182&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D182+F182,2)))</f>
+        <f>IF(OR(D182&lt;=0,C182&gt;Parametry!$C$6),0,MIN(IF(C182&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D182+F182,2)))</f>
         <v/>
       </c>
       <c r="H182" s="18" t="n"/>
@@ -9922,7 +9922,7 @@
         <v/>
       </c>
       <c r="E183" s="17">
-        <f>IF(OR(D183&lt;=0,C183&gt;Parametry!$C$6),0,IF(C183&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D183&lt;=0,C183&gt;Parametry!$C$6),0,IF(C183&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F183" s="16">
@@ -9930,7 +9930,7 @@
         <v/>
       </c>
       <c r="G183" s="16">
-        <f>IF(OR(D183&lt;=0,C183&gt;Parametry!$C$6),0,MIN(IF(C183&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D183+F183,2)))</f>
+        <f>IF(OR(D183&lt;=0,C183&gt;Parametry!$C$6),0,MIN(IF(C183&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D183+F183,2)))</f>
         <v/>
       </c>
       <c r="H183" s="18" t="n"/>
@@ -9971,7 +9971,7 @@
         <v/>
       </c>
       <c r="E184" s="26">
-        <f>IF(OR(D184&lt;=0,C184&gt;Parametry!$C$6),0,IF(C184&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D184&lt;=0,C184&gt;Parametry!$C$6),0,IF(C184&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F184" s="25">
@@ -9979,7 +9979,7 @@
         <v/>
       </c>
       <c r="G184" s="25">
-        <f>IF(OR(D184&lt;=0,C184&gt;Parametry!$C$6),0,MIN(IF(C184&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D184+F184,2)))</f>
+        <f>IF(OR(D184&lt;=0,C184&gt;Parametry!$C$6),0,MIN(IF(C184&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D184+F184,2)))</f>
         <v/>
       </c>
       <c r="H184" s="18" t="n"/>
@@ -10020,7 +10020,7 @@
         <v/>
       </c>
       <c r="E185" s="17">
-        <f>IF(OR(D185&lt;=0,C185&gt;Parametry!$C$6),0,IF(C185&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D185&lt;=0,C185&gt;Parametry!$C$6),0,IF(C185&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F185" s="16">
@@ -10028,7 +10028,7 @@
         <v/>
       </c>
       <c r="G185" s="16">
-        <f>IF(OR(D185&lt;=0,C185&gt;Parametry!$C$6),0,MIN(IF(C185&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D185+F185,2)))</f>
+        <f>IF(OR(D185&lt;=0,C185&gt;Parametry!$C$6),0,MIN(IF(C185&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D185+F185,2)))</f>
         <v/>
       </c>
       <c r="H185" s="18" t="n"/>
@@ -10069,7 +10069,7 @@
         <v/>
       </c>
       <c r="E186" s="26">
-        <f>IF(OR(D186&lt;=0,C186&gt;Parametry!$C$6),0,IF(C186&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D186&lt;=0,C186&gt;Parametry!$C$6),0,IF(C186&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F186" s="25">
@@ -10077,7 +10077,7 @@
         <v/>
       </c>
       <c r="G186" s="25">
-        <f>IF(OR(D186&lt;=0,C186&gt;Parametry!$C$6),0,MIN(IF(C186&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D186+F186,2)))</f>
+        <f>IF(OR(D186&lt;=0,C186&gt;Parametry!$C$6),0,MIN(IF(C186&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D186+F186,2)))</f>
         <v/>
       </c>
       <c r="H186" s="18" t="n"/>
@@ -10118,7 +10118,7 @@
         <v/>
       </c>
       <c r="E187" s="17">
-        <f>IF(OR(D187&lt;=0,C187&gt;Parametry!$C$6),0,IF(C187&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D187&lt;=0,C187&gt;Parametry!$C$6),0,IF(C187&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F187" s="16">
@@ -10126,7 +10126,7 @@
         <v/>
       </c>
       <c r="G187" s="16">
-        <f>IF(OR(D187&lt;=0,C187&gt;Parametry!$C$6),0,MIN(IF(C187&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D187+F187,2)))</f>
+        <f>IF(OR(D187&lt;=0,C187&gt;Parametry!$C$6),0,MIN(IF(C187&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D187+F187,2)))</f>
         <v/>
       </c>
       <c r="H187" s="18" t="n"/>
@@ -10167,7 +10167,7 @@
         <v/>
       </c>
       <c r="E188" s="26">
-        <f>IF(OR(D188&lt;=0,C188&gt;Parametry!$C$6),0,IF(C188&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D188&lt;=0,C188&gt;Parametry!$C$6),0,IF(C188&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F188" s="25">
@@ -10175,7 +10175,7 @@
         <v/>
       </c>
       <c r="G188" s="25">
-        <f>IF(OR(D188&lt;=0,C188&gt;Parametry!$C$6),0,MIN(IF(C188&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D188+F188,2)))</f>
+        <f>IF(OR(D188&lt;=0,C188&gt;Parametry!$C$6),0,MIN(IF(C188&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D188+F188,2)))</f>
         <v/>
       </c>
       <c r="H188" s="18" t="n"/>
@@ -10216,7 +10216,7 @@
         <v/>
       </c>
       <c r="E189" s="17">
-        <f>IF(OR(D189&lt;=0,C189&gt;Parametry!$C$6),0,IF(C189&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D189&lt;=0,C189&gt;Parametry!$C$6),0,IF(C189&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F189" s="16">
@@ -10224,7 +10224,7 @@
         <v/>
       </c>
       <c r="G189" s="16">
-        <f>IF(OR(D189&lt;=0,C189&gt;Parametry!$C$6),0,MIN(IF(C189&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D189+F189,2)))</f>
+        <f>IF(OR(D189&lt;=0,C189&gt;Parametry!$C$6),0,MIN(IF(C189&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D189+F189,2)))</f>
         <v/>
       </c>
       <c r="H189" s="18" t="n"/>
@@ -10265,7 +10265,7 @@
         <v/>
       </c>
       <c r="E190" s="26">
-        <f>IF(OR(D190&lt;=0,C190&gt;Parametry!$C$6),0,IF(C190&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D190&lt;=0,C190&gt;Parametry!$C$6),0,IF(C190&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F190" s="25">
@@ -10273,7 +10273,7 @@
         <v/>
       </c>
       <c r="G190" s="25">
-        <f>IF(OR(D190&lt;=0,C190&gt;Parametry!$C$6),0,MIN(IF(C190&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D190+F190,2)))</f>
+        <f>IF(OR(D190&lt;=0,C190&gt;Parametry!$C$6),0,MIN(IF(C190&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D190+F190,2)))</f>
         <v/>
       </c>
       <c r="H190" s="18" t="n"/>
@@ -10314,7 +10314,7 @@
         <v/>
       </c>
       <c r="E191" s="17">
-        <f>IF(OR(D191&lt;=0,C191&gt;Parametry!$C$6),0,IF(C191&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D191&lt;=0,C191&gt;Parametry!$C$6),0,IF(C191&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F191" s="16">
@@ -10322,7 +10322,7 @@
         <v/>
       </c>
       <c r="G191" s="16">
-        <f>IF(OR(D191&lt;=0,C191&gt;Parametry!$C$6),0,MIN(IF(C191&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D191+F191,2)))</f>
+        <f>IF(OR(D191&lt;=0,C191&gt;Parametry!$C$6),0,MIN(IF(C191&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D191+F191,2)))</f>
         <v/>
       </c>
       <c r="H191" s="18" t="n"/>
@@ -10363,7 +10363,7 @@
         <v/>
       </c>
       <c r="E192" s="26">
-        <f>IF(OR(D192&lt;=0,C192&gt;Parametry!$C$6),0,IF(C192&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D192&lt;=0,C192&gt;Parametry!$C$6),0,IF(C192&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F192" s="25">
@@ -10371,7 +10371,7 @@
         <v/>
       </c>
       <c r="G192" s="25">
-        <f>IF(OR(D192&lt;=0,C192&gt;Parametry!$C$6),0,MIN(IF(C192&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D192+F192,2)))</f>
+        <f>IF(OR(D192&lt;=0,C192&gt;Parametry!$C$6),0,MIN(IF(C192&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D192+F192,2)))</f>
         <v/>
       </c>
       <c r="H192" s="18" t="n"/>
@@ -10412,7 +10412,7 @@
         <v/>
       </c>
       <c r="E193" s="17">
-        <f>IF(OR(D193&lt;=0,C193&gt;Parametry!$C$6),0,IF(C193&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D193&lt;=0,C193&gt;Parametry!$C$6),0,IF(C193&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F193" s="16">
@@ -10420,7 +10420,7 @@
         <v/>
       </c>
       <c r="G193" s="16">
-        <f>IF(OR(D193&lt;=0,C193&gt;Parametry!$C$6),0,MIN(IF(C193&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D193+F193,2)))</f>
+        <f>IF(OR(D193&lt;=0,C193&gt;Parametry!$C$6),0,MIN(IF(C193&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D193+F193,2)))</f>
         <v/>
       </c>
       <c r="H193" s="18" t="n"/>
@@ -10461,7 +10461,7 @@
         <v/>
       </c>
       <c r="E194" s="26">
-        <f>IF(OR(D194&lt;=0,C194&gt;Parametry!$C$6),0,IF(C194&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D194&lt;=0,C194&gt;Parametry!$C$6),0,IF(C194&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F194" s="25">
@@ -10469,7 +10469,7 @@
         <v/>
       </c>
       <c r="G194" s="25">
-        <f>IF(OR(D194&lt;=0,C194&gt;Parametry!$C$6),0,MIN(IF(C194&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D194+F194,2)))</f>
+        <f>IF(OR(D194&lt;=0,C194&gt;Parametry!$C$6),0,MIN(IF(C194&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D194+F194,2)))</f>
         <v/>
       </c>
       <c r="H194" s="18" t="n"/>
@@ -10510,7 +10510,7 @@
         <v/>
       </c>
       <c r="E195" s="17">
-        <f>IF(OR(D195&lt;=0,C195&gt;Parametry!$C$6),0,IF(C195&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D195&lt;=0,C195&gt;Parametry!$C$6),0,IF(C195&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F195" s="16">
@@ -10518,7 +10518,7 @@
         <v/>
       </c>
       <c r="G195" s="16">
-        <f>IF(OR(D195&lt;=0,C195&gt;Parametry!$C$6),0,MIN(IF(C195&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D195+F195,2)))</f>
+        <f>IF(OR(D195&lt;=0,C195&gt;Parametry!$C$6),0,MIN(IF(C195&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D195+F195,2)))</f>
         <v/>
       </c>
       <c r="H195" s="18" t="n"/>
@@ -10559,7 +10559,7 @@
         <v/>
       </c>
       <c r="E196" s="26">
-        <f>IF(OR(D196&lt;=0,C196&gt;Parametry!$C$6),0,IF(C196&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D196&lt;=0,C196&gt;Parametry!$C$6),0,IF(C196&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F196" s="25">
@@ -10567,7 +10567,7 @@
         <v/>
       </c>
       <c r="G196" s="25">
-        <f>IF(OR(D196&lt;=0,C196&gt;Parametry!$C$6),0,MIN(IF(C196&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D196+F196,2)))</f>
+        <f>IF(OR(D196&lt;=0,C196&gt;Parametry!$C$6),0,MIN(IF(C196&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D196+F196,2)))</f>
         <v/>
       </c>
       <c r="H196" s="18" t="n"/>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="E197" s="17">
-        <f>IF(OR(D197&lt;=0,C197&gt;Parametry!$C$6),0,IF(C197&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D197&lt;=0,C197&gt;Parametry!$C$6),0,IF(C197&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F197" s="16">
@@ -10616,7 +10616,7 @@
         <v/>
       </c>
       <c r="G197" s="16">
-        <f>IF(OR(D197&lt;=0,C197&gt;Parametry!$C$6),0,MIN(IF(C197&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D197+F197,2)))</f>
+        <f>IF(OR(D197&lt;=0,C197&gt;Parametry!$C$6),0,MIN(IF(C197&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D197+F197,2)))</f>
         <v/>
       </c>
       <c r="H197" s="18" t="n"/>
@@ -10657,7 +10657,7 @@
         <v/>
       </c>
       <c r="E198" s="26">
-        <f>IF(OR(D198&lt;=0,C198&gt;Parametry!$C$6),0,IF(C198&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D198&lt;=0,C198&gt;Parametry!$C$6),0,IF(C198&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F198" s="25">
@@ -10665,7 +10665,7 @@
         <v/>
       </c>
       <c r="G198" s="25">
-        <f>IF(OR(D198&lt;=0,C198&gt;Parametry!$C$6),0,MIN(IF(C198&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D198+F198,2)))</f>
+        <f>IF(OR(D198&lt;=0,C198&gt;Parametry!$C$6),0,MIN(IF(C198&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D198+F198,2)))</f>
         <v/>
       </c>
       <c r="H198" s="18" t="n"/>
@@ -10706,7 +10706,7 @@
         <v/>
       </c>
       <c r="E199" s="17">
-        <f>IF(OR(D199&lt;=0,C199&gt;Parametry!$C$6),0,IF(C199&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D199&lt;=0,C199&gt;Parametry!$C$6),0,IF(C199&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F199" s="16">
@@ -10714,7 +10714,7 @@
         <v/>
       </c>
       <c r="G199" s="16">
-        <f>IF(OR(D199&lt;=0,C199&gt;Parametry!$C$6),0,MIN(IF(C199&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D199+F199,2)))</f>
+        <f>IF(OR(D199&lt;=0,C199&gt;Parametry!$C$6),0,MIN(IF(C199&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D199+F199,2)))</f>
         <v/>
       </c>
       <c r="H199" s="18" t="n"/>
@@ -10755,7 +10755,7 @@
         <v/>
       </c>
       <c r="E200" s="26">
-        <f>IF(OR(D200&lt;=0,C200&gt;Parametry!$C$6),0,IF(C200&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D200&lt;=0,C200&gt;Parametry!$C$6),0,IF(C200&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F200" s="25">
@@ -10763,7 +10763,7 @@
         <v/>
       </c>
       <c r="G200" s="25">
-        <f>IF(OR(D200&lt;=0,C200&gt;Parametry!$C$6),0,MIN(IF(C200&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D200+F200,2)))</f>
+        <f>IF(OR(D200&lt;=0,C200&gt;Parametry!$C$6),0,MIN(IF(C200&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D200+F200,2)))</f>
         <v/>
       </c>
       <c r="H200" s="18" t="n"/>
@@ -10804,7 +10804,7 @@
         <v/>
       </c>
       <c r="E201" s="17">
-        <f>IF(OR(D201&lt;=0,C201&gt;Parametry!$C$6),0,IF(C201&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D201&lt;=0,C201&gt;Parametry!$C$6),0,IF(C201&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F201" s="16">
@@ -10812,7 +10812,7 @@
         <v/>
       </c>
       <c r="G201" s="16">
-        <f>IF(OR(D201&lt;=0,C201&gt;Parametry!$C$6),0,MIN(IF(C201&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D201+F201,2)))</f>
+        <f>IF(OR(D201&lt;=0,C201&gt;Parametry!$C$6),0,MIN(IF(C201&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D201+F201,2)))</f>
         <v/>
       </c>
       <c r="H201" s="18" t="n"/>
@@ -10853,7 +10853,7 @@
         <v/>
       </c>
       <c r="E202" s="26">
-        <f>IF(OR(D202&lt;=0,C202&gt;Parametry!$C$6),0,IF(C202&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D202&lt;=0,C202&gt;Parametry!$C$6),0,IF(C202&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F202" s="25">
@@ -10861,7 +10861,7 @@
         <v/>
       </c>
       <c r="G202" s="25">
-        <f>IF(OR(D202&lt;=0,C202&gt;Parametry!$C$6),0,MIN(IF(C202&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D202+F202,2)))</f>
+        <f>IF(OR(D202&lt;=0,C202&gt;Parametry!$C$6),0,MIN(IF(C202&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D202+F202,2)))</f>
         <v/>
       </c>
       <c r="H202" s="18" t="n"/>
@@ -10902,7 +10902,7 @@
         <v/>
       </c>
       <c r="E203" s="17">
-        <f>IF(OR(D203&lt;=0,C203&gt;Parametry!$C$6),0,IF(C203&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D203&lt;=0,C203&gt;Parametry!$C$6),0,IF(C203&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F203" s="16">
@@ -10910,7 +10910,7 @@
         <v/>
       </c>
       <c r="G203" s="16">
-        <f>IF(OR(D203&lt;=0,C203&gt;Parametry!$C$6),0,MIN(IF(C203&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D203+F203,2)))</f>
+        <f>IF(OR(D203&lt;=0,C203&gt;Parametry!$C$6),0,MIN(IF(C203&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D203+F203,2)))</f>
         <v/>
       </c>
       <c r="H203" s="18" t="n"/>
@@ -10951,7 +10951,7 @@
         <v/>
       </c>
       <c r="E204" s="26">
-        <f>IF(OR(D204&lt;=0,C204&gt;Parametry!$C$6),0,IF(C204&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D204&lt;=0,C204&gt;Parametry!$C$6),0,IF(C204&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F204" s="25">
@@ -10959,7 +10959,7 @@
         <v/>
       </c>
       <c r="G204" s="25">
-        <f>IF(OR(D204&lt;=0,C204&gt;Parametry!$C$6),0,MIN(IF(C204&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D204+F204,2)))</f>
+        <f>IF(OR(D204&lt;=0,C204&gt;Parametry!$C$6),0,MIN(IF(C204&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D204+F204,2)))</f>
         <v/>
       </c>
       <c r="H204" s="18" t="n"/>
@@ -11000,7 +11000,7 @@
         <v/>
       </c>
       <c r="E205" s="17">
-        <f>IF(OR(D205&lt;=0,C205&gt;Parametry!$C$6),0,IF(C205&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D205&lt;=0,C205&gt;Parametry!$C$6),0,IF(C205&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F205" s="16">
@@ -11008,7 +11008,7 @@
         <v/>
       </c>
       <c r="G205" s="16">
-        <f>IF(OR(D205&lt;=0,C205&gt;Parametry!$C$6),0,MIN(IF(C205&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D205+F205,2)))</f>
+        <f>IF(OR(D205&lt;=0,C205&gt;Parametry!$C$6),0,MIN(IF(C205&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D205+F205,2)))</f>
         <v/>
       </c>
       <c r="H205" s="18" t="n"/>
@@ -11049,7 +11049,7 @@
         <v/>
       </c>
       <c r="E206" s="26">
-        <f>IF(OR(D206&lt;=0,C206&gt;Parametry!$C$6),0,IF(C206&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D206&lt;=0,C206&gt;Parametry!$C$6),0,IF(C206&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F206" s="25">
@@ -11057,7 +11057,7 @@
         <v/>
       </c>
       <c r="G206" s="25">
-        <f>IF(OR(D206&lt;=0,C206&gt;Parametry!$C$6),0,MIN(IF(C206&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D206+F206,2)))</f>
+        <f>IF(OR(D206&lt;=0,C206&gt;Parametry!$C$6),0,MIN(IF(C206&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D206+F206,2)))</f>
         <v/>
       </c>
       <c r="H206" s="18" t="n"/>
@@ -11098,7 +11098,7 @@
         <v/>
       </c>
       <c r="E207" s="17">
-        <f>IF(OR(D207&lt;=0,C207&gt;Parametry!$C$6),0,IF(C207&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D207&lt;=0,C207&gt;Parametry!$C$6),0,IF(C207&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F207" s="16">
@@ -11106,7 +11106,7 @@
         <v/>
       </c>
       <c r="G207" s="16">
-        <f>IF(OR(D207&lt;=0,C207&gt;Parametry!$C$6),0,MIN(IF(C207&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D207+F207,2)))</f>
+        <f>IF(OR(D207&lt;=0,C207&gt;Parametry!$C$6),0,MIN(IF(C207&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D207+F207,2)))</f>
         <v/>
       </c>
       <c r="H207" s="18" t="n"/>
@@ -11147,7 +11147,7 @@
         <v/>
       </c>
       <c r="E208" s="26">
-        <f>IF(OR(D208&lt;=0,C208&gt;Parametry!$C$6),0,IF(C208&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D208&lt;=0,C208&gt;Parametry!$C$6),0,IF(C208&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F208" s="25">
@@ -11155,7 +11155,7 @@
         <v/>
       </c>
       <c r="G208" s="25">
-        <f>IF(OR(D208&lt;=0,C208&gt;Parametry!$C$6),0,MIN(IF(C208&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D208+F208,2)))</f>
+        <f>IF(OR(D208&lt;=0,C208&gt;Parametry!$C$6),0,MIN(IF(C208&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D208+F208,2)))</f>
         <v/>
       </c>
       <c r="H208" s="18" t="n"/>
@@ -11196,7 +11196,7 @@
         <v/>
       </c>
       <c r="E209" s="17">
-        <f>IF(OR(D209&lt;=0,C209&gt;Parametry!$C$6),0,IF(C209&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D209&lt;=0,C209&gt;Parametry!$C$6),0,IF(C209&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F209" s="16">
@@ -11204,7 +11204,7 @@
         <v/>
       </c>
       <c r="G209" s="16">
-        <f>IF(OR(D209&lt;=0,C209&gt;Parametry!$C$6),0,MIN(IF(C209&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D209+F209,2)))</f>
+        <f>IF(OR(D209&lt;=0,C209&gt;Parametry!$C$6),0,MIN(IF(C209&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D209+F209,2)))</f>
         <v/>
       </c>
       <c r="H209" s="18" t="n"/>
@@ -11245,7 +11245,7 @@
         <v/>
       </c>
       <c r="E210" s="26">
-        <f>IF(OR(D210&lt;=0,C210&gt;Parametry!$C$6),0,IF(C210&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D210&lt;=0,C210&gt;Parametry!$C$6),0,IF(C210&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F210" s="25">
@@ -11253,7 +11253,7 @@
         <v/>
       </c>
       <c r="G210" s="25">
-        <f>IF(OR(D210&lt;=0,C210&gt;Parametry!$C$6),0,MIN(IF(C210&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D210+F210,2)))</f>
+        <f>IF(OR(D210&lt;=0,C210&gt;Parametry!$C$6),0,MIN(IF(C210&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D210+F210,2)))</f>
         <v/>
       </c>
       <c r="H210" s="18" t="n"/>
@@ -11294,7 +11294,7 @@
         <v/>
       </c>
       <c r="E211" s="17">
-        <f>IF(OR(D211&lt;=0,C211&gt;Parametry!$C$6),0,IF(C211&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D211&lt;=0,C211&gt;Parametry!$C$6),0,IF(C211&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F211" s="16">
@@ -11302,7 +11302,7 @@
         <v/>
       </c>
       <c r="G211" s="16">
-        <f>IF(OR(D211&lt;=0,C211&gt;Parametry!$C$6),0,MIN(IF(C211&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D211+F211,2)))</f>
+        <f>IF(OR(D211&lt;=0,C211&gt;Parametry!$C$6),0,MIN(IF(C211&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D211+F211,2)))</f>
         <v/>
       </c>
       <c r="H211" s="18" t="n"/>
@@ -11343,7 +11343,7 @@
         <v/>
       </c>
       <c r="E212" s="26">
-        <f>IF(OR(D212&lt;=0,C212&gt;Parametry!$C$6),0,IF(C212&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D212&lt;=0,C212&gt;Parametry!$C$6),0,IF(C212&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F212" s="25">
@@ -11351,7 +11351,7 @@
         <v/>
       </c>
       <c r="G212" s="25">
-        <f>IF(OR(D212&lt;=0,C212&gt;Parametry!$C$6),0,MIN(IF(C212&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D212+F212,2)))</f>
+        <f>IF(OR(D212&lt;=0,C212&gt;Parametry!$C$6),0,MIN(IF(C212&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D212+F212,2)))</f>
         <v/>
       </c>
       <c r="H212" s="18" t="n"/>
@@ -11392,7 +11392,7 @@
         <v/>
       </c>
       <c r="E213" s="17">
-        <f>IF(OR(D213&lt;=0,C213&gt;Parametry!$C$6),0,IF(C213&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D213&lt;=0,C213&gt;Parametry!$C$6),0,IF(C213&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F213" s="16">
@@ -11400,7 +11400,7 @@
         <v/>
       </c>
       <c r="G213" s="16">
-        <f>IF(OR(D213&lt;=0,C213&gt;Parametry!$C$6),0,MIN(IF(C213&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D213+F213,2)))</f>
+        <f>IF(OR(D213&lt;=0,C213&gt;Parametry!$C$6),0,MIN(IF(C213&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D213+F213,2)))</f>
         <v/>
       </c>
       <c r="H213" s="18" t="n"/>
@@ -11441,7 +11441,7 @@
         <v/>
       </c>
       <c r="E214" s="26">
-        <f>IF(OR(D214&lt;=0,C214&gt;Parametry!$C$6),0,IF(C214&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D214&lt;=0,C214&gt;Parametry!$C$6),0,IF(C214&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F214" s="25">
@@ -11449,7 +11449,7 @@
         <v/>
       </c>
       <c r="G214" s="25">
-        <f>IF(OR(D214&lt;=0,C214&gt;Parametry!$C$6),0,MIN(IF(C214&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D214+F214,2)))</f>
+        <f>IF(OR(D214&lt;=0,C214&gt;Parametry!$C$6),0,MIN(IF(C214&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D214+F214,2)))</f>
         <v/>
       </c>
       <c r="H214" s="18" t="n"/>
@@ -11490,7 +11490,7 @@
         <v/>
       </c>
       <c r="E215" s="17">
-        <f>IF(OR(D215&lt;=0,C215&gt;Parametry!$C$6),0,IF(C215&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D215&lt;=0,C215&gt;Parametry!$C$6),0,IF(C215&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F215" s="16">
@@ -11498,7 +11498,7 @@
         <v/>
       </c>
       <c r="G215" s="16">
-        <f>IF(OR(D215&lt;=0,C215&gt;Parametry!$C$6),0,MIN(IF(C215&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D215+F215,2)))</f>
+        <f>IF(OR(D215&lt;=0,C215&gt;Parametry!$C$6),0,MIN(IF(C215&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D215+F215,2)))</f>
         <v/>
       </c>
       <c r="H215" s="18" t="n"/>
@@ -11539,7 +11539,7 @@
         <v/>
       </c>
       <c r="E216" s="26">
-        <f>IF(OR(D216&lt;=0,C216&gt;Parametry!$C$6),0,IF(C216&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D216&lt;=0,C216&gt;Parametry!$C$6),0,IF(C216&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F216" s="25">
@@ -11547,7 +11547,7 @@
         <v/>
       </c>
       <c r="G216" s="25">
-        <f>IF(OR(D216&lt;=0,C216&gt;Parametry!$C$6),0,MIN(IF(C216&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D216+F216,2)))</f>
+        <f>IF(OR(D216&lt;=0,C216&gt;Parametry!$C$6),0,MIN(IF(C216&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D216+F216,2)))</f>
         <v/>
       </c>
       <c r="H216" s="18" t="n"/>
@@ -11588,7 +11588,7 @@
         <v/>
       </c>
       <c r="E217" s="17">
-        <f>IF(OR(D217&lt;=0,C217&gt;Parametry!$C$6),0,IF(C217&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D217&lt;=0,C217&gt;Parametry!$C$6),0,IF(C217&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F217" s="16">
@@ -11596,7 +11596,7 @@
         <v/>
       </c>
       <c r="G217" s="16">
-        <f>IF(OR(D217&lt;=0,C217&gt;Parametry!$C$6),0,MIN(IF(C217&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D217+F217,2)))</f>
+        <f>IF(OR(D217&lt;=0,C217&gt;Parametry!$C$6),0,MIN(IF(C217&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D217+F217,2)))</f>
         <v/>
       </c>
       <c r="H217" s="18" t="n"/>
@@ -11637,7 +11637,7 @@
         <v/>
       </c>
       <c r="E218" s="26">
-        <f>IF(OR(D218&lt;=0,C218&gt;Parametry!$C$6),0,IF(C218&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D218&lt;=0,C218&gt;Parametry!$C$6),0,IF(C218&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F218" s="25">
@@ -11645,7 +11645,7 @@
         <v/>
       </c>
       <c r="G218" s="25">
-        <f>IF(OR(D218&lt;=0,C218&gt;Parametry!$C$6),0,MIN(IF(C218&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D218+F218,2)))</f>
+        <f>IF(OR(D218&lt;=0,C218&gt;Parametry!$C$6),0,MIN(IF(C218&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D218+F218,2)))</f>
         <v/>
       </c>
       <c r="H218" s="18" t="n"/>
@@ -11686,7 +11686,7 @@
         <v/>
       </c>
       <c r="E219" s="17">
-        <f>IF(OR(D219&lt;=0,C219&gt;Parametry!$C$6),0,IF(C219&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D219&lt;=0,C219&gt;Parametry!$C$6),0,IF(C219&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F219" s="16">
@@ -11694,7 +11694,7 @@
         <v/>
       </c>
       <c r="G219" s="16">
-        <f>IF(OR(D219&lt;=0,C219&gt;Parametry!$C$6),0,MIN(IF(C219&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D219+F219,2)))</f>
+        <f>IF(OR(D219&lt;=0,C219&gt;Parametry!$C$6),0,MIN(IF(C219&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D219+F219,2)))</f>
         <v/>
       </c>
       <c r="H219" s="18" t="n"/>
@@ -11735,7 +11735,7 @@
         <v/>
       </c>
       <c r="E220" s="26">
-        <f>IF(OR(D220&lt;=0,C220&gt;Parametry!$C$6),0,IF(C220&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D220&lt;=0,C220&gt;Parametry!$C$6),0,IF(C220&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F220" s="25">
@@ -11743,7 +11743,7 @@
         <v/>
       </c>
       <c r="G220" s="25">
-        <f>IF(OR(D220&lt;=0,C220&gt;Parametry!$C$6),0,MIN(IF(C220&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D220+F220,2)))</f>
+        <f>IF(OR(D220&lt;=0,C220&gt;Parametry!$C$6),0,MIN(IF(C220&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D220+F220,2)))</f>
         <v/>
       </c>
       <c r="H220" s="18" t="n"/>
@@ -11784,7 +11784,7 @@
         <v/>
       </c>
       <c r="E221" s="17">
-        <f>IF(OR(D221&lt;=0,C221&gt;Parametry!$C$6),0,IF(C221&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D221&lt;=0,C221&gt;Parametry!$C$6),0,IF(C221&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F221" s="16">
@@ -11792,7 +11792,7 @@
         <v/>
       </c>
       <c r="G221" s="16">
-        <f>IF(OR(D221&lt;=0,C221&gt;Parametry!$C$6),0,MIN(IF(C221&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D221+F221,2)))</f>
+        <f>IF(OR(D221&lt;=0,C221&gt;Parametry!$C$6),0,MIN(IF(C221&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D221+F221,2)))</f>
         <v/>
       </c>
       <c r="H221" s="18" t="n"/>
@@ -11833,7 +11833,7 @@
         <v/>
       </c>
       <c r="E222" s="26">
-        <f>IF(OR(D222&lt;=0,C222&gt;Parametry!$C$6),0,IF(C222&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D222&lt;=0,C222&gt;Parametry!$C$6),0,IF(C222&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F222" s="25">
@@ -11841,7 +11841,7 @@
         <v/>
       </c>
       <c r="G222" s="25">
-        <f>IF(OR(D222&lt;=0,C222&gt;Parametry!$C$6),0,MIN(IF(C222&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D222+F222,2)))</f>
+        <f>IF(OR(D222&lt;=0,C222&gt;Parametry!$C$6),0,MIN(IF(C222&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D222+F222,2)))</f>
         <v/>
       </c>
       <c r="H222" s="18" t="n"/>
@@ -11882,7 +11882,7 @@
         <v/>
       </c>
       <c r="E223" s="17">
-        <f>IF(OR(D223&lt;=0,C223&gt;Parametry!$C$6),0,IF(C223&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D223&lt;=0,C223&gt;Parametry!$C$6),0,IF(C223&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F223" s="16">
@@ -11890,7 +11890,7 @@
         <v/>
       </c>
       <c r="G223" s="16">
-        <f>IF(OR(D223&lt;=0,C223&gt;Parametry!$C$6),0,MIN(IF(C223&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D223+F223,2)))</f>
+        <f>IF(OR(D223&lt;=0,C223&gt;Parametry!$C$6),0,MIN(IF(C223&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D223+F223,2)))</f>
         <v/>
       </c>
       <c r="H223" s="18" t="n"/>
@@ -11931,7 +11931,7 @@
         <v/>
       </c>
       <c r="E224" s="26">
-        <f>IF(OR(D224&lt;=0,C224&gt;Parametry!$C$6),0,IF(C224&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D224&lt;=0,C224&gt;Parametry!$C$6),0,IF(C224&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F224" s="25">
@@ -11939,7 +11939,7 @@
         <v/>
       </c>
       <c r="G224" s="25">
-        <f>IF(OR(D224&lt;=0,C224&gt;Parametry!$C$6),0,MIN(IF(C224&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D224+F224,2)))</f>
+        <f>IF(OR(D224&lt;=0,C224&gt;Parametry!$C$6),0,MIN(IF(C224&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D224+F224,2)))</f>
         <v/>
       </c>
       <c r="H224" s="18" t="n"/>
@@ -11980,7 +11980,7 @@
         <v/>
       </c>
       <c r="E225" s="17">
-        <f>IF(OR(D225&lt;=0,C225&gt;Parametry!$C$6),0,IF(C225&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D225&lt;=0,C225&gt;Parametry!$C$6),0,IF(C225&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F225" s="16">
@@ -11988,7 +11988,7 @@
         <v/>
       </c>
       <c r="G225" s="16">
-        <f>IF(OR(D225&lt;=0,C225&gt;Parametry!$C$6),0,MIN(IF(C225&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D225+F225,2)))</f>
+        <f>IF(OR(D225&lt;=0,C225&gt;Parametry!$C$6),0,MIN(IF(C225&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D225+F225,2)))</f>
         <v/>
       </c>
       <c r="H225" s="18" t="n"/>
@@ -12029,7 +12029,7 @@
         <v/>
       </c>
       <c r="E226" s="26">
-        <f>IF(OR(D226&lt;=0,C226&gt;Parametry!$C$6),0,IF(C226&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D226&lt;=0,C226&gt;Parametry!$C$6),0,IF(C226&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F226" s="25">
@@ -12037,7 +12037,7 @@
         <v/>
       </c>
       <c r="G226" s="25">
-        <f>IF(OR(D226&lt;=0,C226&gt;Parametry!$C$6),0,MIN(IF(C226&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D226+F226,2)))</f>
+        <f>IF(OR(D226&lt;=0,C226&gt;Parametry!$C$6),0,MIN(IF(C226&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D226+F226,2)))</f>
         <v/>
       </c>
       <c r="H226" s="18" t="n"/>
@@ -12078,7 +12078,7 @@
         <v/>
       </c>
       <c r="E227" s="17">
-        <f>IF(OR(D227&lt;=0,C227&gt;Parametry!$C$6),0,IF(C227&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D227&lt;=0,C227&gt;Parametry!$C$6),0,IF(C227&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F227" s="16">
@@ -12086,7 +12086,7 @@
         <v/>
       </c>
       <c r="G227" s="16">
-        <f>IF(OR(D227&lt;=0,C227&gt;Parametry!$C$6),0,MIN(IF(C227&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D227+F227,2)))</f>
+        <f>IF(OR(D227&lt;=0,C227&gt;Parametry!$C$6),0,MIN(IF(C227&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D227+F227,2)))</f>
         <v/>
       </c>
       <c r="H227" s="18" t="n"/>
@@ -12127,7 +12127,7 @@
         <v/>
       </c>
       <c r="E228" s="26">
-        <f>IF(OR(D228&lt;=0,C228&gt;Parametry!$C$6),0,IF(C228&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D228&lt;=0,C228&gt;Parametry!$C$6),0,IF(C228&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F228" s="25">
@@ -12135,7 +12135,7 @@
         <v/>
       </c>
       <c r="G228" s="25">
-        <f>IF(OR(D228&lt;=0,C228&gt;Parametry!$C$6),0,MIN(IF(C228&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D228+F228,2)))</f>
+        <f>IF(OR(D228&lt;=0,C228&gt;Parametry!$C$6),0,MIN(IF(C228&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D228+F228,2)))</f>
         <v/>
       </c>
       <c r="H228" s="18" t="n"/>
@@ -12176,7 +12176,7 @@
         <v/>
       </c>
       <c r="E229" s="17">
-        <f>IF(OR(D229&lt;=0,C229&gt;Parametry!$C$6),0,IF(C229&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D229&lt;=0,C229&gt;Parametry!$C$6),0,IF(C229&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F229" s="16">
@@ -12184,7 +12184,7 @@
         <v/>
       </c>
       <c r="G229" s="16">
-        <f>IF(OR(D229&lt;=0,C229&gt;Parametry!$C$6),0,MIN(IF(C229&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D229+F229,2)))</f>
+        <f>IF(OR(D229&lt;=0,C229&gt;Parametry!$C$6),0,MIN(IF(C229&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D229+F229,2)))</f>
         <v/>
       </c>
       <c r="H229" s="18" t="n"/>
@@ -12225,7 +12225,7 @@
         <v/>
       </c>
       <c r="E230" s="26">
-        <f>IF(OR(D230&lt;=0,C230&gt;Parametry!$C$6),0,IF(C230&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D230&lt;=0,C230&gt;Parametry!$C$6),0,IF(C230&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F230" s="25">
@@ -12233,7 +12233,7 @@
         <v/>
       </c>
       <c r="G230" s="25">
-        <f>IF(OR(D230&lt;=0,C230&gt;Parametry!$C$6),0,MIN(IF(C230&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D230+F230,2)))</f>
+        <f>IF(OR(D230&lt;=0,C230&gt;Parametry!$C$6),0,MIN(IF(C230&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D230+F230,2)))</f>
         <v/>
       </c>
       <c r="H230" s="18" t="n"/>
@@ -12274,7 +12274,7 @@
         <v/>
       </c>
       <c r="E231" s="17">
-        <f>IF(OR(D231&lt;=0,C231&gt;Parametry!$C$6),0,IF(C231&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D231&lt;=0,C231&gt;Parametry!$C$6),0,IF(C231&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F231" s="16">
@@ -12282,7 +12282,7 @@
         <v/>
       </c>
       <c r="G231" s="16">
-        <f>IF(OR(D231&lt;=0,C231&gt;Parametry!$C$6),0,MIN(IF(C231&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D231+F231,2)))</f>
+        <f>IF(OR(D231&lt;=0,C231&gt;Parametry!$C$6),0,MIN(IF(C231&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D231+F231,2)))</f>
         <v/>
       </c>
       <c r="H231" s="18" t="n"/>
@@ -12323,7 +12323,7 @@
         <v/>
       </c>
       <c r="E232" s="26">
-        <f>IF(OR(D232&lt;=0,C232&gt;Parametry!$C$6),0,IF(C232&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D232&lt;=0,C232&gt;Parametry!$C$6),0,IF(C232&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F232" s="25">
@@ -12331,7 +12331,7 @@
         <v/>
       </c>
       <c r="G232" s="25">
-        <f>IF(OR(D232&lt;=0,C232&gt;Parametry!$C$6),0,MIN(IF(C232&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D232+F232,2)))</f>
+        <f>IF(OR(D232&lt;=0,C232&gt;Parametry!$C$6),0,MIN(IF(C232&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D232+F232,2)))</f>
         <v/>
       </c>
       <c r="H232" s="18" t="n"/>
@@ -12372,7 +12372,7 @@
         <v/>
       </c>
       <c r="E233" s="17">
-        <f>IF(OR(D233&lt;=0,C233&gt;Parametry!$C$6),0,IF(C233&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D233&lt;=0,C233&gt;Parametry!$C$6),0,IF(C233&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F233" s="16">
@@ -12380,7 +12380,7 @@
         <v/>
       </c>
       <c r="G233" s="16">
-        <f>IF(OR(D233&lt;=0,C233&gt;Parametry!$C$6),0,MIN(IF(C233&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D233+F233,2)))</f>
+        <f>IF(OR(D233&lt;=0,C233&gt;Parametry!$C$6),0,MIN(IF(C233&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D233+F233,2)))</f>
         <v/>
       </c>
       <c r="H233" s="18" t="n"/>
@@ -12421,7 +12421,7 @@
         <v/>
       </c>
       <c r="E234" s="26">
-        <f>IF(OR(D234&lt;=0,C234&gt;Parametry!$C$6),0,IF(C234&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D234&lt;=0,C234&gt;Parametry!$C$6),0,IF(C234&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F234" s="25">
@@ -12429,7 +12429,7 @@
         <v/>
       </c>
       <c r="G234" s="25">
-        <f>IF(OR(D234&lt;=0,C234&gt;Parametry!$C$6),0,MIN(IF(C234&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D234+F234,2)))</f>
+        <f>IF(OR(D234&lt;=0,C234&gt;Parametry!$C$6),0,MIN(IF(C234&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D234+F234,2)))</f>
         <v/>
       </c>
       <c r="H234" s="18" t="n"/>
@@ -12470,7 +12470,7 @@
         <v/>
       </c>
       <c r="E235" s="17">
-        <f>IF(OR(D235&lt;=0,C235&gt;Parametry!$C$6),0,IF(C235&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D235&lt;=0,C235&gt;Parametry!$C$6),0,IF(C235&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F235" s="16">
@@ -12478,7 +12478,7 @@
         <v/>
       </c>
       <c r="G235" s="16">
-        <f>IF(OR(D235&lt;=0,C235&gt;Parametry!$C$6),0,MIN(IF(C235&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D235+F235,2)))</f>
+        <f>IF(OR(D235&lt;=0,C235&gt;Parametry!$C$6),0,MIN(IF(C235&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D235+F235,2)))</f>
         <v/>
       </c>
       <c r="H235" s="18" t="n"/>
@@ -12519,7 +12519,7 @@
         <v/>
       </c>
       <c r="E236" s="26">
-        <f>IF(OR(D236&lt;=0,C236&gt;Parametry!$C$6),0,IF(C236&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D236&lt;=0,C236&gt;Parametry!$C$6),0,IF(C236&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F236" s="25">
@@ -12527,7 +12527,7 @@
         <v/>
       </c>
       <c r="G236" s="25">
-        <f>IF(OR(D236&lt;=0,C236&gt;Parametry!$C$6),0,MIN(IF(C236&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D236+F236,2)))</f>
+        <f>IF(OR(D236&lt;=0,C236&gt;Parametry!$C$6),0,MIN(IF(C236&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D236+F236,2)))</f>
         <v/>
       </c>
       <c r="H236" s="18" t="n"/>
@@ -12568,7 +12568,7 @@
         <v/>
       </c>
       <c r="E237" s="17">
-        <f>IF(OR(D237&lt;=0,C237&gt;Parametry!$C$6),0,IF(C237&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D237&lt;=0,C237&gt;Parametry!$C$6),0,IF(C237&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F237" s="16">
@@ -12576,7 +12576,7 @@
         <v/>
       </c>
       <c r="G237" s="16">
-        <f>IF(OR(D237&lt;=0,C237&gt;Parametry!$C$6),0,MIN(IF(C237&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D237+F237,2)))</f>
+        <f>IF(OR(D237&lt;=0,C237&gt;Parametry!$C$6),0,MIN(IF(C237&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D237+F237,2)))</f>
         <v/>
       </c>
       <c r="H237" s="18" t="n"/>
@@ -12617,7 +12617,7 @@
         <v/>
       </c>
       <c r="E238" s="26">
-        <f>IF(OR(D238&lt;=0,C238&gt;Parametry!$C$6),0,IF(C238&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D238&lt;=0,C238&gt;Parametry!$C$6),0,IF(C238&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F238" s="25">
@@ -12625,7 +12625,7 @@
         <v/>
       </c>
       <c r="G238" s="25">
-        <f>IF(OR(D238&lt;=0,C238&gt;Parametry!$C$6),0,MIN(IF(C238&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D238+F238,2)))</f>
+        <f>IF(OR(D238&lt;=0,C238&gt;Parametry!$C$6),0,MIN(IF(C238&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D238+F238,2)))</f>
         <v/>
       </c>
       <c r="H238" s="18" t="n"/>
@@ -12666,7 +12666,7 @@
         <v/>
       </c>
       <c r="E239" s="17">
-        <f>IF(OR(D239&lt;=0,C239&gt;Parametry!$C$6),0,IF(C239&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D239&lt;=0,C239&gt;Parametry!$C$6),0,IF(C239&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F239" s="16">
@@ -12674,7 +12674,7 @@
         <v/>
       </c>
       <c r="G239" s="16">
-        <f>IF(OR(D239&lt;=0,C239&gt;Parametry!$C$6),0,MIN(IF(C239&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D239+F239,2)))</f>
+        <f>IF(OR(D239&lt;=0,C239&gt;Parametry!$C$6),0,MIN(IF(C239&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D239+F239,2)))</f>
         <v/>
       </c>
       <c r="H239" s="18" t="n"/>
@@ -12715,7 +12715,7 @@
         <v/>
       </c>
       <c r="E240" s="26">
-        <f>IF(OR(D240&lt;=0,C240&gt;Parametry!$C$6),0,IF(C240&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D240&lt;=0,C240&gt;Parametry!$C$6),0,IF(C240&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F240" s="25">
@@ -12723,7 +12723,7 @@
         <v/>
       </c>
       <c r="G240" s="25">
-        <f>IF(OR(D240&lt;=0,C240&gt;Parametry!$C$6),0,MIN(IF(C240&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D240+F240,2)))</f>
+        <f>IF(OR(D240&lt;=0,C240&gt;Parametry!$C$6),0,MIN(IF(C240&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D240+F240,2)))</f>
         <v/>
       </c>
       <c r="H240" s="18" t="n"/>
@@ -12764,7 +12764,7 @@
         <v/>
       </c>
       <c r="E241" s="17">
-        <f>IF(OR(D241&lt;=0,C241&gt;Parametry!$C$6),0,IF(C241&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D241&lt;=0,C241&gt;Parametry!$C$6),0,IF(C241&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F241" s="16">
@@ -12772,7 +12772,7 @@
         <v/>
       </c>
       <c r="G241" s="16">
-        <f>IF(OR(D241&lt;=0,C241&gt;Parametry!$C$6),0,MIN(IF(C241&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D241+F241,2)))</f>
+        <f>IF(OR(D241&lt;=0,C241&gt;Parametry!$C$6),0,MIN(IF(C241&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D241+F241,2)))</f>
         <v/>
       </c>
       <c r="H241" s="18" t="n"/>
@@ -12813,7 +12813,7 @@
         <v/>
       </c>
       <c r="E242" s="26">
-        <f>IF(OR(D242&lt;=0,C242&gt;Parametry!$C$6),0,IF(C242&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D242&lt;=0,C242&gt;Parametry!$C$6),0,IF(C242&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F242" s="25">
@@ -12821,7 +12821,7 @@
         <v/>
       </c>
       <c r="G242" s="25">
-        <f>IF(OR(D242&lt;=0,C242&gt;Parametry!$C$6),0,MIN(IF(C242&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D242+F242,2)))</f>
+        <f>IF(OR(D242&lt;=0,C242&gt;Parametry!$C$6),0,MIN(IF(C242&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D242+F242,2)))</f>
         <v/>
       </c>
       <c r="H242" s="18" t="n"/>
@@ -12862,7 +12862,7 @@
         <v/>
       </c>
       <c r="E243" s="17">
-        <f>IF(OR(D243&lt;=0,C243&gt;Parametry!$C$6),0,IF(C243&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D243&lt;=0,C243&gt;Parametry!$C$6),0,IF(C243&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F243" s="16">
@@ -12870,7 +12870,7 @@
         <v/>
       </c>
       <c r="G243" s="16">
-        <f>IF(OR(D243&lt;=0,C243&gt;Parametry!$C$6),0,MIN(IF(C243&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D243+F243,2)))</f>
+        <f>IF(OR(D243&lt;=0,C243&gt;Parametry!$C$6),0,MIN(IF(C243&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D243+F243,2)))</f>
         <v/>
       </c>
       <c r="H243" s="18" t="n"/>
@@ -12911,7 +12911,7 @@
         <v/>
       </c>
       <c r="E244" s="26">
-        <f>IF(OR(D244&lt;=0,C244&gt;Parametry!$C$6),0,IF(C244&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D244&lt;=0,C244&gt;Parametry!$C$6),0,IF(C244&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F244" s="25">
@@ -12919,7 +12919,7 @@
         <v/>
       </c>
       <c r="G244" s="25">
-        <f>IF(OR(D244&lt;=0,C244&gt;Parametry!$C$6),0,MIN(IF(C244&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D244+F244,2)))</f>
+        <f>IF(OR(D244&lt;=0,C244&gt;Parametry!$C$6),0,MIN(IF(C244&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D244+F244,2)))</f>
         <v/>
       </c>
       <c r="H244" s="18" t="n"/>
@@ -12960,7 +12960,7 @@
         <v/>
       </c>
       <c r="E245" s="17">
-        <f>IF(OR(D245&lt;=0,C245&gt;Parametry!$C$6),0,IF(C245&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D245&lt;=0,C245&gt;Parametry!$C$6),0,IF(C245&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F245" s="16">
@@ -12968,7 +12968,7 @@
         <v/>
       </c>
       <c r="G245" s="16">
-        <f>IF(OR(D245&lt;=0,C245&gt;Parametry!$C$6),0,MIN(IF(C245&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D245+F245,2)))</f>
+        <f>IF(OR(D245&lt;=0,C245&gt;Parametry!$C$6),0,MIN(IF(C245&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D245+F245,2)))</f>
         <v/>
       </c>
       <c r="H245" s="18" t="n"/>
@@ -13009,7 +13009,7 @@
         <v/>
       </c>
       <c r="E246" s="26">
-        <f>IF(OR(D246&lt;=0,C246&gt;Parametry!$C$6),0,IF(C246&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D246&lt;=0,C246&gt;Parametry!$C$6),0,IF(C246&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F246" s="25">
@@ -13017,7 +13017,7 @@
         <v/>
       </c>
       <c r="G246" s="25">
-        <f>IF(OR(D246&lt;=0,C246&gt;Parametry!$C$6),0,MIN(IF(C246&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D246+F246,2)))</f>
+        <f>IF(OR(D246&lt;=0,C246&gt;Parametry!$C$6),0,MIN(IF(C246&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D246+F246,2)))</f>
         <v/>
       </c>
       <c r="H246" s="18" t="n"/>
@@ -13058,7 +13058,7 @@
         <v/>
       </c>
       <c r="E247" s="17">
-        <f>IF(OR(D247&lt;=0,C247&gt;Parametry!$C$6),0,IF(C247&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D247&lt;=0,C247&gt;Parametry!$C$6),0,IF(C247&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F247" s="16">
@@ -13066,7 +13066,7 @@
         <v/>
       </c>
       <c r="G247" s="16">
-        <f>IF(OR(D247&lt;=0,C247&gt;Parametry!$C$6),0,MIN(IF(C247&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D247+F247,2)))</f>
+        <f>IF(OR(D247&lt;=0,C247&gt;Parametry!$C$6),0,MIN(IF(C247&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D247+F247,2)))</f>
         <v/>
       </c>
       <c r="H247" s="18" t="n"/>
@@ -13107,7 +13107,7 @@
         <v/>
       </c>
       <c r="E248" s="26">
-        <f>IF(OR(D248&lt;=0,C248&gt;Parametry!$C$6),0,IF(C248&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D248&lt;=0,C248&gt;Parametry!$C$6),0,IF(C248&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F248" s="25">
@@ -13115,7 +13115,7 @@
         <v/>
       </c>
       <c r="G248" s="25">
-        <f>IF(OR(D248&lt;=0,C248&gt;Parametry!$C$6),0,MIN(IF(C248&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D248+F248,2)))</f>
+        <f>IF(OR(D248&lt;=0,C248&gt;Parametry!$C$6),0,MIN(IF(C248&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D248+F248,2)))</f>
         <v/>
       </c>
       <c r="H248" s="18" t="n"/>
@@ -13156,7 +13156,7 @@
         <v/>
       </c>
       <c r="E249" s="17">
-        <f>IF(OR(D249&lt;=0,C249&gt;Parametry!$C$6),0,IF(C249&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D249&lt;=0,C249&gt;Parametry!$C$6),0,IF(C249&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F249" s="16">
@@ -13164,7 +13164,7 @@
         <v/>
       </c>
       <c r="G249" s="16">
-        <f>IF(OR(D249&lt;=0,C249&gt;Parametry!$C$6),0,MIN(IF(C249&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D249+F249,2)))</f>
+        <f>IF(OR(D249&lt;=0,C249&gt;Parametry!$C$6),0,MIN(IF(C249&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D249+F249,2)))</f>
         <v/>
       </c>
       <c r="H249" s="18" t="n"/>
@@ -13205,7 +13205,7 @@
         <v/>
       </c>
       <c r="E250" s="26">
-        <f>IF(OR(D250&lt;=0,C250&gt;Parametry!$C$6),0,IF(C250&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D250&lt;=0,C250&gt;Parametry!$C$6),0,IF(C250&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F250" s="25">
@@ -13213,7 +13213,7 @@
         <v/>
       </c>
       <c r="G250" s="25">
-        <f>IF(OR(D250&lt;=0,C250&gt;Parametry!$C$6),0,MIN(IF(C250&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D250+F250,2)))</f>
+        <f>IF(OR(D250&lt;=0,C250&gt;Parametry!$C$6),0,MIN(IF(C250&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D250+F250,2)))</f>
         <v/>
       </c>
       <c r="H250" s="18" t="n"/>
@@ -13254,7 +13254,7 @@
         <v/>
       </c>
       <c r="E251" s="17">
-        <f>IF(OR(D251&lt;=0,C251&gt;Parametry!$C$6),0,IF(C251&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D251&lt;=0,C251&gt;Parametry!$C$6),0,IF(C251&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F251" s="16">
@@ -13262,7 +13262,7 @@
         <v/>
       </c>
       <c r="G251" s="16">
-        <f>IF(OR(D251&lt;=0,C251&gt;Parametry!$C$6),0,MIN(IF(C251&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D251+F251,2)))</f>
+        <f>IF(OR(D251&lt;=0,C251&gt;Parametry!$C$6),0,MIN(IF(C251&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D251+F251,2)))</f>
         <v/>
       </c>
       <c r="H251" s="18" t="n"/>
@@ -13303,7 +13303,7 @@
         <v/>
       </c>
       <c r="E252" s="26">
-        <f>IF(OR(D252&lt;=0,C252&gt;Parametry!$C$6),0,IF(C252&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D252&lt;=0,C252&gt;Parametry!$C$6),0,IF(C252&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F252" s="25">
@@ -13311,7 +13311,7 @@
         <v/>
       </c>
       <c r="G252" s="25">
-        <f>IF(OR(D252&lt;=0,C252&gt;Parametry!$C$6),0,MIN(IF(C252&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D252+F252,2)))</f>
+        <f>IF(OR(D252&lt;=0,C252&gt;Parametry!$C$6),0,MIN(IF(C252&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D252+F252,2)))</f>
         <v/>
       </c>
       <c r="H252" s="18" t="n"/>
@@ -13352,7 +13352,7 @@
         <v/>
       </c>
       <c r="E253" s="17">
-        <f>IF(OR(D253&lt;=0,C253&gt;Parametry!$C$6),0,IF(C253&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D253&lt;=0,C253&gt;Parametry!$C$6),0,IF(C253&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F253" s="16">
@@ -13360,7 +13360,7 @@
         <v/>
       </c>
       <c r="G253" s="16">
-        <f>IF(OR(D253&lt;=0,C253&gt;Parametry!$C$6),0,MIN(IF(C253&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D253+F253,2)))</f>
+        <f>IF(OR(D253&lt;=0,C253&gt;Parametry!$C$6),0,MIN(IF(C253&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D253+F253,2)))</f>
         <v/>
       </c>
       <c r="H253" s="18" t="n"/>
@@ -13401,7 +13401,7 @@
         <v/>
       </c>
       <c r="E254" s="26">
-        <f>IF(OR(D254&lt;=0,C254&gt;Parametry!$C$6),0,IF(C254&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D254&lt;=0,C254&gt;Parametry!$C$6),0,IF(C254&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F254" s="25">
@@ -13409,7 +13409,7 @@
         <v/>
       </c>
       <c r="G254" s="25">
-        <f>IF(OR(D254&lt;=0,C254&gt;Parametry!$C$6),0,MIN(IF(C254&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D254+F254,2)))</f>
+        <f>IF(OR(D254&lt;=0,C254&gt;Parametry!$C$6),0,MIN(IF(C254&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D254+F254,2)))</f>
         <v/>
       </c>
       <c r="H254" s="18" t="n"/>
@@ -13450,7 +13450,7 @@
         <v/>
       </c>
       <c r="E255" s="17">
-        <f>IF(OR(D255&lt;=0,C255&gt;Parametry!$C$6),0,IF(C255&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D255&lt;=0,C255&gt;Parametry!$C$6),0,IF(C255&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F255" s="16">
@@ -13458,7 +13458,7 @@
         <v/>
       </c>
       <c r="G255" s="16">
-        <f>IF(OR(D255&lt;=0,C255&gt;Parametry!$C$6),0,MIN(IF(C255&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D255+F255,2)))</f>
+        <f>IF(OR(D255&lt;=0,C255&gt;Parametry!$C$6),0,MIN(IF(C255&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D255+F255,2)))</f>
         <v/>
       </c>
       <c r="H255" s="18" t="n"/>
@@ -13499,7 +13499,7 @@
         <v/>
       </c>
       <c r="E256" s="26">
-        <f>IF(OR(D256&lt;=0,C256&gt;Parametry!$C$6),0,IF(C256&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D256&lt;=0,C256&gt;Parametry!$C$6),0,IF(C256&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F256" s="25">
@@ -13507,7 +13507,7 @@
         <v/>
       </c>
       <c r="G256" s="25">
-        <f>IF(OR(D256&lt;=0,C256&gt;Parametry!$C$6),0,MIN(IF(C256&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D256+F256,2)))</f>
+        <f>IF(OR(D256&lt;=0,C256&gt;Parametry!$C$6),0,MIN(IF(C256&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D256+F256,2)))</f>
         <v/>
       </c>
       <c r="H256" s="18" t="n"/>
@@ -13548,7 +13548,7 @@
         <v/>
       </c>
       <c r="E257" s="17">
-        <f>IF(OR(D257&lt;=0,C257&gt;Parametry!$C$6),0,IF(C257&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D257&lt;=0,C257&gt;Parametry!$C$6),0,IF(C257&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F257" s="16">
@@ -13556,7 +13556,7 @@
         <v/>
       </c>
       <c r="G257" s="16">
-        <f>IF(OR(D257&lt;=0,C257&gt;Parametry!$C$6),0,MIN(IF(C257&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D257+F257,2)))</f>
+        <f>IF(OR(D257&lt;=0,C257&gt;Parametry!$C$6),0,MIN(IF(C257&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D257+F257,2)))</f>
         <v/>
       </c>
       <c r="H257" s="18" t="n"/>
@@ -13597,7 +13597,7 @@
         <v/>
       </c>
       <c r="E258" s="26">
-        <f>IF(OR(D258&lt;=0,C258&gt;Parametry!$C$6),0,IF(C258&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D258&lt;=0,C258&gt;Parametry!$C$6),0,IF(C258&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F258" s="25">
@@ -13605,7 +13605,7 @@
         <v/>
       </c>
       <c r="G258" s="25">
-        <f>IF(OR(D258&lt;=0,C258&gt;Parametry!$C$6),0,MIN(IF(C258&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D258+F258,2)))</f>
+        <f>IF(OR(D258&lt;=0,C258&gt;Parametry!$C$6),0,MIN(IF(C258&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D258+F258,2)))</f>
         <v/>
       </c>
       <c r="H258" s="18" t="n"/>
@@ -13646,7 +13646,7 @@
         <v/>
       </c>
       <c r="E259" s="17">
-        <f>IF(OR(D259&lt;=0,C259&gt;Parametry!$C$6),0,IF(C259&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D259&lt;=0,C259&gt;Parametry!$C$6),0,IF(C259&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F259" s="16">
@@ -13654,7 +13654,7 @@
         <v/>
       </c>
       <c r="G259" s="16">
-        <f>IF(OR(D259&lt;=0,C259&gt;Parametry!$C$6),0,MIN(IF(C259&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D259+F259,2)))</f>
+        <f>IF(OR(D259&lt;=0,C259&gt;Parametry!$C$6),0,MIN(IF(C259&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D259+F259,2)))</f>
         <v/>
       </c>
       <c r="H259" s="18" t="n"/>
@@ -13695,7 +13695,7 @@
         <v/>
       </c>
       <c r="E260" s="26">
-        <f>IF(OR(D260&lt;=0,C260&gt;Parametry!$C$6),0,IF(C260&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D260&lt;=0,C260&gt;Parametry!$C$6),0,IF(C260&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F260" s="25">
@@ -13703,7 +13703,7 @@
         <v/>
       </c>
       <c r="G260" s="25">
-        <f>IF(OR(D260&lt;=0,C260&gt;Parametry!$C$6),0,MIN(IF(C260&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D260+F260,2)))</f>
+        <f>IF(OR(D260&lt;=0,C260&gt;Parametry!$C$6),0,MIN(IF(C260&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D260+F260,2)))</f>
         <v/>
       </c>
       <c r="H260" s="18" t="n"/>
@@ -13744,7 +13744,7 @@
         <v/>
       </c>
       <c r="E261" s="17">
-        <f>IF(OR(D261&lt;=0,C261&gt;Parametry!$C$6),0,IF(C261&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D261&lt;=0,C261&gt;Parametry!$C$6),0,IF(C261&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F261" s="16">
@@ -13752,7 +13752,7 @@
         <v/>
       </c>
       <c r="G261" s="16">
-        <f>IF(OR(D261&lt;=0,C261&gt;Parametry!$C$6),0,MIN(IF(C261&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D261+F261,2)))</f>
+        <f>IF(OR(D261&lt;=0,C261&gt;Parametry!$C$6),0,MIN(IF(C261&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D261+F261,2)))</f>
         <v/>
       </c>
       <c r="H261" s="18" t="n"/>
@@ -13793,7 +13793,7 @@
         <v/>
       </c>
       <c r="E262" s="26">
-        <f>IF(OR(D262&lt;=0,C262&gt;Parametry!$C$6),0,IF(C262&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D262&lt;=0,C262&gt;Parametry!$C$6),0,IF(C262&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F262" s="25">
@@ -13801,7 +13801,7 @@
         <v/>
       </c>
       <c r="G262" s="25">
-        <f>IF(OR(D262&lt;=0,C262&gt;Parametry!$C$6),0,MIN(IF(C262&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D262+F262,2)))</f>
+        <f>IF(OR(D262&lt;=0,C262&gt;Parametry!$C$6),0,MIN(IF(C262&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D262+F262,2)))</f>
         <v/>
       </c>
       <c r="H262" s="18" t="n"/>
@@ -13842,7 +13842,7 @@
         <v/>
       </c>
       <c r="E263" s="17">
-        <f>IF(OR(D263&lt;=0,C263&gt;Parametry!$C$6),0,IF(C263&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D263&lt;=0,C263&gt;Parametry!$C$6),0,IF(C263&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F263" s="16">
@@ -13850,7 +13850,7 @@
         <v/>
       </c>
       <c r="G263" s="16">
-        <f>IF(OR(D263&lt;=0,C263&gt;Parametry!$C$6),0,MIN(IF(C263&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D263+F263,2)))</f>
+        <f>IF(OR(D263&lt;=0,C263&gt;Parametry!$C$6),0,MIN(IF(C263&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D263+F263,2)))</f>
         <v/>
       </c>
       <c r="H263" s="18" t="n"/>
@@ -13891,7 +13891,7 @@
         <v/>
       </c>
       <c r="E264" s="26">
-        <f>IF(OR(D264&lt;=0,C264&gt;Parametry!$C$6),0,IF(C264&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D264&lt;=0,C264&gt;Parametry!$C$6),0,IF(C264&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F264" s="25">
@@ -13899,7 +13899,7 @@
         <v/>
       </c>
       <c r="G264" s="25">
-        <f>IF(OR(D264&lt;=0,C264&gt;Parametry!$C$6),0,MIN(IF(C264&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D264+F264,2)))</f>
+        <f>IF(OR(D264&lt;=0,C264&gt;Parametry!$C$6),0,MIN(IF(C264&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D264+F264,2)))</f>
         <v/>
       </c>
       <c r="H264" s="18" t="n"/>
@@ -13940,7 +13940,7 @@
         <v/>
       </c>
       <c r="E265" s="17">
-        <f>IF(OR(D265&lt;=0,C265&gt;Parametry!$C$6),0,IF(C265&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D265&lt;=0,C265&gt;Parametry!$C$6),0,IF(C265&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F265" s="16">
@@ -13948,7 +13948,7 @@
         <v/>
       </c>
       <c r="G265" s="16">
-        <f>IF(OR(D265&lt;=0,C265&gt;Parametry!$C$6),0,MIN(IF(C265&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D265+F265,2)))</f>
+        <f>IF(OR(D265&lt;=0,C265&gt;Parametry!$C$6),0,MIN(IF(C265&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D265+F265,2)))</f>
         <v/>
       </c>
       <c r="H265" s="18" t="n"/>
@@ -13989,7 +13989,7 @@
         <v/>
       </c>
       <c r="E266" s="26">
-        <f>IF(OR(D266&lt;=0,C266&gt;Parametry!$C$6),0,IF(C266&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D266&lt;=0,C266&gt;Parametry!$C$6),0,IF(C266&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F266" s="25">
@@ -13997,7 +13997,7 @@
         <v/>
       </c>
       <c r="G266" s="25">
-        <f>IF(OR(D266&lt;=0,C266&gt;Parametry!$C$6),0,MIN(IF(C266&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D266+F266,2)))</f>
+        <f>IF(OR(D266&lt;=0,C266&gt;Parametry!$C$6),0,MIN(IF(C266&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D266+F266,2)))</f>
         <v/>
       </c>
       <c r="H266" s="18" t="n"/>
@@ -14038,7 +14038,7 @@
         <v/>
       </c>
       <c r="E267" s="17">
-        <f>IF(OR(D267&lt;=0,C267&gt;Parametry!$C$6),0,IF(C267&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D267&lt;=0,C267&gt;Parametry!$C$6),0,IF(C267&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F267" s="16">
@@ -14046,7 +14046,7 @@
         <v/>
       </c>
       <c r="G267" s="16">
-        <f>IF(OR(D267&lt;=0,C267&gt;Parametry!$C$6),0,MIN(IF(C267&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D267+F267,2)))</f>
+        <f>IF(OR(D267&lt;=0,C267&gt;Parametry!$C$6),0,MIN(IF(C267&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D267+F267,2)))</f>
         <v/>
       </c>
       <c r="H267" s="18" t="n"/>
@@ -14087,7 +14087,7 @@
         <v/>
       </c>
       <c r="E268" s="26">
-        <f>IF(OR(D268&lt;=0,C268&gt;Parametry!$C$6),0,IF(C268&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D268&lt;=0,C268&gt;Parametry!$C$6),0,IF(C268&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F268" s="25">
@@ -14095,7 +14095,7 @@
         <v/>
       </c>
       <c r="G268" s="25">
-        <f>IF(OR(D268&lt;=0,C268&gt;Parametry!$C$6),0,MIN(IF(C268&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D268+F268,2)))</f>
+        <f>IF(OR(D268&lt;=0,C268&gt;Parametry!$C$6),0,MIN(IF(C268&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D268+F268,2)))</f>
         <v/>
       </c>
       <c r="H268" s="18" t="n"/>
@@ -14136,7 +14136,7 @@
         <v/>
       </c>
       <c r="E269" s="17">
-        <f>IF(OR(D269&lt;=0,C269&gt;Parametry!$C$6),0,IF(C269&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D269&lt;=0,C269&gt;Parametry!$C$6),0,IF(C269&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F269" s="16">
@@ -14144,7 +14144,7 @@
         <v/>
       </c>
       <c r="G269" s="16">
-        <f>IF(OR(D269&lt;=0,C269&gt;Parametry!$C$6),0,MIN(IF(C269&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D269+F269,2)))</f>
+        <f>IF(OR(D269&lt;=0,C269&gt;Parametry!$C$6),0,MIN(IF(C269&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D269+F269,2)))</f>
         <v/>
       </c>
       <c r="H269" s="18" t="n"/>
@@ -14185,7 +14185,7 @@
         <v/>
       </c>
       <c r="E270" s="26">
-        <f>IF(OR(D270&lt;=0,C270&gt;Parametry!$C$6),0,IF(C270&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D270&lt;=0,C270&gt;Parametry!$C$6),0,IF(C270&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F270" s="25">
@@ -14193,7 +14193,7 @@
         <v/>
       </c>
       <c r="G270" s="25">
-        <f>IF(OR(D270&lt;=0,C270&gt;Parametry!$C$6),0,MIN(IF(C270&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D270+F270,2)))</f>
+        <f>IF(OR(D270&lt;=0,C270&gt;Parametry!$C$6),0,MIN(IF(C270&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D270+F270,2)))</f>
         <v/>
       </c>
       <c r="H270" s="18" t="n"/>
@@ -14234,7 +14234,7 @@
         <v/>
       </c>
       <c r="E271" s="17">
-        <f>IF(OR(D271&lt;=0,C271&gt;Parametry!$C$6),0,IF(C271&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D271&lt;=0,C271&gt;Parametry!$C$6),0,IF(C271&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F271" s="16">
@@ -14242,7 +14242,7 @@
         <v/>
       </c>
       <c r="G271" s="16">
-        <f>IF(OR(D271&lt;=0,C271&gt;Parametry!$C$6),0,MIN(IF(C271&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D271+F271,2)))</f>
+        <f>IF(OR(D271&lt;=0,C271&gt;Parametry!$C$6),0,MIN(IF(C271&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D271+F271,2)))</f>
         <v/>
       </c>
       <c r="H271" s="18" t="n"/>
@@ -14283,7 +14283,7 @@
         <v/>
       </c>
       <c r="E272" s="26">
-        <f>IF(OR(D272&lt;=0,C272&gt;Parametry!$C$6),0,IF(C272&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D272&lt;=0,C272&gt;Parametry!$C$6),0,IF(C272&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F272" s="25">
@@ -14291,7 +14291,7 @@
         <v/>
       </c>
       <c r="G272" s="25">
-        <f>IF(OR(D272&lt;=0,C272&gt;Parametry!$C$6),0,MIN(IF(C272&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D272+F272,2)))</f>
+        <f>IF(OR(D272&lt;=0,C272&gt;Parametry!$C$6),0,MIN(IF(C272&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D272+F272,2)))</f>
         <v/>
       </c>
       <c r="H272" s="18" t="n"/>
@@ -14332,7 +14332,7 @@
         <v/>
       </c>
       <c r="E273" s="17">
-        <f>IF(OR(D273&lt;=0,C273&gt;Parametry!$C$6),0,IF(C273&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D273&lt;=0,C273&gt;Parametry!$C$6),0,IF(C273&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F273" s="16">
@@ -14340,7 +14340,7 @@
         <v/>
       </c>
       <c r="G273" s="16">
-        <f>IF(OR(D273&lt;=0,C273&gt;Parametry!$C$6),0,MIN(IF(C273&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D273+F273,2)))</f>
+        <f>IF(OR(D273&lt;=0,C273&gt;Parametry!$C$6),0,MIN(IF(C273&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D273+F273,2)))</f>
         <v/>
       </c>
       <c r="H273" s="18" t="n"/>
@@ -14381,7 +14381,7 @@
         <v/>
       </c>
       <c r="E274" s="26">
-        <f>IF(OR(D274&lt;=0,C274&gt;Parametry!$C$6),0,IF(C274&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D274&lt;=0,C274&gt;Parametry!$C$6),0,IF(C274&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F274" s="25">
@@ -14389,7 +14389,7 @@
         <v/>
       </c>
       <c r="G274" s="25">
-        <f>IF(OR(D274&lt;=0,C274&gt;Parametry!$C$6),0,MIN(IF(C274&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D274+F274,2)))</f>
+        <f>IF(OR(D274&lt;=0,C274&gt;Parametry!$C$6),0,MIN(IF(C274&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D274+F274,2)))</f>
         <v/>
       </c>
       <c r="H274" s="18" t="n"/>
@@ -14430,7 +14430,7 @@
         <v/>
       </c>
       <c r="E275" s="17">
-        <f>IF(OR(D275&lt;=0,C275&gt;Parametry!$C$6),0,IF(C275&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D275&lt;=0,C275&gt;Parametry!$C$6),0,IF(C275&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F275" s="16">
@@ -14438,7 +14438,7 @@
         <v/>
       </c>
       <c r="G275" s="16">
-        <f>IF(OR(D275&lt;=0,C275&gt;Parametry!$C$6),0,MIN(IF(C275&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D275+F275,2)))</f>
+        <f>IF(OR(D275&lt;=0,C275&gt;Parametry!$C$6),0,MIN(IF(C275&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D275+F275,2)))</f>
         <v/>
       </c>
       <c r="H275" s="18" t="n"/>
@@ -14479,7 +14479,7 @@
         <v/>
       </c>
       <c r="E276" s="26">
-        <f>IF(OR(D276&lt;=0,C276&gt;Parametry!$C$6),0,IF(C276&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D276&lt;=0,C276&gt;Parametry!$C$6),0,IF(C276&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F276" s="25">
@@ -14487,7 +14487,7 @@
         <v/>
       </c>
       <c r="G276" s="25">
-        <f>IF(OR(D276&lt;=0,C276&gt;Parametry!$C$6),0,MIN(IF(C276&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D276+F276,2)))</f>
+        <f>IF(OR(D276&lt;=0,C276&gt;Parametry!$C$6),0,MIN(IF(C276&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D276+F276,2)))</f>
         <v/>
       </c>
       <c r="H276" s="18" t="n"/>
@@ -14528,7 +14528,7 @@
         <v/>
       </c>
       <c r="E277" s="17">
-        <f>IF(OR(D277&lt;=0,C277&gt;Parametry!$C$6),0,IF(C277&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D277&lt;=0,C277&gt;Parametry!$C$6),0,IF(C277&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F277" s="16">
@@ -14536,7 +14536,7 @@
         <v/>
       </c>
       <c r="G277" s="16">
-        <f>IF(OR(D277&lt;=0,C277&gt;Parametry!$C$6),0,MIN(IF(C277&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D277+F277,2)))</f>
+        <f>IF(OR(D277&lt;=0,C277&gt;Parametry!$C$6),0,MIN(IF(C277&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D277+F277,2)))</f>
         <v/>
       </c>
       <c r="H277" s="18" t="n"/>
@@ -14577,7 +14577,7 @@
         <v/>
       </c>
       <c r="E278" s="26">
-        <f>IF(OR(D278&lt;=0,C278&gt;Parametry!$C$6),0,IF(C278&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D278&lt;=0,C278&gt;Parametry!$C$6),0,IF(C278&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F278" s="25">
@@ -14585,7 +14585,7 @@
         <v/>
       </c>
       <c r="G278" s="25">
-        <f>IF(OR(D278&lt;=0,C278&gt;Parametry!$C$6),0,MIN(IF(C278&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D278+F278,2)))</f>
+        <f>IF(OR(D278&lt;=0,C278&gt;Parametry!$C$6),0,MIN(IF(C278&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D278+F278,2)))</f>
         <v/>
       </c>
       <c r="H278" s="18" t="n"/>
@@ -14626,7 +14626,7 @@
         <v/>
       </c>
       <c r="E279" s="17">
-        <f>IF(OR(D279&lt;=0,C279&gt;Parametry!$C$6),0,IF(C279&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D279&lt;=0,C279&gt;Parametry!$C$6),0,IF(C279&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F279" s="16">
@@ -14634,7 +14634,7 @@
         <v/>
       </c>
       <c r="G279" s="16">
-        <f>IF(OR(D279&lt;=0,C279&gt;Parametry!$C$6),0,MIN(IF(C279&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D279+F279,2)))</f>
+        <f>IF(OR(D279&lt;=0,C279&gt;Parametry!$C$6),0,MIN(IF(C279&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D279+F279,2)))</f>
         <v/>
       </c>
       <c r="H279" s="18" t="n"/>
@@ -14675,7 +14675,7 @@
         <v/>
       </c>
       <c r="E280" s="26">
-        <f>IF(OR(D280&lt;=0,C280&gt;Parametry!$C$6),0,IF(C280&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D280&lt;=0,C280&gt;Parametry!$C$6),0,IF(C280&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F280" s="25">
@@ -14683,7 +14683,7 @@
         <v/>
       </c>
       <c r="G280" s="25">
-        <f>IF(OR(D280&lt;=0,C280&gt;Parametry!$C$6),0,MIN(IF(C280&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D280+F280,2)))</f>
+        <f>IF(OR(D280&lt;=0,C280&gt;Parametry!$C$6),0,MIN(IF(C280&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D280+F280,2)))</f>
         <v/>
       </c>
       <c r="H280" s="18" t="n"/>
@@ -14724,7 +14724,7 @@
         <v/>
       </c>
       <c r="E281" s="17">
-        <f>IF(OR(D281&lt;=0,C281&gt;Parametry!$C$6),0,IF(C281&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D281&lt;=0,C281&gt;Parametry!$C$6),0,IF(C281&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F281" s="16">
@@ -14732,7 +14732,7 @@
         <v/>
       </c>
       <c r="G281" s="16">
-        <f>IF(OR(D281&lt;=0,C281&gt;Parametry!$C$6),0,MIN(IF(C281&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D281+F281,2)))</f>
+        <f>IF(OR(D281&lt;=0,C281&gt;Parametry!$C$6),0,MIN(IF(C281&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D281+F281,2)))</f>
         <v/>
       </c>
       <c r="H281" s="18" t="n"/>
@@ -14773,7 +14773,7 @@
         <v/>
       </c>
       <c r="E282" s="26">
-        <f>IF(OR(D282&lt;=0,C282&gt;Parametry!$C$6),0,IF(C282&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D282&lt;=0,C282&gt;Parametry!$C$6),0,IF(C282&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F282" s="25">
@@ -14781,7 +14781,7 @@
         <v/>
       </c>
       <c r="G282" s="25">
-        <f>IF(OR(D282&lt;=0,C282&gt;Parametry!$C$6),0,MIN(IF(C282&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D282+F282,2)))</f>
+        <f>IF(OR(D282&lt;=0,C282&gt;Parametry!$C$6),0,MIN(IF(C282&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D282+F282,2)))</f>
         <v/>
       </c>
       <c r="H282" s="18" t="n"/>
@@ -14822,7 +14822,7 @@
         <v/>
       </c>
       <c r="E283" s="17">
-        <f>IF(OR(D283&lt;=0,C283&gt;Parametry!$C$6),0,IF(C283&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D283&lt;=0,C283&gt;Parametry!$C$6),0,IF(C283&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F283" s="16">
@@ -14830,7 +14830,7 @@
         <v/>
       </c>
       <c r="G283" s="16">
-        <f>IF(OR(D283&lt;=0,C283&gt;Parametry!$C$6),0,MIN(IF(C283&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D283+F283,2)))</f>
+        <f>IF(OR(D283&lt;=0,C283&gt;Parametry!$C$6),0,MIN(IF(C283&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D283+F283,2)))</f>
         <v/>
       </c>
       <c r="H283" s="18" t="n"/>
@@ -14871,7 +14871,7 @@
         <v/>
       </c>
       <c r="E284" s="26">
-        <f>IF(OR(D284&lt;=0,C284&gt;Parametry!$C$6),0,IF(C284&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D284&lt;=0,C284&gt;Parametry!$C$6),0,IF(C284&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F284" s="25">
@@ -14879,7 +14879,7 @@
         <v/>
       </c>
       <c r="G284" s="25">
-        <f>IF(OR(D284&lt;=0,C284&gt;Parametry!$C$6),0,MIN(IF(C284&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D284+F284,2)))</f>
+        <f>IF(OR(D284&lt;=0,C284&gt;Parametry!$C$6),0,MIN(IF(C284&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D284+F284,2)))</f>
         <v/>
       </c>
       <c r="H284" s="18" t="n"/>
@@ -14920,7 +14920,7 @@
         <v/>
       </c>
       <c r="E285" s="17">
-        <f>IF(OR(D285&lt;=0,C285&gt;Parametry!$C$6),0,IF(C285&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D285&lt;=0,C285&gt;Parametry!$C$6),0,IF(C285&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F285" s="16">
@@ -14928,7 +14928,7 @@
         <v/>
       </c>
       <c r="G285" s="16">
-        <f>IF(OR(D285&lt;=0,C285&gt;Parametry!$C$6),0,MIN(IF(C285&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D285+F285,2)))</f>
+        <f>IF(OR(D285&lt;=0,C285&gt;Parametry!$C$6),0,MIN(IF(C285&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D285+F285,2)))</f>
         <v/>
       </c>
       <c r="H285" s="18" t="n"/>
@@ -14969,7 +14969,7 @@
         <v/>
       </c>
       <c r="E286" s="26">
-        <f>IF(OR(D286&lt;=0,C286&gt;Parametry!$C$6),0,IF(C286&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D286&lt;=0,C286&gt;Parametry!$C$6),0,IF(C286&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F286" s="25">
@@ -14977,7 +14977,7 @@
         <v/>
       </c>
       <c r="G286" s="25">
-        <f>IF(OR(D286&lt;=0,C286&gt;Parametry!$C$6),0,MIN(IF(C286&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D286+F286,2)))</f>
+        <f>IF(OR(D286&lt;=0,C286&gt;Parametry!$C$6),0,MIN(IF(C286&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D286+F286,2)))</f>
         <v/>
       </c>
       <c r="H286" s="18" t="n"/>
@@ -15018,7 +15018,7 @@
         <v/>
       </c>
       <c r="E287" s="17">
-        <f>IF(OR(D287&lt;=0,C287&gt;Parametry!$C$6),0,IF(C287&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D287&lt;=0,C287&gt;Parametry!$C$6),0,IF(C287&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F287" s="16">
@@ -15026,7 +15026,7 @@
         <v/>
       </c>
       <c r="G287" s="16">
-        <f>IF(OR(D287&lt;=0,C287&gt;Parametry!$C$6),0,MIN(IF(C287&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D287+F287,2)))</f>
+        <f>IF(OR(D287&lt;=0,C287&gt;Parametry!$C$6),0,MIN(IF(C287&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D287+F287,2)))</f>
         <v/>
       </c>
       <c r="H287" s="18" t="n"/>
@@ -15067,7 +15067,7 @@
         <v/>
       </c>
       <c r="E288" s="26">
-        <f>IF(OR(D288&lt;=0,C288&gt;Parametry!$C$6),0,IF(C288&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D288&lt;=0,C288&gt;Parametry!$C$6),0,IF(C288&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F288" s="25">
@@ -15075,7 +15075,7 @@
         <v/>
       </c>
       <c r="G288" s="25">
-        <f>IF(OR(D288&lt;=0,C288&gt;Parametry!$C$6),0,MIN(IF(C288&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D288+F288,2)))</f>
+        <f>IF(OR(D288&lt;=0,C288&gt;Parametry!$C$6),0,MIN(IF(C288&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D288+F288,2)))</f>
         <v/>
       </c>
       <c r="H288" s="18" t="n"/>
@@ -15116,7 +15116,7 @@
         <v/>
       </c>
       <c r="E289" s="17">
-        <f>IF(OR(D289&lt;=0,C289&gt;Parametry!$C$6),0,IF(C289&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D289&lt;=0,C289&gt;Parametry!$C$6),0,IF(C289&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F289" s="16">
@@ -15124,7 +15124,7 @@
         <v/>
       </c>
       <c r="G289" s="16">
-        <f>IF(OR(D289&lt;=0,C289&gt;Parametry!$C$6),0,MIN(IF(C289&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D289+F289,2)))</f>
+        <f>IF(OR(D289&lt;=0,C289&gt;Parametry!$C$6),0,MIN(IF(C289&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D289+F289,2)))</f>
         <v/>
       </c>
       <c r="H289" s="18" t="n"/>
@@ -15165,7 +15165,7 @@
         <v/>
       </c>
       <c r="E290" s="26">
-        <f>IF(OR(D290&lt;=0,C290&gt;Parametry!$C$6),0,IF(C290&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D290&lt;=0,C290&gt;Parametry!$C$6),0,IF(C290&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F290" s="25">
@@ -15173,7 +15173,7 @@
         <v/>
       </c>
       <c r="G290" s="25">
-        <f>IF(OR(D290&lt;=0,C290&gt;Parametry!$C$6),0,MIN(IF(C290&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D290+F290,2)))</f>
+        <f>IF(OR(D290&lt;=0,C290&gt;Parametry!$C$6),0,MIN(IF(C290&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D290+F290,2)))</f>
         <v/>
       </c>
       <c r="H290" s="18" t="n"/>
@@ -15214,7 +15214,7 @@
         <v/>
       </c>
       <c r="E291" s="17">
-        <f>IF(OR(D291&lt;=0,C291&gt;Parametry!$C$6),0,IF(C291&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D291&lt;=0,C291&gt;Parametry!$C$6),0,IF(C291&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F291" s="16">
@@ -15222,7 +15222,7 @@
         <v/>
       </c>
       <c r="G291" s="16">
-        <f>IF(OR(D291&lt;=0,C291&gt;Parametry!$C$6),0,MIN(IF(C291&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D291+F291,2)))</f>
+        <f>IF(OR(D291&lt;=0,C291&gt;Parametry!$C$6),0,MIN(IF(C291&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D291+F291,2)))</f>
         <v/>
       </c>
       <c r="H291" s="18" t="n"/>
@@ -15263,7 +15263,7 @@
         <v/>
       </c>
       <c r="E292" s="26">
-        <f>IF(OR(D292&lt;=0,C292&gt;Parametry!$C$6),0,IF(C292&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D292&lt;=0,C292&gt;Parametry!$C$6),0,IF(C292&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F292" s="25">
@@ -15271,7 +15271,7 @@
         <v/>
       </c>
       <c r="G292" s="25">
-        <f>IF(OR(D292&lt;=0,C292&gt;Parametry!$C$6),0,MIN(IF(C292&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D292+F292,2)))</f>
+        <f>IF(OR(D292&lt;=0,C292&gt;Parametry!$C$6),0,MIN(IF(C292&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D292+F292,2)))</f>
         <v/>
       </c>
       <c r="H292" s="18" t="n"/>
@@ -15312,7 +15312,7 @@
         <v/>
       </c>
       <c r="E293" s="17">
-        <f>IF(OR(D293&lt;=0,C293&gt;Parametry!$C$6),0,IF(C293&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D293&lt;=0,C293&gt;Parametry!$C$6),0,IF(C293&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F293" s="16">
@@ -15320,7 +15320,7 @@
         <v/>
       </c>
       <c r="G293" s="16">
-        <f>IF(OR(D293&lt;=0,C293&gt;Parametry!$C$6),0,MIN(IF(C293&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D293+F293,2)))</f>
+        <f>IF(OR(D293&lt;=0,C293&gt;Parametry!$C$6),0,MIN(IF(C293&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D293+F293,2)))</f>
         <v/>
       </c>
       <c r="H293" s="18" t="n"/>
@@ -15361,7 +15361,7 @@
         <v/>
       </c>
       <c r="E294" s="26">
-        <f>IF(OR(D294&lt;=0,C294&gt;Parametry!$C$6),0,IF(C294&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D294&lt;=0,C294&gt;Parametry!$C$6),0,IF(C294&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F294" s="25">
@@ -15369,7 +15369,7 @@
         <v/>
       </c>
       <c r="G294" s="25">
-        <f>IF(OR(D294&lt;=0,C294&gt;Parametry!$C$6),0,MIN(IF(C294&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D294+F294,2)))</f>
+        <f>IF(OR(D294&lt;=0,C294&gt;Parametry!$C$6),0,MIN(IF(C294&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D294+F294,2)))</f>
         <v/>
       </c>
       <c r="H294" s="18" t="n"/>
@@ -15410,7 +15410,7 @@
         <v/>
       </c>
       <c r="E295" s="17">
-        <f>IF(OR(D295&lt;=0,C295&gt;Parametry!$C$6),0,IF(C295&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D295&lt;=0,C295&gt;Parametry!$C$6),0,IF(C295&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F295" s="16">
@@ -15418,7 +15418,7 @@
         <v/>
       </c>
       <c r="G295" s="16">
-        <f>IF(OR(D295&lt;=0,C295&gt;Parametry!$C$6),0,MIN(IF(C295&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D295+F295,2)))</f>
+        <f>IF(OR(D295&lt;=0,C295&gt;Parametry!$C$6),0,MIN(IF(C295&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D295+F295,2)))</f>
         <v/>
       </c>
       <c r="H295" s="18" t="n"/>
@@ -15459,7 +15459,7 @@
         <v/>
       </c>
       <c r="E296" s="26">
-        <f>IF(OR(D296&lt;=0,C296&gt;Parametry!$C$6),0,IF(C296&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D296&lt;=0,C296&gt;Parametry!$C$6),0,IF(C296&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F296" s="25">
@@ -15467,7 +15467,7 @@
         <v/>
       </c>
       <c r="G296" s="25">
-        <f>IF(OR(D296&lt;=0,C296&gt;Parametry!$C$6),0,MIN(IF(C296&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D296+F296,2)))</f>
+        <f>IF(OR(D296&lt;=0,C296&gt;Parametry!$C$6),0,MIN(IF(C296&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D296+F296,2)))</f>
         <v/>
       </c>
       <c r="H296" s="18" t="n"/>
@@ -15508,7 +15508,7 @@
         <v/>
       </c>
       <c r="E297" s="17">
-        <f>IF(OR(D297&lt;=0,C297&gt;Parametry!$C$6),0,IF(C297&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D297&lt;=0,C297&gt;Parametry!$C$6),0,IF(C297&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F297" s="16">
@@ -15516,7 +15516,7 @@
         <v/>
       </c>
       <c r="G297" s="16">
-        <f>IF(OR(D297&lt;=0,C297&gt;Parametry!$C$6),0,MIN(IF(C297&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D297+F297,2)))</f>
+        <f>IF(OR(D297&lt;=0,C297&gt;Parametry!$C$6),0,MIN(IF(C297&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D297+F297,2)))</f>
         <v/>
       </c>
       <c r="H297" s="18" t="n"/>
@@ -15557,7 +15557,7 @@
         <v/>
       </c>
       <c r="E298" s="26">
-        <f>IF(OR(D298&lt;=0,C298&gt;Parametry!$C$6),0,IF(C298&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D298&lt;=0,C298&gt;Parametry!$C$6),0,IF(C298&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F298" s="25">
@@ -15565,7 +15565,7 @@
         <v/>
       </c>
       <c r="G298" s="25">
-        <f>IF(OR(D298&lt;=0,C298&gt;Parametry!$C$6),0,MIN(IF(C298&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D298+F298,2)))</f>
+        <f>IF(OR(D298&lt;=0,C298&gt;Parametry!$C$6),0,MIN(IF(C298&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D298+F298,2)))</f>
         <v/>
       </c>
       <c r="H298" s="18" t="n"/>
@@ -15606,7 +15606,7 @@
         <v/>
       </c>
       <c r="E299" s="17">
-        <f>IF(OR(D299&lt;=0,C299&gt;Parametry!$C$6),0,IF(C299&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D299&lt;=0,C299&gt;Parametry!$C$6),0,IF(C299&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F299" s="16">
@@ -15614,7 +15614,7 @@
         <v/>
       </c>
       <c r="G299" s="16">
-        <f>IF(OR(D299&lt;=0,C299&gt;Parametry!$C$6),0,MIN(IF(C299&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D299+F299,2)))</f>
+        <f>IF(OR(D299&lt;=0,C299&gt;Parametry!$C$6),0,MIN(IF(C299&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D299+F299,2)))</f>
         <v/>
       </c>
       <c r="H299" s="18" t="n"/>
@@ -15655,7 +15655,7 @@
         <v/>
       </c>
       <c r="E300" s="26">
-        <f>IF(OR(D300&lt;=0,C300&gt;Parametry!$C$6),0,IF(C300&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D300&lt;=0,C300&gt;Parametry!$C$6),0,IF(C300&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F300" s="25">
@@ -15663,7 +15663,7 @@
         <v/>
       </c>
       <c r="G300" s="25">
-        <f>IF(OR(D300&lt;=0,C300&gt;Parametry!$C$6),0,MIN(IF(C300&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D300+F300,2)))</f>
+        <f>IF(OR(D300&lt;=0,C300&gt;Parametry!$C$6),0,MIN(IF(C300&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D300+F300,2)))</f>
         <v/>
       </c>
       <c r="H300" s="18" t="n"/>
@@ -15704,7 +15704,7 @@
         <v/>
       </c>
       <c r="E301" s="17">
-        <f>IF(OR(D301&lt;=0,C301&gt;Parametry!$C$6),0,IF(C301&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D301&lt;=0,C301&gt;Parametry!$C$6),0,IF(C301&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F301" s="16">
@@ -15712,7 +15712,7 @@
         <v/>
       </c>
       <c r="G301" s="16">
-        <f>IF(OR(D301&lt;=0,C301&gt;Parametry!$C$6),0,MIN(IF(C301&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D301+F301,2)))</f>
+        <f>IF(OR(D301&lt;=0,C301&gt;Parametry!$C$6),0,MIN(IF(C301&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D301+F301,2)))</f>
         <v/>
       </c>
       <c r="H301" s="18" t="n"/>
@@ -15753,7 +15753,7 @@
         <v/>
       </c>
       <c r="E302" s="26">
-        <f>IF(OR(D302&lt;=0,C302&gt;Parametry!$C$6),0,IF(C302&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D302&lt;=0,C302&gt;Parametry!$C$6),0,IF(C302&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F302" s="25">
@@ -15761,7 +15761,7 @@
         <v/>
       </c>
       <c r="G302" s="25">
-        <f>IF(OR(D302&lt;=0,C302&gt;Parametry!$C$6),0,MIN(IF(C302&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D302+F302,2)))</f>
+        <f>IF(OR(D302&lt;=0,C302&gt;Parametry!$C$6),0,MIN(IF(C302&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D302+F302,2)))</f>
         <v/>
       </c>
       <c r="H302" s="18" t="n"/>
@@ -15802,7 +15802,7 @@
         <v/>
       </c>
       <c r="E303" s="17">
-        <f>IF(OR(D303&lt;=0,C303&gt;Parametry!$C$6),0,IF(C303&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D303&lt;=0,C303&gt;Parametry!$C$6),0,IF(C303&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F303" s="16">
@@ -15810,7 +15810,7 @@
         <v/>
       </c>
       <c r="G303" s="16">
-        <f>IF(OR(D303&lt;=0,C303&gt;Parametry!$C$6),0,MIN(IF(C303&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D303+F303,2)))</f>
+        <f>IF(OR(D303&lt;=0,C303&gt;Parametry!$C$6),0,MIN(IF(C303&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D303+F303,2)))</f>
         <v/>
       </c>
       <c r="H303" s="18" t="n"/>
@@ -15851,7 +15851,7 @@
         <v/>
       </c>
       <c r="E304" s="26">
-        <f>IF(OR(D304&lt;=0,C304&gt;Parametry!$C$6),0,IF(C304&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D304&lt;=0,C304&gt;Parametry!$C$6),0,IF(C304&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F304" s="25">
@@ -15859,7 +15859,7 @@
         <v/>
       </c>
       <c r="G304" s="25">
-        <f>IF(OR(D304&lt;=0,C304&gt;Parametry!$C$6),0,MIN(IF(C304&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D304+F304,2)))</f>
+        <f>IF(OR(D304&lt;=0,C304&gt;Parametry!$C$6),0,MIN(IF(C304&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D304+F304,2)))</f>
         <v/>
       </c>
       <c r="H304" s="18" t="n"/>
@@ -15900,7 +15900,7 @@
         <v/>
       </c>
       <c r="E305" s="17">
-        <f>IF(OR(D305&lt;=0,C305&gt;Parametry!$C$6),0,IF(C305&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D305&lt;=0,C305&gt;Parametry!$C$6),0,IF(C305&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F305" s="16">
@@ -15908,7 +15908,7 @@
         <v/>
       </c>
       <c r="G305" s="16">
-        <f>IF(OR(D305&lt;=0,C305&gt;Parametry!$C$6),0,MIN(IF(C305&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D305+F305,2)))</f>
+        <f>IF(OR(D305&lt;=0,C305&gt;Parametry!$C$6),0,MIN(IF(C305&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D305+F305,2)))</f>
         <v/>
       </c>
       <c r="H305" s="18" t="n"/>
@@ -15949,7 +15949,7 @@
         <v/>
       </c>
       <c r="E306" s="26">
-        <f>IF(OR(D306&lt;=0,C306&gt;Parametry!$C$6),0,IF(C306&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D306&lt;=0,C306&gt;Parametry!$C$6),0,IF(C306&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F306" s="25">
@@ -15957,7 +15957,7 @@
         <v/>
       </c>
       <c r="G306" s="25">
-        <f>IF(OR(D306&lt;=0,C306&gt;Parametry!$C$6),0,MIN(IF(C306&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D306+F306,2)))</f>
+        <f>IF(OR(D306&lt;=0,C306&gt;Parametry!$C$6),0,MIN(IF(C306&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D306+F306,2)))</f>
         <v/>
       </c>
       <c r="H306" s="18" t="n"/>
@@ -15998,7 +15998,7 @@
         <v/>
       </c>
       <c r="E307" s="17">
-        <f>IF(OR(D307&lt;=0,C307&gt;Parametry!$C$6),0,IF(C307&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D307&lt;=0,C307&gt;Parametry!$C$6),0,IF(C307&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F307" s="16">
@@ -16006,7 +16006,7 @@
         <v/>
       </c>
       <c r="G307" s="16">
-        <f>IF(OR(D307&lt;=0,C307&gt;Parametry!$C$6),0,MIN(IF(C307&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D307+F307,2)))</f>
+        <f>IF(OR(D307&lt;=0,C307&gt;Parametry!$C$6),0,MIN(IF(C307&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D307+F307,2)))</f>
         <v/>
       </c>
       <c r="H307" s="18" t="n"/>
@@ -16047,7 +16047,7 @@
         <v/>
       </c>
       <c r="E308" s="26">
-        <f>IF(OR(D308&lt;=0,C308&gt;Parametry!$C$6),0,IF(C308&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D308&lt;=0,C308&gt;Parametry!$C$6),0,IF(C308&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F308" s="25">
@@ -16055,7 +16055,7 @@
         <v/>
       </c>
       <c r="G308" s="25">
-        <f>IF(OR(D308&lt;=0,C308&gt;Parametry!$C$6),0,MIN(IF(C308&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D308+F308,2)))</f>
+        <f>IF(OR(D308&lt;=0,C308&gt;Parametry!$C$6),0,MIN(IF(C308&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D308+F308,2)))</f>
         <v/>
       </c>
       <c r="H308" s="18" t="n"/>
@@ -16096,7 +16096,7 @@
         <v/>
       </c>
       <c r="E309" s="17">
-        <f>IF(OR(D309&lt;=0,C309&gt;Parametry!$C$6),0,IF(C309&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D309&lt;=0,C309&gt;Parametry!$C$6),0,IF(C309&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F309" s="16">
@@ -16104,7 +16104,7 @@
         <v/>
       </c>
       <c r="G309" s="16">
-        <f>IF(OR(D309&lt;=0,C309&gt;Parametry!$C$6),0,MIN(IF(C309&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D309+F309,2)))</f>
+        <f>IF(OR(D309&lt;=0,C309&gt;Parametry!$C$6),0,MIN(IF(C309&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D309+F309,2)))</f>
         <v/>
       </c>
       <c r="H309" s="18" t="n"/>
@@ -16145,7 +16145,7 @@
         <v/>
       </c>
       <c r="E310" s="26">
-        <f>IF(OR(D310&lt;=0,C310&gt;Parametry!$C$6),0,IF(C310&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D310&lt;=0,C310&gt;Parametry!$C$6),0,IF(C310&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F310" s="25">
@@ -16153,7 +16153,7 @@
         <v/>
       </c>
       <c r="G310" s="25">
-        <f>IF(OR(D310&lt;=0,C310&gt;Parametry!$C$6),0,MIN(IF(C310&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D310+F310,2)))</f>
+        <f>IF(OR(D310&lt;=0,C310&gt;Parametry!$C$6),0,MIN(IF(C310&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D310+F310,2)))</f>
         <v/>
       </c>
       <c r="H310" s="18" t="n"/>
@@ -16194,7 +16194,7 @@
         <v/>
       </c>
       <c r="E311" s="17">
-        <f>IF(OR(D311&lt;=0,C311&gt;Parametry!$C$6),0,IF(C311&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D311&lt;=0,C311&gt;Parametry!$C$6),0,IF(C311&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F311" s="16">
@@ -16202,7 +16202,7 @@
         <v/>
       </c>
       <c r="G311" s="16">
-        <f>IF(OR(D311&lt;=0,C311&gt;Parametry!$C$6),0,MIN(IF(C311&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D311+F311,2)))</f>
+        <f>IF(OR(D311&lt;=0,C311&gt;Parametry!$C$6),0,MIN(IF(C311&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D311+F311,2)))</f>
         <v/>
       </c>
       <c r="H311" s="18" t="n"/>
@@ -16243,7 +16243,7 @@
         <v/>
       </c>
       <c r="E312" s="26">
-        <f>IF(OR(D312&lt;=0,C312&gt;Parametry!$C$6),0,IF(C312&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D312&lt;=0,C312&gt;Parametry!$C$6),0,IF(C312&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F312" s="25">
@@ -16251,7 +16251,7 @@
         <v/>
       </c>
       <c r="G312" s="25">
-        <f>IF(OR(D312&lt;=0,C312&gt;Parametry!$C$6),0,MIN(IF(C312&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D312+F312,2)))</f>
+        <f>IF(OR(D312&lt;=0,C312&gt;Parametry!$C$6),0,MIN(IF(C312&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D312+F312,2)))</f>
         <v/>
       </c>
       <c r="H312" s="18" t="n"/>
@@ -16292,7 +16292,7 @@
         <v/>
       </c>
       <c r="E313" s="17">
-        <f>IF(OR(D313&lt;=0,C313&gt;Parametry!$C$6),0,IF(C313&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D313&lt;=0,C313&gt;Parametry!$C$6),0,IF(C313&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F313" s="16">
@@ -16300,7 +16300,7 @@
         <v/>
       </c>
       <c r="G313" s="16">
-        <f>IF(OR(D313&lt;=0,C313&gt;Parametry!$C$6),0,MIN(IF(C313&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D313+F313,2)))</f>
+        <f>IF(OR(D313&lt;=0,C313&gt;Parametry!$C$6),0,MIN(IF(C313&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D313+F313,2)))</f>
         <v/>
       </c>
       <c r="H313" s="18" t="n"/>
@@ -16341,7 +16341,7 @@
         <v/>
       </c>
       <c r="E314" s="26">
-        <f>IF(OR(D314&lt;=0,C314&gt;Parametry!$C$6),0,IF(C314&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D314&lt;=0,C314&gt;Parametry!$C$6),0,IF(C314&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F314" s="25">
@@ -16349,7 +16349,7 @@
         <v/>
       </c>
       <c r="G314" s="25">
-        <f>IF(OR(D314&lt;=0,C314&gt;Parametry!$C$6),0,MIN(IF(C314&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D314+F314,2)))</f>
+        <f>IF(OR(D314&lt;=0,C314&gt;Parametry!$C$6),0,MIN(IF(C314&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D314+F314,2)))</f>
         <v/>
       </c>
       <c r="H314" s="18" t="n"/>
@@ -16390,7 +16390,7 @@
         <v/>
       </c>
       <c r="E315" s="17">
-        <f>IF(OR(D315&lt;=0,C315&gt;Parametry!$C$6),0,IF(C315&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D315&lt;=0,C315&gt;Parametry!$C$6),0,IF(C315&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F315" s="16">
@@ -16398,7 +16398,7 @@
         <v/>
       </c>
       <c r="G315" s="16">
-        <f>IF(OR(D315&lt;=0,C315&gt;Parametry!$C$6),0,MIN(IF(C315&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D315+F315,2)))</f>
+        <f>IF(OR(D315&lt;=0,C315&gt;Parametry!$C$6),0,MIN(IF(C315&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D315+F315,2)))</f>
         <v/>
       </c>
       <c r="H315" s="18" t="n"/>
@@ -16439,7 +16439,7 @@
         <v/>
       </c>
       <c r="E316" s="26">
-        <f>IF(OR(D316&lt;=0,C316&gt;Parametry!$C$6),0,IF(C316&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D316&lt;=0,C316&gt;Parametry!$C$6),0,IF(C316&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F316" s="25">
@@ -16447,7 +16447,7 @@
         <v/>
       </c>
       <c r="G316" s="25">
-        <f>IF(OR(D316&lt;=0,C316&gt;Parametry!$C$6),0,MIN(IF(C316&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D316+F316,2)))</f>
+        <f>IF(OR(D316&lt;=0,C316&gt;Parametry!$C$6),0,MIN(IF(C316&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D316+F316,2)))</f>
         <v/>
       </c>
       <c r="H316" s="18" t="n"/>
@@ -16488,7 +16488,7 @@
         <v/>
       </c>
       <c r="E317" s="17">
-        <f>IF(OR(D317&lt;=0,C317&gt;Parametry!$C$6),0,IF(C317&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D317&lt;=0,C317&gt;Parametry!$C$6),0,IF(C317&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F317" s="16">
@@ -16496,7 +16496,7 @@
         <v/>
       </c>
       <c r="G317" s="16">
-        <f>IF(OR(D317&lt;=0,C317&gt;Parametry!$C$6),0,MIN(IF(C317&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D317+F317,2)))</f>
+        <f>IF(OR(D317&lt;=0,C317&gt;Parametry!$C$6),0,MIN(IF(C317&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D317+F317,2)))</f>
         <v/>
       </c>
       <c r="H317" s="18" t="n"/>
@@ -16537,7 +16537,7 @@
         <v/>
       </c>
       <c r="E318" s="26">
-        <f>IF(OR(D318&lt;=0,C318&gt;Parametry!$C$6),0,IF(C318&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D318&lt;=0,C318&gt;Parametry!$C$6),0,IF(C318&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F318" s="25">
@@ -16545,7 +16545,7 @@
         <v/>
       </c>
       <c r="G318" s="25">
-        <f>IF(OR(D318&lt;=0,C318&gt;Parametry!$C$6),0,MIN(IF(C318&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D318+F318,2)))</f>
+        <f>IF(OR(D318&lt;=0,C318&gt;Parametry!$C$6),0,MIN(IF(C318&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D318+F318,2)))</f>
         <v/>
       </c>
       <c r="H318" s="18" t="n"/>
@@ -16586,7 +16586,7 @@
         <v/>
       </c>
       <c r="E319" s="17">
-        <f>IF(OR(D319&lt;=0,C319&gt;Parametry!$C$6),0,IF(C319&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D319&lt;=0,C319&gt;Parametry!$C$6),0,IF(C319&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F319" s="16">
@@ -16594,7 +16594,7 @@
         <v/>
       </c>
       <c r="G319" s="16">
-        <f>IF(OR(D319&lt;=0,C319&gt;Parametry!$C$6),0,MIN(IF(C319&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D319+F319,2)))</f>
+        <f>IF(OR(D319&lt;=0,C319&gt;Parametry!$C$6),0,MIN(IF(C319&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D319+F319,2)))</f>
         <v/>
       </c>
       <c r="H319" s="18" t="n"/>
@@ -16635,7 +16635,7 @@
         <v/>
       </c>
       <c r="E320" s="26">
-        <f>IF(OR(D320&lt;=0,C320&gt;Parametry!$C$6),0,IF(C320&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D320&lt;=0,C320&gt;Parametry!$C$6),0,IF(C320&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F320" s="25">
@@ -16643,7 +16643,7 @@
         <v/>
       </c>
       <c r="G320" s="25">
-        <f>IF(OR(D320&lt;=0,C320&gt;Parametry!$C$6),0,MIN(IF(C320&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D320+F320,2)))</f>
+        <f>IF(OR(D320&lt;=0,C320&gt;Parametry!$C$6),0,MIN(IF(C320&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D320+F320,2)))</f>
         <v/>
       </c>
       <c r="H320" s="18" t="n"/>
@@ -16684,7 +16684,7 @@
         <v/>
       </c>
       <c r="E321" s="17">
-        <f>IF(OR(D321&lt;=0,C321&gt;Parametry!$C$6),0,IF(C321&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D321&lt;=0,C321&gt;Parametry!$C$6),0,IF(C321&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F321" s="16">
@@ -16692,7 +16692,7 @@
         <v/>
       </c>
       <c r="G321" s="16">
-        <f>IF(OR(D321&lt;=0,C321&gt;Parametry!$C$6),0,MIN(IF(C321&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D321+F321,2)))</f>
+        <f>IF(OR(D321&lt;=0,C321&gt;Parametry!$C$6),0,MIN(IF(C321&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D321+F321,2)))</f>
         <v/>
       </c>
       <c r="H321" s="18" t="n"/>
@@ -16733,7 +16733,7 @@
         <v/>
       </c>
       <c r="E322" s="26">
-        <f>IF(OR(D322&lt;=0,C322&gt;Parametry!$C$6),0,IF(C322&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D322&lt;=0,C322&gt;Parametry!$C$6),0,IF(C322&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F322" s="25">
@@ -16741,7 +16741,7 @@
         <v/>
       </c>
       <c r="G322" s="25">
-        <f>IF(OR(D322&lt;=0,C322&gt;Parametry!$C$6),0,MIN(IF(C322&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D322+F322,2)))</f>
+        <f>IF(OR(D322&lt;=0,C322&gt;Parametry!$C$6),0,MIN(IF(C322&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D322+F322,2)))</f>
         <v/>
       </c>
       <c r="H322" s="18" t="n"/>
@@ -16782,7 +16782,7 @@
         <v/>
       </c>
       <c r="E323" s="17">
-        <f>IF(OR(D323&lt;=0,C323&gt;Parametry!$C$6),0,IF(C323&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D323&lt;=0,C323&gt;Parametry!$C$6),0,IF(C323&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F323" s="16">
@@ -16790,7 +16790,7 @@
         <v/>
       </c>
       <c r="G323" s="16">
-        <f>IF(OR(D323&lt;=0,C323&gt;Parametry!$C$6),0,MIN(IF(C323&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D323+F323,2)))</f>
+        <f>IF(OR(D323&lt;=0,C323&gt;Parametry!$C$6),0,MIN(IF(C323&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D323+F323,2)))</f>
         <v/>
       </c>
       <c r="H323" s="18" t="n"/>
@@ -16831,7 +16831,7 @@
         <v/>
       </c>
       <c r="E324" s="26">
-        <f>IF(OR(D324&lt;=0,C324&gt;Parametry!$C$6),0,IF(C324&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D324&lt;=0,C324&gt;Parametry!$C$6),0,IF(C324&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F324" s="25">
@@ -16839,7 +16839,7 @@
         <v/>
       </c>
       <c r="G324" s="25">
-        <f>IF(OR(D324&lt;=0,C324&gt;Parametry!$C$6),0,MIN(IF(C324&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D324+F324,2)))</f>
+        <f>IF(OR(D324&lt;=0,C324&gt;Parametry!$C$6),0,MIN(IF(C324&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D324+F324,2)))</f>
         <v/>
       </c>
       <c r="H324" s="18" t="n"/>
@@ -16880,7 +16880,7 @@
         <v/>
       </c>
       <c r="E325" s="17">
-        <f>IF(OR(D325&lt;=0,C325&gt;Parametry!$C$6),0,IF(C325&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D325&lt;=0,C325&gt;Parametry!$C$6),0,IF(C325&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F325" s="16">
@@ -16888,7 +16888,7 @@
         <v/>
       </c>
       <c r="G325" s="16">
-        <f>IF(OR(D325&lt;=0,C325&gt;Parametry!$C$6),0,MIN(IF(C325&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D325+F325,2)))</f>
+        <f>IF(OR(D325&lt;=0,C325&gt;Parametry!$C$6),0,MIN(IF(C325&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D325+F325,2)))</f>
         <v/>
       </c>
       <c r="H325" s="18" t="n"/>
@@ -16929,7 +16929,7 @@
         <v/>
       </c>
       <c r="E326" s="26">
-        <f>IF(OR(D326&lt;=0,C326&gt;Parametry!$C$6),0,IF(C326&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D326&lt;=0,C326&gt;Parametry!$C$6),0,IF(C326&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F326" s="25">
@@ -16937,7 +16937,7 @@
         <v/>
       </c>
       <c r="G326" s="25">
-        <f>IF(OR(D326&lt;=0,C326&gt;Parametry!$C$6),0,MIN(IF(C326&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D326+F326,2)))</f>
+        <f>IF(OR(D326&lt;=0,C326&gt;Parametry!$C$6),0,MIN(IF(C326&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D326+F326,2)))</f>
         <v/>
       </c>
       <c r="H326" s="18" t="n"/>
@@ -16978,7 +16978,7 @@
         <v/>
       </c>
       <c r="E327" s="17">
-        <f>IF(OR(D327&lt;=0,C327&gt;Parametry!$C$6),0,IF(C327&lt;=Parametry!$C$9+1,Parametry!$C$8,Parametry!$C$10))</f>
+        <f>IF(OR(D327&lt;=0,C327&gt;Parametry!$C$6),0,IF(C327&lt;Parametry!$C$9,Parametry!$C$8,Parametry!$C$10))</f>
         <v/>
       </c>
       <c r="F327" s="16">
@@ -16986,7 +16986,7 @@
         <v/>
       </c>
       <c r="G327" s="16">
-        <f>IF(OR(D327&lt;=0,C327&gt;Parametry!$C$6),0,MIN(IF(C327&lt;=Parametry!$C$9+1,Parametry!$C$7,Parametry!$C$14),ROUND(D327+F327,2)))</f>
+        <f>IF(OR(D327&lt;=0,C327&gt;Parametry!$C$6),0,MIN(IF(C327&lt;Parametry!$C$9,Parametry!$C$7,Parametry!$C$14),ROUND(D327+F327,2)))</f>
         <v/>
       </c>
       <c r="H327" s="18" t="n"/>
